--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$351</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$415</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="446">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1267,6 +1267,99 @@
   </si>
   <si>
     <t>FERRETERIA BEDINI</t>
+  </si>
+  <si>
+    <t>LOS PRIMOS FERRETERIA</t>
+  </si>
+  <si>
+    <t>FERRETERIA ACYCA</t>
+  </si>
+  <si>
+    <t>BENJA LOS 22 FERRETE</t>
+  </si>
+  <si>
+    <t>FERRETERIA 07</t>
+  </si>
+  <si>
+    <t>EL PORTUGUECITO CORR</t>
+  </si>
+  <si>
+    <t>FERRETERIA NEXO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERRETERIA LA LOMA </t>
+  </si>
+  <si>
+    <t>FERRETERIA ARI</t>
+  </si>
+  <si>
+    <t>FERNANDO ELECTRICIDA</t>
+  </si>
+  <si>
+    <t>CASA PORTUGAL</t>
+  </si>
+  <si>
+    <t>FERRETERIA JUAN</t>
+  </si>
+  <si>
+    <t>FERRETERIA ULISES</t>
+  </si>
+  <si>
+    <t>FERRETERIA HUMBERTO</t>
+  </si>
+  <si>
+    <t>FERRETERIA DAUBERT</t>
+  </si>
+  <si>
+    <t>POLIRUBRO ROCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   FERRETERIA FACU</t>
+  </si>
+  <si>
+    <t>FERRETERIA MARTINEZ</t>
+  </si>
+  <si>
+    <t>FERRETERIA BECO</t>
+  </si>
+  <si>
+    <t>FERRETERIA ARGENTINA</t>
+  </si>
+  <si>
+    <t>GRAMA COMERCIAL</t>
+  </si>
+  <si>
+    <t>PALOMER FERRETERIA</t>
+  </si>
+  <si>
+    <t>FERRETERIA FERREMAX</t>
+  </si>
+  <si>
+    <t>FERRETERIA SANTA ANG</t>
+  </si>
+  <si>
+    <t>CORRALON 1003</t>
+  </si>
+  <si>
+    <t>CORRALON MIMA</t>
+  </si>
+  <si>
+    <t>FERRETERIA LA SOLUCI</t>
+  </si>
+  <si>
+    <t>BENITO SOSA FERRETER</t>
+  </si>
+  <si>
+    <t>SPIRO EDUARDO FERRET</t>
+  </si>
+  <si>
+    <t>FERRETERIA DUARTE HE</t>
+  </si>
+  <si>
+    <t>EL POCHOLO FERRETERI</t>
+  </si>
+  <si>
+    <t>FERRETERIA JULIAN</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1392,6 +1485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1621,7 +1715,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D408"/>
+  <dimension ref="A1:D439"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1841,10 +1935,10 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>416</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1855,24 +1949,24 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B17" t="s">
-        <v>393</v>
+        <v>195</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>933</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>413</v>
+        <v>921</v>
+      </c>
+      <c r="B18" t="s">
+        <v>393</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1883,52 +1977,52 @@
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>936</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
+        <v>933</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>413</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B20" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>8</v>
+      <c r="D21" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1939,38 +2033,38 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D23" t="s">
-        <v>9</v>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>8</v>
+      <c r="D24" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1981,10 +2075,10 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1995,52 +2089,52 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B27" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D28" t="s">
-        <v>9</v>
+      <c r="D28" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>8</v>
+      <c r="D29" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -2051,10 +2145,10 @@
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B31" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -2065,38 +2159,38 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>8</v>
+      <c r="D33" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -2107,24 +2201,24 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
+      <c r="D35" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -2135,66 +2229,66 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>8</v>
+      <c r="D37" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B38" t="s">
-        <v>226</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D38" t="s">
-        <v>9</v>
+      <c r="D38" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B39" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>5</v>
+      <c r="D39" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>8</v>
+      <c r="D40" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -2205,10 +2299,10 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -2219,24 +2313,24 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B43" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>5</v>
+      <c r="D43" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -2247,66 +2341,66 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
-        <v>990</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>414</v>
+        <v>989</v>
+      </c>
+      <c r="B46" t="s">
+        <v>191</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>992</v>
-      </c>
-      <c r="B47" t="s">
-        <v>66</v>
+        <v>990</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>414</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>8</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>993</v>
-      </c>
-      <c r="B48" t="s">
-        <v>78</v>
+        <v>991</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>417</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -2317,10 +2411,10 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B50" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -2331,10 +2425,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -2345,24 +2439,24 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B52" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D52" t="s">
-        <v>9</v>
+      <c r="D52" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B53" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -2373,24 +2467,24 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>8</v>
+      <c r="D54" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>222</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -2401,10 +2495,10 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B56" t="s">
-        <v>182</v>
+        <v>75</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -2415,24 +2509,24 @@
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B58" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
@@ -2443,80 +2537,80 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>8</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>214</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D60" t="s">
-        <v>9</v>
+      <c r="D60" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="B61" t="s">
-        <v>189</v>
+        <v>74</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D61" t="s">
-        <v>9</v>
+      <c r="D61" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B62" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>8</v>
+      <c r="D62" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>8</v>
+      <c r="D63" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>1018</v>
-      </c>
-      <c r="B64" s="18" t="s">
-        <v>399</v>
+        <v>1013</v>
+      </c>
+      <c r="B64" t="s">
+        <v>152</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
@@ -2527,38 +2621,38 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B65" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="11" t="s">
-        <v>5</v>
+      <c r="D65" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>1021</v>
-      </c>
-      <c r="B66" t="s">
-        <v>367</v>
+        <v>1018</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="14" t="s">
-        <v>5</v>
+      <c r="D66" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="B67" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
@@ -2569,80 +2663,80 @@
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B68" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B69" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B70" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B71" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B72" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B73" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
@@ -2653,38 +2747,38 @@
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B74" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>1031</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>346</v>
+        <v>1029</v>
+      </c>
+      <c r="B75" t="s">
+        <v>359</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="14" t="s">
-        <v>8</v>
+      <c r="D75" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B76" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
@@ -2695,38 +2789,38 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>1033</v>
-      </c>
-      <c r="B77" t="s">
-        <v>357</v>
+        <v>1031</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>346</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D77" s="11" t="s">
-        <v>5</v>
+      <c r="D77" s="14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>1034</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>373</v>
+        <v>1032</v>
+      </c>
+      <c r="B78" t="s">
+        <v>369</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D78" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>1035</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>345</v>
+        <v>1033</v>
+      </c>
+      <c r="B79" t="s">
+        <v>357</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
@@ -2737,10 +2831,10 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>1036</v>
-      </c>
-      <c r="B80" t="s">
-        <v>358</v>
+        <v>1034</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>373</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
@@ -2751,10 +2845,10 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>1037</v>
-      </c>
-      <c r="B81" t="s">
-        <v>353</v>
+        <v>1035</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>345</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
@@ -2765,10 +2859,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B82" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
@@ -2779,10 +2873,10 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B83" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
@@ -2793,24 +2887,24 @@
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B84" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B85" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
@@ -2821,94 +2915,94 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="B86" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="B87" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B88" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>1050</v>
-      </c>
-      <c r="B89" s="18" t="s">
-        <v>409</v>
+        <v>1048</v>
+      </c>
+      <c r="B89" t="s">
+        <v>404</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>1416</v>
+        <v>1049</v>
       </c>
       <c r="B90" t="s">
-        <v>217</v>
+        <v>406</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10107</v>
-      </c>
-      <c r="B91" t="s">
-        <v>96</v>
+        <v>1050</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>409</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D91" t="s">
-        <v>9</v>
+      <c r="D91" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10137</v>
+        <v>1416</v>
       </c>
       <c r="B92" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
@@ -2919,24 +3013,24 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10157</v>
+        <v>10107</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>8</v>
+      <c r="D93" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10158</v>
+        <v>10137</v>
       </c>
       <c r="B94" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
@@ -2947,24 +3041,24 @@
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10160</v>
+        <v>10157</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="13" t="s">
-        <v>5</v>
+      <c r="D95" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10162</v>
+        <v>10158</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
@@ -2975,10 +3069,10 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10163</v>
+        <v>10160</v>
       </c>
       <c r="B97" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
@@ -2989,10 +3083,10 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10165</v>
+        <v>10162</v>
       </c>
       <c r="B98" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
@@ -3003,136 +3097,136 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>348</v>
+        <v>10163</v>
+      </c>
+      <c r="B99" t="s">
+        <v>90</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="11" t="s">
-        <v>8</v>
+      <c r="D99" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>10167</v>
+        <v>10165</v>
       </c>
       <c r="B100" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="13" t="s">
-        <v>5</v>
+      <c r="D100" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>10424</v>
-      </c>
-      <c r="B101" t="s">
-        <v>12</v>
+        <v>10166</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D101" s="17" t="s">
-        <v>9</v>
+      <c r="D101" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>10425</v>
+        <v>10167</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="17" t="s">
-        <v>9</v>
+      <c r="D102" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20094</v>
+        <v>10424</v>
       </c>
       <c r="B103" t="s">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="10" t="s">
-        <v>8</v>
+      <c r="D103" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20095</v>
+        <v>10425</v>
       </c>
       <c r="B104" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="10" t="s">
-        <v>8</v>
+      <c r="D104" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20096</v>
+        <v>20094</v>
       </c>
       <c r="B105" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20100</v>
+        <v>20095</v>
       </c>
       <c r="B106" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20101</v>
+        <v>20096</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D107" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20103</v>
+        <v>20100</v>
       </c>
       <c r="B108" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
@@ -3143,38 +3237,38 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20106</v>
+        <v>20101</v>
       </c>
       <c r="B109" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20108</v>
+        <v>20103</v>
       </c>
       <c r="B110" t="s">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="D110" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20109</v>
+        <v>20106</v>
       </c>
       <c r="B111" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3185,66 +3279,66 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20110</v>
+        <v>20108</v>
       </c>
       <c r="B112" t="s">
-        <v>33</v>
+        <v>219</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="13" t="s">
-        <v>5</v>
+      <c r="D112" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20113</v>
+        <v>20109</v>
       </c>
       <c r="B113" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="D113" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20114</v>
+        <v>20110</v>
       </c>
       <c r="B114" t="s">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>8</v>
+      <c r="D114" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20116</v>
+        <v>20113</v>
       </c>
       <c r="B115" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20117</v>
+        <v>20114</v>
       </c>
       <c r="B116" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
@@ -3255,10 +3349,10 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20118</v>
+        <v>20116</v>
       </c>
       <c r="B117" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
@@ -3269,10 +3363,10 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20120</v>
+        <v>20117</v>
       </c>
       <c r="B118" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
@@ -3283,10 +3377,10 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20121</v>
+        <v>20118</v>
       </c>
       <c r="B119" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
@@ -3297,24 +3391,24 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20125</v>
+        <v>20120</v>
       </c>
       <c r="B120" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20127</v>
+        <v>20121</v>
       </c>
       <c r="B121" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3325,108 +3419,108 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20128</v>
+        <v>20125</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>88</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20129</v>
+        <v>20127</v>
       </c>
       <c r="B123" t="s">
-        <v>326</v>
+        <v>168</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20137</v>
+        <v>20128</v>
       </c>
       <c r="B124" t="s">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>5</v>
+      <c r="D124" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20138</v>
+        <v>20129</v>
       </c>
       <c r="B125" t="s">
-        <v>113</v>
+        <v>326</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="13" t="s">
-        <v>5</v>
+      <c r="D125" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20140</v>
+        <v>20137</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D126" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20142</v>
+        <v>20138</v>
       </c>
       <c r="B127" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>8</v>
+      <c r="D127" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20146</v>
+        <v>20140</v>
       </c>
       <c r="B128" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>8</v>
+      <c r="D128" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20148</v>
+        <v>20142</v>
       </c>
       <c r="B129" t="s">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
@@ -3437,38 +3531,38 @@
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20156</v>
+        <v>20146</v>
       </c>
       <c r="B130" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="D130" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20159</v>
+        <v>20148</v>
       </c>
       <c r="B131" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="17" t="s">
-        <v>9</v>
+      <c r="D131" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20160</v>
+        <v>20156</v>
       </c>
       <c r="B132" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
@@ -3479,38 +3573,38 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20163</v>
+        <v>20159</v>
       </c>
       <c r="B133" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="10" t="s">
-        <v>8</v>
+      <c r="D133" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20164</v>
+        <v>20160</v>
       </c>
       <c r="B134" t="s">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" t="s">
-        <v>9</v>
+      <c r="D134" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20165</v>
+        <v>20163</v>
       </c>
       <c r="B135" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
@@ -3521,52 +3615,52 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20166</v>
+        <v>20164</v>
       </c>
       <c r="B136" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>8</v>
+      <c r="D136" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20169</v>
+        <v>20165</v>
       </c>
       <c r="B137" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20173</v>
+        <v>20166</v>
       </c>
       <c r="B138" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="10" t="s">
+      <c r="D138" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20174</v>
+        <v>20169</v>
       </c>
       <c r="B139" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
@@ -3577,38 +3671,38 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20178</v>
+        <v>20173</v>
       </c>
       <c r="B140" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="D140" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20179</v>
+        <v>20174</v>
       </c>
       <c r="B141" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" t="s">
-        <v>9</v>
+      <c r="D141" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20180</v>
+        <v>20178</v>
       </c>
       <c r="B142" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
@@ -3619,24 +3713,24 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20183</v>
+        <v>20179</v>
       </c>
       <c r="B143" t="s">
-        <v>370</v>
+        <v>171</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="14" t="s">
-        <v>5</v>
+      <c r="D143" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20189</v>
+        <v>20180</v>
       </c>
       <c r="B144" t="s">
-        <v>329</v>
+        <v>149</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
@@ -3647,66 +3741,66 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20200</v>
+        <v>20183</v>
       </c>
       <c r="B145" t="s">
-        <v>83</v>
+        <v>370</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="13" t="s">
+      <c r="D145" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20201</v>
+        <v>20189</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="13" t="s">
-        <v>5</v>
+      <c r="D146" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20204</v>
+        <v>20200</v>
       </c>
       <c r="B147" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="10" t="s">
-        <v>8</v>
+      <c r="D147" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20205</v>
+        <v>20201</v>
       </c>
       <c r="B148" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="1" t="s">
-        <v>9</v>
+      <c r="D148" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20211</v>
+        <v>20204</v>
       </c>
       <c r="B149" t="s">
-        <v>190</v>
+        <v>57</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
@@ -3717,24 +3811,24 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20224</v>
+        <v>20205</v>
       </c>
       <c r="B150" t="s">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20227</v>
+        <v>20211</v>
       </c>
       <c r="B151" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
@@ -3745,24 +3839,24 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20228</v>
+        <v>20224</v>
       </c>
       <c r="B152" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="13" t="s">
-        <v>5</v>
+      <c r="D152" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20230</v>
+        <v>20227</v>
       </c>
       <c r="B153" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
@@ -3773,10 +3867,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20234</v>
+        <v>20228</v>
       </c>
       <c r="B154" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
@@ -3787,24 +3881,24 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20236</v>
+        <v>20230</v>
       </c>
       <c r="B155" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="3" t="s">
-        <v>5</v>
+      <c r="D155" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20238</v>
+        <v>20234</v>
       </c>
       <c r="B156" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
@@ -3815,66 +3909,66 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20241</v>
+        <v>20236</v>
       </c>
       <c r="B157" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="13" t="s">
+      <c r="D157" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20242</v>
+        <v>20238</v>
       </c>
       <c r="B158" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="10" t="s">
-        <v>8</v>
+      <c r="D158" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20244</v>
+        <v>20241</v>
       </c>
       <c r="B159" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="10" t="s">
-        <v>8</v>
+      <c r="D159" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20246</v>
+        <v>20242</v>
       </c>
       <c r="B160" t="s">
-        <v>14</v>
+        <v>216</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="13" t="s">
-        <v>5</v>
+      <c r="D160" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20249</v>
+        <v>20244</v>
       </c>
       <c r="B161" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
@@ -3885,38 +3979,38 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20256</v>
+        <v>20246</v>
       </c>
       <c r="B162" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="1" t="s">
-        <v>8</v>
+      <c r="D162" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20257</v>
+        <v>20249</v>
       </c>
       <c r="B163" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="17" t="s">
-        <v>9</v>
+      <c r="D163" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20258</v>
+        <v>20256</v>
       </c>
       <c r="B164" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
@@ -3927,94 +4021,94 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20260</v>
+        <v>20257</v>
       </c>
       <c r="B165" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="13" t="s">
-        <v>5</v>
+      <c r="D165" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20261</v>
+        <v>20258</v>
       </c>
       <c r="B166" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="10" t="s">
+      <c r="D166" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20262</v>
+        <v>20260</v>
       </c>
       <c r="B167" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="10" t="s">
-        <v>8</v>
+      <c r="D167" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20267</v>
+        <v>20261</v>
       </c>
       <c r="B168" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20268</v>
+        <v>20262</v>
       </c>
       <c r="B169" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="D169" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20271</v>
+        <v>20267</v>
       </c>
       <c r="B170" t="s">
-        <v>34</v>
+        <v>401</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="13" t="s">
+      <c r="D170" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20272</v>
+        <v>20268</v>
       </c>
       <c r="B171" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
@@ -4025,10 +4119,10 @@
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20275</v>
+        <v>20271</v>
       </c>
       <c r="B172" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
@@ -4039,10 +4133,10 @@
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20277</v>
+        <v>20272</v>
       </c>
       <c r="B173" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
@@ -4053,80 +4147,80 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20281</v>
+        <v>20275</v>
       </c>
       <c r="B174" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="3" t="s">
+      <c r="D174" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20282</v>
+        <v>20277</v>
       </c>
       <c r="B175" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20284</v>
+        <v>20281</v>
       </c>
       <c r="B176" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="17" t="s">
-        <v>9</v>
+      <c r="D176" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20285</v>
+        <v>20282</v>
       </c>
       <c r="B177" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20289</v>
+        <v>20284</v>
       </c>
       <c r="B178" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="3" t="s">
-        <v>5</v>
+      <c r="D178" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20290</v>
+        <v>20285</v>
       </c>
       <c r="B179" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
@@ -4137,66 +4231,66 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20291</v>
+        <v>20289</v>
       </c>
       <c r="B180" t="s">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="10" t="s">
-        <v>8</v>
+      <c r="D180" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20292</v>
+        <v>20290</v>
       </c>
       <c r="B181" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="13" t="s">
-        <v>5</v>
+      <c r="D181" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20293</v>
+        <v>20291</v>
       </c>
       <c r="B182" t="s">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="13" t="s">
-        <v>5</v>
+      <c r="D182" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20294</v>
+        <v>20292</v>
       </c>
       <c r="B183" t="s">
-        <v>202</v>
+        <v>32</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="10" t="s">
-        <v>8</v>
+      <c r="D183" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20296</v>
+        <v>20293</v>
       </c>
       <c r="B184" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
@@ -4207,38 +4301,38 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20298</v>
+        <v>20294</v>
       </c>
       <c r="B185" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="D185" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20299</v>
+        <v>20296</v>
       </c>
       <c r="B186" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="1" t="s">
-        <v>8</v>
+      <c r="D186" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20301</v>
+        <v>20298</v>
       </c>
       <c r="B187" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
@@ -4249,10 +4343,10 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20303</v>
+        <v>20299</v>
       </c>
       <c r="B188" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
@@ -4263,66 +4357,66 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20309</v>
+        <v>20301</v>
       </c>
       <c r="B189" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="13" t="s">
-        <v>5</v>
+      <c r="D189" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20310</v>
+        <v>20303</v>
       </c>
       <c r="B190" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="13" t="s">
-        <v>5</v>
+      <c r="D190" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20318</v>
+        <v>20309</v>
       </c>
       <c r="B191" t="s">
-        <v>209</v>
+        <v>28</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="1" t="s">
-        <v>8</v>
+      <c r="D191" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20319</v>
+        <v>20310</v>
       </c>
       <c r="B192" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="10" t="s">
-        <v>8</v>
+      <c r="D192" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20320</v>
+        <v>20318</v>
       </c>
       <c r="B193" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4333,24 +4427,24 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20324</v>
+        <v>20319</v>
       </c>
       <c r="B194" t="s">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="D194" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20331</v>
+        <v>20320</v>
       </c>
       <c r="B195" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
@@ -4361,24 +4455,24 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20333</v>
+        <v>20324</v>
       </c>
       <c r="B196" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="13" t="s">
-        <v>5</v>
+      <c r="D196" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20337</v>
+        <v>20331</v>
       </c>
       <c r="B197" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4389,24 +4483,24 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20343</v>
+        <v>20333</v>
       </c>
       <c r="B198" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>8</v>
+      <c r="D198" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20344</v>
+        <v>20337</v>
       </c>
       <c r="B199" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
@@ -4417,24 +4511,24 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20351</v>
+        <v>20343</v>
       </c>
       <c r="B200" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="13" t="s">
-        <v>5</v>
+      <c r="D200" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20357</v>
+        <v>20344</v>
       </c>
       <c r="B201" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4445,10 +4539,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20361</v>
+        <v>20351</v>
       </c>
       <c r="B202" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4459,80 +4553,80 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20362</v>
+        <v>20357</v>
       </c>
       <c r="B203" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="10" t="s">
+      <c r="D203" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20363</v>
+        <v>20361</v>
       </c>
       <c r="B204" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="10" t="s">
-        <v>8</v>
+      <c r="D204" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20364</v>
+        <v>20362</v>
       </c>
       <c r="B205" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="13" t="s">
-        <v>5</v>
+      <c r="D205" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20366</v>
+        <v>20363</v>
       </c>
       <c r="B206" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="D206" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20367</v>
+        <v>20364</v>
       </c>
       <c r="B207" t="s">
-        <v>47</v>
+        <v>196</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="1" t="s">
-        <v>8</v>
+      <c r="D207" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20369</v>
+        <v>20366</v>
       </c>
       <c r="B208" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
@@ -4543,10 +4637,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20371</v>
+        <v>20367</v>
       </c>
       <c r="B209" t="s">
-        <v>223</v>
+        <v>47</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
@@ -4557,24 +4651,24 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20372</v>
+        <v>20369</v>
       </c>
       <c r="B210" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="D210" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20374</v>
+        <v>20371</v>
       </c>
       <c r="B211" t="s">
-        <v>61</v>
+        <v>223</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
@@ -4585,10 +4679,10 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20377</v>
+        <v>20372</v>
       </c>
       <c r="B212" t="s">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
@@ -4599,66 +4693,66 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20379</v>
+        <v>20374</v>
       </c>
       <c r="B213" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="D213" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20380</v>
+        <v>20377</v>
       </c>
       <c r="B214" t="s">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="13" t="s">
-        <v>5</v>
+      <c r="D214" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20381</v>
+        <v>20379</v>
       </c>
       <c r="B215" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D215" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20384</v>
+        <v>20380</v>
       </c>
       <c r="B216" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="10" t="s">
-        <v>8</v>
+      <c r="D216" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20385</v>
+        <v>20381</v>
       </c>
       <c r="B217" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
@@ -4669,38 +4763,38 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20386</v>
+        <v>20384</v>
       </c>
       <c r="B218" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D218" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20388</v>
+        <v>20385</v>
       </c>
       <c r="B219" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="10" t="s">
+      <c r="D219" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20391</v>
+        <v>20386</v>
       </c>
       <c r="B220" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
@@ -4711,10 +4805,10 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20394</v>
+        <v>20388</v>
       </c>
       <c r="B221" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
@@ -4725,10 +4819,10 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20395</v>
+        <v>20391</v>
       </c>
       <c r="B222" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
@@ -4739,38 +4833,38 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20396</v>
+        <v>20394</v>
       </c>
       <c r="B223" t="s">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="1" t="s">
+      <c r="D223" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B224" s="8" t="s">
-        <v>344</v>
+        <v>20395</v>
+      </c>
+      <c r="B224" t="s">
+        <v>161</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="11" t="s">
-        <v>5</v>
+      <c r="D224" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>30101</v>
+        <v>20396</v>
       </c>
       <c r="B225" t="s">
-        <v>167</v>
+        <v>330</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
@@ -4781,136 +4875,136 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40124</v>
-      </c>
-      <c r="B226" t="s">
-        <v>24</v>
+        <v>20397</v>
+      </c>
+      <c r="B226" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="13" t="s">
+      <c r="D226" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40125</v>
+        <v>30101</v>
       </c>
       <c r="B227" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="13" t="s">
-        <v>5</v>
+      <c r="D227" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40127</v>
+        <v>40124</v>
       </c>
       <c r="B228" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="1" t="s">
-        <v>8</v>
+      <c r="D228" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40129</v>
+        <v>40125</v>
       </c>
       <c r="B229" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="1" t="s">
-        <v>8</v>
+      <c r="D229" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40137</v>
+        <v>40127</v>
       </c>
       <c r="B230" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="10" t="s">
+      <c r="D230" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40139</v>
+        <v>40129</v>
       </c>
       <c r="B231" t="s">
-        <v>327</v>
+        <v>138</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="10" t="s">
+      <c r="D231" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40140</v>
+        <v>40137</v>
       </c>
       <c r="B232" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="1" t="s">
+      <c r="D232" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40141</v>
+        <v>40139</v>
       </c>
       <c r="B233" t="s">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="13" t="s">
-        <v>5</v>
+      <c r="D233" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40143</v>
+        <v>40140</v>
       </c>
       <c r="B234" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="10" t="s">
+      <c r="D234" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40144</v>
+        <v>40141</v>
       </c>
       <c r="B235" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
@@ -4921,80 +5015,80 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40145</v>
+        <v>40143</v>
       </c>
       <c r="B236" t="s">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="13" t="s">
-        <v>5</v>
+      <c r="D236" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40147</v>
+        <v>40144</v>
       </c>
       <c r="B237" t="s">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="19" t="s">
-        <v>8</v>
+      <c r="D237" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40150</v>
+        <v>40145</v>
       </c>
       <c r="B238" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="10" t="s">
-        <v>8</v>
+      <c r="D238" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40151</v>
+        <v>40147</v>
       </c>
       <c r="B239" t="s">
-        <v>54</v>
+        <v>405</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="1" t="s">
+      <c r="D239" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50102</v>
+        <v>40150</v>
       </c>
       <c r="B240" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="13" t="s">
-        <v>5</v>
+      <c r="D240" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50222</v>
+        <v>40151</v>
       </c>
       <c r="B241" t="s">
-        <v>215</v>
+        <v>54</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
@@ -5005,206 +5099,206 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50223</v>
+        <v>50102</v>
       </c>
       <c r="B242" t="s">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="10" t="s">
-        <v>8</v>
+      <c r="D242" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50224</v>
+        <v>50222</v>
       </c>
       <c r="B243" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="3" t="s">
-        <v>5</v>
+      <c r="D243" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50444</v>
+        <v>50223</v>
       </c>
       <c r="B244" t="s">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="1" t="s">
+      <c r="D244" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50445</v>
+        <v>50224</v>
       </c>
       <c r="B245" t="s">
-        <v>354</v>
+        <v>42</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="11" t="s">
+      <c r="D245" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50607</v>
+        <v>50444</v>
       </c>
       <c r="B246" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="13" t="s">
-        <v>5</v>
+      <c r="D246" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50608</v>
+        <v>50445</v>
       </c>
       <c r="B247" t="s">
-        <v>177</v>
+        <v>354</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="1" t="s">
-        <v>8</v>
+      <c r="D247" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B248" s="8" t="s">
-        <v>347</v>
+        <v>50607</v>
+      </c>
+      <c r="B248" t="s">
+        <v>76</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="14" t="s">
-        <v>8</v>
+      <c r="D248" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50622</v>
+        <v>50608</v>
       </c>
       <c r="B249" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="16" t="s">
+      <c r="D249" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50623</v>
-      </c>
-      <c r="B250" t="s">
-        <v>110</v>
+        <v>50611</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="10" t="s">
+      <c r="D250" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50625</v>
+        <v>50622</v>
       </c>
       <c r="B251" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="10" t="s">
+      <c r="D251" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50629</v>
+        <v>50623</v>
       </c>
       <c r="B252" t="s">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>5</v>
+      <c r="D252" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50630</v>
+        <v>50625</v>
       </c>
       <c r="B253" t="s">
-        <v>360</v>
+        <v>204</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="14" t="s">
+      <c r="D253" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50803</v>
+        <v>50629</v>
       </c>
       <c r="B254" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50805</v>
+        <v>50630</v>
       </c>
       <c r="B255" t="s">
-        <v>135</v>
+        <v>360</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="10" t="s">
+      <c r="D255" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50806</v>
+        <v>50803</v>
       </c>
       <c r="B256" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
@@ -5215,304 +5309,304 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50808</v>
+        <v>50805</v>
       </c>
       <c r="B257" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="13" t="s">
-        <v>5</v>
+      <c r="D257" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50809</v>
+        <v>50806</v>
       </c>
       <c r="B258" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="13" t="s">
-        <v>5</v>
+      <c r="D258" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50810</v>
+        <v>50808</v>
       </c>
       <c r="B259" t="s">
-        <v>175</v>
+        <v>16</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="1" t="s">
-        <v>8</v>
+      <c r="D259" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50812</v>
+        <v>50809</v>
       </c>
       <c r="B260" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="1" t="s">
-        <v>8</v>
+      <c r="D260" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50813</v>
+        <v>50810</v>
       </c>
       <c r="B261" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="17" t="s">
-        <v>9</v>
+      <c r="D261" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50815</v>
+        <v>50812</v>
       </c>
       <c r="B262" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="10" t="s">
+      <c r="D262" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50816</v>
+        <v>50813</v>
       </c>
       <c r="B263" t="s">
-        <v>205</v>
+        <v>71</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="1" t="s">
-        <v>8</v>
+      <c r="D263" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50818</v>
+        <v>50815</v>
       </c>
       <c r="B264" t="s">
-        <v>227</v>
+        <v>114</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="13" t="s">
-        <v>5</v>
+      <c r="D264" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50819</v>
+        <v>50816</v>
       </c>
       <c r="B265" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="10" t="s">
+      <c r="D265" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50820</v>
+        <v>50818</v>
       </c>
       <c r="B266" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="10" t="s">
-        <v>8</v>
+      <c r="D266" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50821</v>
+        <v>50819</v>
       </c>
       <c r="B267" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="1" t="s">
+      <c r="D267" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50823</v>
+        <v>50820</v>
       </c>
       <c r="B268" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="17" t="s">
-        <v>9</v>
+      <c r="D268" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50824</v>
+        <v>50821</v>
       </c>
       <c r="B269" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="13" t="s">
-        <v>5</v>
+      <c r="D269" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50825</v>
+        <v>50823</v>
       </c>
       <c r="B270" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="10" t="s">
-        <v>8</v>
+      <c r="D270" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50826</v>
+        <v>50824</v>
       </c>
       <c r="B271" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="10" t="s">
-        <v>8</v>
+      <c r="D271" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50827</v>
+        <v>50825</v>
       </c>
       <c r="B272" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="1" t="s">
+      <c r="D272" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50829</v>
+        <v>50826</v>
       </c>
       <c r="B273" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="1" t="s">
+      <c r="D273" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50830</v>
+        <v>50827</v>
       </c>
       <c r="B274" t="s">
-        <v>366</v>
+        <v>235</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="11" t="s">
+      <c r="D274" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50831</v>
+        <v>50829</v>
       </c>
       <c r="B275" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="11" t="s">
-        <v>9</v>
+      <c r="D275" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B276" s="8" t="s">
-        <v>349</v>
+        <v>50830</v>
+      </c>
+      <c r="B276" t="s">
+        <v>366</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50833</v>
-      </c>
-      <c r="B277" s="8" t="s">
-        <v>397</v>
+        <v>50831</v>
+      </c>
+      <c r="B277" t="s">
+        <v>351</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50230</v>
+        <v>50832</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
@@ -5523,52 +5617,52 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B279" t="s">
-        <v>237</v>
+        <v>50833</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="13" t="s">
-        <v>5</v>
+      <c r="D279" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60109</v>
-      </c>
-      <c r="B280" t="s">
-        <v>328</v>
+        <v>50230</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60124</v>
-      </c>
-      <c r="B281" t="s">
-        <v>238</v>
+        <v>50231</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>421</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="13" t="s">
-        <v>5</v>
+      <c r="D281" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60125</v>
+        <v>60103</v>
       </c>
       <c r="B282" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5579,80 +5673,80 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60126</v>
+        <v>60109</v>
       </c>
       <c r="B283" t="s">
-        <v>240</v>
+        <v>328</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="10" t="s">
-        <v>8</v>
+      <c r="D283" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60128</v>
+        <v>60124</v>
       </c>
       <c r="B284" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="3" t="s">
+      <c r="D284" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60130</v>
+        <v>60125</v>
       </c>
       <c r="B285" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="1" t="s">
-        <v>8</v>
+      <c r="D285" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60133</v>
+        <v>60126</v>
       </c>
       <c r="B286" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="13" t="s">
-        <v>5</v>
+      <c r="D286" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="B287" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="1" t="s">
-        <v>8</v>
+      <c r="D287" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60137</v>
+        <v>60130</v>
       </c>
       <c r="B288" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5663,24 +5757,24 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60139</v>
+        <v>60133</v>
       </c>
       <c r="B289" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="1" t="s">
-        <v>8</v>
+      <c r="D289" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60142</v>
+        <v>60134</v>
       </c>
       <c r="B290" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
@@ -5691,10 +5785,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60148</v>
+        <v>60137</v>
       </c>
       <c r="B291" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
@@ -5705,10 +5799,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60149</v>
+        <v>60139</v>
       </c>
       <c r="B292" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
@@ -5719,38 +5813,38 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60150</v>
+        <v>60142</v>
       </c>
       <c r="B293" t="s">
-        <v>332</v>
+        <v>247</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="13" t="s">
-        <v>5</v>
+      <c r="D293" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60158</v>
+        <v>60148</v>
       </c>
       <c r="B294" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="10" t="s">
+      <c r="D294" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60159</v>
+        <v>60149</v>
       </c>
       <c r="B295" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5761,10 +5855,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60162</v>
+        <v>60150</v>
       </c>
       <c r="B296" t="s">
-        <v>252</v>
+        <v>332</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5775,24 +5869,24 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60163</v>
+        <v>60158</v>
       </c>
       <c r="B297" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="13" t="s">
-        <v>5</v>
+      <c r="D297" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60165</v>
+        <v>60159</v>
       </c>
       <c r="B298" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5803,38 +5897,38 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60169</v>
+        <v>60162</v>
       </c>
       <c r="B299" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="1" t="s">
-        <v>8</v>
+      <c r="D299" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B300" s="8" t="s">
-        <v>337</v>
+        <v>60163</v>
+      </c>
+      <c r="B300" t="s">
+        <v>253</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="11" t="s">
-        <v>8</v>
+      <c r="D300" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60172</v>
+        <v>60165</v>
       </c>
       <c r="B301" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5845,38 +5939,38 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60174</v>
+        <v>60169</v>
       </c>
       <c r="B302" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="13" t="s">
-        <v>5</v>
+      <c r="D302" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60176</v>
-      </c>
-      <c r="B303" t="s">
-        <v>258</v>
+        <v>60170</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="13" t="s">
-        <v>5</v>
+      <c r="D303" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60178</v>
+        <v>60172</v>
       </c>
       <c r="B304" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -5887,38 +5981,38 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60180</v>
+        <v>60174</v>
       </c>
       <c r="B305" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="10" t="s">
-        <v>8</v>
+      <c r="D305" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60184</v>
+        <v>60176</v>
       </c>
       <c r="B306" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="1" t="s">
-        <v>8</v>
+      <c r="D306" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60190</v>
+        <v>60178</v>
       </c>
       <c r="B307" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -5929,10 +6023,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60191</v>
+        <v>60180</v>
       </c>
       <c r="B308" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -5943,38 +6037,38 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60192</v>
+        <v>60184</v>
       </c>
       <c r="B309" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="10" t="s">
+      <c r="D309" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B310" s="18" t="s">
-        <v>410</v>
+        <v>60190</v>
+      </c>
+      <c r="B310" t="s">
+        <v>262</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="10" t="s">
+      <c r="D310" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60195</v>
+        <v>60191</v>
       </c>
       <c r="B311" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
@@ -5985,10 +6079,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60196</v>
+        <v>60192</v>
       </c>
       <c r="B312" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
@@ -5999,10 +6093,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60198</v>
-      </c>
-      <c r="B313" t="s">
-        <v>267</v>
+        <v>60194</v>
+      </c>
+      <c r="B313" s="18" t="s">
+        <v>410</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -6013,94 +6107,94 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60201</v>
+        <v>60195</v>
       </c>
       <c r="B314" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" t="s">
-        <v>9</v>
+      <c r="D314" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60202</v>
+        <v>60196</v>
       </c>
       <c r="B315" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="13" t="s">
-        <v>5</v>
+      <c r="D315" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60204</v>
+        <v>60198</v>
       </c>
       <c r="B316" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="1" t="s">
+      <c r="D316" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60205</v>
+        <v>60201</v>
       </c>
       <c r="B317" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="1" t="s">
-        <v>8</v>
+      <c r="D317" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60206</v>
+        <v>60202</v>
       </c>
       <c r="B318" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="1" t="s">
-        <v>8</v>
+      <c r="D318" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60209</v>
+        <v>60204</v>
       </c>
       <c r="B319" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="10" t="s">
+      <c r="D319" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60211</v>
+        <v>60205</v>
       </c>
       <c r="B320" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
@@ -6111,164 +6205,164 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60215</v>
+        <v>60206</v>
       </c>
       <c r="B321" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="10" t="s">
+      <c r="D321" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60216</v>
+        <v>60209</v>
       </c>
       <c r="B322" t="s">
-        <v>381</v>
+        <v>273</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D322" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60217</v>
+        <v>60211</v>
       </c>
       <c r="B323" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="10" t="s">
+      <c r="D323" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60219</v>
+        <v>60215</v>
       </c>
       <c r="B324" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="1" t="s">
+      <c r="D324" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60222</v>
+        <v>60216</v>
       </c>
       <c r="B325" t="s">
-        <v>278</v>
+        <v>381</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D325" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60225</v>
+        <v>60217</v>
       </c>
       <c r="B326" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="17" t="s">
-        <v>9</v>
+      <c r="D326" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60230</v>
+        <v>60219</v>
       </c>
       <c r="B327" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="10" t="s">
+      <c r="D327" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B328" s="8" t="s">
-        <v>338</v>
+        <v>60222</v>
+      </c>
+      <c r="B328" t="s">
+        <v>278</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="7" t="s">
-        <v>9</v>
+      <c r="D328" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60242</v>
-      </c>
-      <c r="B329" s="8" t="s">
-        <v>341</v>
+        <v>60225</v>
+      </c>
+      <c r="B329" t="s">
+        <v>279</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="7" t="s">
-        <v>5</v>
+      <c r="D329" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60243</v>
-      </c>
-      <c r="B330" s="8" t="s">
-        <v>395</v>
+        <v>60230</v>
+      </c>
+      <c r="B330" t="s">
+        <v>280</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="7" t="s">
-        <v>9</v>
+      <c r="D330" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60245</v>
+        <v>60241</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D331" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60246</v>
+        <v>60242</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>407</v>
+        <v>341</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6279,80 +6373,80 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B333" s="18" t="s">
-        <v>408</v>
+        <v>60243</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>395</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D333" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60250</v>
+        <v>60245</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="11" t="s">
-        <v>8</v>
+      <c r="D334" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B335" t="s">
-        <v>281</v>
+        <v>60246</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="1" t="s">
-        <v>8</v>
+      <c r="D335" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60254</v>
-      </c>
-      <c r="B336" t="s">
-        <v>282</v>
+        <v>60249</v>
+      </c>
+      <c r="B336" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="1" t="s">
-        <v>8</v>
+      <c r="D336" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60257</v>
-      </c>
-      <c r="B337" t="s">
-        <v>283</v>
+        <v>60250</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="1" t="s">
+      <c r="D337" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60258</v>
+        <v>60253</v>
       </c>
       <c r="B338" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
@@ -6363,94 +6457,94 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B339" s="8" t="s">
-        <v>343</v>
+        <v>60254</v>
+      </c>
+      <c r="B339" t="s">
+        <v>282</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="11" t="s">
+      <c r="D339" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60269</v>
+        <v>60257</v>
       </c>
       <c r="B340" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="10" t="s">
+      <c r="D340" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60270</v>
+        <v>60258</v>
       </c>
       <c r="B341" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60272</v>
-      </c>
-      <c r="B342" t="s">
-        <v>287</v>
+        <v>60266</v>
+      </c>
+      <c r="B342" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="1" t="s">
+      <c r="D342" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60274</v>
+        <v>60269</v>
       </c>
       <c r="B343" t="s">
-        <v>380</v>
+        <v>285</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="1" t="s">
+      <c r="D343" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60275</v>
+        <v>60270</v>
       </c>
       <c r="B344" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60276</v>
+        <v>60272</v>
       </c>
       <c r="B345" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
@@ -6461,24 +6555,24 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60278</v>
+        <v>60274</v>
       </c>
       <c r="B346" t="s">
-        <v>290</v>
+        <v>380</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="13" t="s">
+      <c r="D346" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60279</v>
+        <v>60275</v>
       </c>
       <c r="B347" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6489,150 +6583,150 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60280</v>
+        <v>60276</v>
       </c>
       <c r="B348" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B349" s="8" t="s">
-        <v>336</v>
+        <v>60278</v>
+      </c>
+      <c r="B349" t="s">
+        <v>290</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="11" t="s">
-        <v>9</v>
+      <c r="D349" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60282</v>
-      </c>
-      <c r="B350" s="8" t="s">
-        <v>340</v>
+        <v>60279</v>
+      </c>
+      <c r="B350" t="s">
+        <v>291</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="11" t="s">
+      <c r="D350" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60283</v>
+        <v>60280</v>
       </c>
       <c r="B351" t="s">
-        <v>378</v>
+        <v>292</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60284</v>
+        <v>60281</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D352" s="9" t="s">
-        <v>5</v>
+      <c r="D352" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60285</v>
+        <v>60282</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="9" t="s">
+      <c r="D353" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60286</v>
-      </c>
-      <c r="B354" s="8" t="s">
-        <v>334</v>
+        <v>60283</v>
+      </c>
+      <c r="B354" t="s">
+        <v>378</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="9" t="s">
-        <v>5</v>
+      <c r="D354" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B355" t="s">
-        <v>377</v>
+        <v>60284</v>
+      </c>
+      <c r="B355" s="8" t="s">
+        <v>335</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="12" t="s">
+      <c r="D355" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60289</v>
-      </c>
-      <c r="B356" t="s">
-        <v>374</v>
+        <v>60285</v>
+      </c>
+      <c r="B356" s="8" t="s">
+        <v>350</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="12" t="s">
-        <v>9</v>
+      <c r="D356" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60290</v>
-      </c>
-      <c r="B357" t="s">
-        <v>375</v>
+        <v>60286</v>
+      </c>
+      <c r="B357" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="12" t="s">
+      <c r="D357" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60291</v>
+        <v>60287</v>
       </c>
       <c r="B358" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6643,38 +6737,38 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B359" s="18" t="s">
-        <v>400</v>
+        <v>60289</v>
+      </c>
+      <c r="B359" t="s">
+        <v>374</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60296</v>
+        <v>60290</v>
       </c>
       <c r="B360" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60297</v>
+        <v>60291</v>
       </c>
       <c r="B361" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6685,24 +6779,24 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60299</v>
-      </c>
-      <c r="B362" t="s">
-        <v>388</v>
+        <v>60292</v>
+      </c>
+      <c r="B362" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D362" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60302</v>
+        <v>60293</v>
       </c>
       <c r="B363" s="18" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6713,80 +6807,80 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60303</v>
-      </c>
-      <c r="B364" s="18" t="s">
-        <v>412</v>
+        <v>60296</v>
+      </c>
+      <c r="B364" t="s">
+        <v>391</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D364" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>61001</v>
+        <v>60297</v>
       </c>
       <c r="B365" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>61004</v>
+        <v>60299</v>
       </c>
       <c r="B366" t="s">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="15" t="s">
+      <c r="D366" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>61009</v>
-      </c>
-      <c r="B367" t="s">
-        <v>294</v>
+        <v>60302</v>
+      </c>
+      <c r="B367" s="18" t="s">
+        <v>411</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D367" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>61012</v>
-      </c>
-      <c r="B368" t="s">
-        <v>295</v>
+        <v>60303</v>
+      </c>
+      <c r="B368" s="18" t="s">
+        <v>412</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D368" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>61018</v>
+        <v>61001</v>
       </c>
       <c r="B369" t="s">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6797,24 +6891,24 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>61102</v>
+        <v>61004</v>
       </c>
       <c r="B370" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="12" t="s">
-        <v>8</v>
+      <c r="D370" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>61205</v>
+        <v>61007</v>
       </c>
       <c r="B371" t="s">
-        <v>298</v>
+        <v>415</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6825,10 +6919,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70100</v>
+        <v>61009</v>
       </c>
       <c r="B372" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6839,38 +6933,38 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70101</v>
+        <v>61012</v>
       </c>
       <c r="B373" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="15" t="s">
-        <v>5</v>
+      <c r="D373" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70102</v>
+        <v>61018</v>
       </c>
       <c r="B374" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="15" t="s">
-        <v>5</v>
+      <c r="D374" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70103</v>
+        <v>61102</v>
       </c>
       <c r="B375" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6881,10 +6975,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>70106</v>
+        <v>61205</v>
       </c>
       <c r="B376" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6895,10 +6989,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>70109</v>
+        <v>70100</v>
       </c>
       <c r="B377" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6909,10 +7003,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>70113</v>
+        <v>70101</v>
       </c>
       <c r="B378" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6923,66 +7017,66 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>70114</v>
+        <v>70102</v>
       </c>
       <c r="B379" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="9" t="s">
-        <v>9</v>
+      <c r="D379" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>70115</v>
+        <v>70103</v>
       </c>
       <c r="B380" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="9" t="s">
-        <v>9</v>
+      <c r="D380" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>70638</v>
+        <v>70106</v>
       </c>
       <c r="B381" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="12" t="s">
-        <v>8</v>
+      <c r="D381" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>70639</v>
+        <v>70107</v>
       </c>
       <c r="B382" t="s">
-        <v>307</v>
+        <v>419</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="12" t="s">
+      <c r="D382" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>70640</v>
+        <v>70109</v>
       </c>
       <c r="B383" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6993,66 +7087,66 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>70642</v>
+        <v>70113</v>
       </c>
       <c r="B384" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D384" s="12" t="s">
-        <v>8</v>
+      <c r="D384" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90504</v>
+        <v>70114</v>
       </c>
       <c r="B385" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="12" t="s">
-        <v>8</v>
+      <c r="D385" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90509</v>
+        <v>70115</v>
       </c>
       <c r="B386" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="12" t="s">
-        <v>8</v>
+      <c r="D386" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90602</v>
+        <v>70116</v>
       </c>
       <c r="B387" t="s">
-        <v>312</v>
+        <v>420</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="15" t="s">
-        <v>5</v>
+      <c r="D387" s="9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90621</v>
+        <v>70638</v>
       </c>
       <c r="B388" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7063,38 +7157,38 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90622</v>
+        <v>70639</v>
       </c>
       <c r="B389" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="9" t="s">
-        <v>5</v>
+      <c r="D389" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B390" s="8" t="s">
-        <v>342</v>
+        <v>70640</v>
+      </c>
+      <c r="B390" t="s">
+        <v>308</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D390" s="9" t="s">
-        <v>5</v>
+      <c r="D390" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90658</v>
+        <v>70642</v>
       </c>
       <c r="B391" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7105,10 +7199,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90660</v>
+        <v>90504</v>
       </c>
       <c r="B392" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7119,10 +7213,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90668</v>
+        <v>90509</v>
       </c>
       <c r="B393" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7133,24 +7227,24 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90671</v>
+        <v>90602</v>
       </c>
       <c r="B394" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D394" s="12" t="s">
-        <v>8</v>
+      <c r="D394" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90679</v>
+        <v>90621</v>
       </c>
       <c r="B395" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7161,38 +7255,38 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90683</v>
+        <v>90622</v>
       </c>
       <c r="B396" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D396" s="12" t="s">
-        <v>8</v>
+      <c r="D396" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90705</v>
-      </c>
-      <c r="B397" t="s">
-        <v>320</v>
+        <v>90631</v>
+      </c>
+      <c r="B397" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D397" s="12" t="s">
-        <v>8</v>
+      <c r="D397" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90706</v>
+        <v>90658</v>
       </c>
       <c r="B398" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7203,10 +7297,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90708</v>
+        <v>90660</v>
       </c>
       <c r="B399" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7217,10 +7311,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90709</v>
+        <v>90668</v>
       </c>
       <c r="B400" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7231,24 +7325,24 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90713</v>
+        <v>90671</v>
       </c>
       <c r="B401" t="s">
-        <v>402</v>
+        <v>317</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D401" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>1218</v>
+        <v>90679</v>
       </c>
       <c r="B402" t="s">
-        <v>382</v>
+        <v>318</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7259,10 +7353,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B403" s="8" t="s">
-        <v>383</v>
+        <v>90683</v>
+      </c>
+      <c r="B403" t="s">
+        <v>319</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7273,10 +7367,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B404" s="8" t="s">
-        <v>384</v>
+        <v>90705</v>
+      </c>
+      <c r="B404" t="s">
+        <v>320</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7287,10 +7381,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>1817</v>
-      </c>
-      <c r="B405" s="8" t="s">
-        <v>389</v>
+        <v>90706</v>
+      </c>
+      <c r="B405" t="s">
+        <v>321</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7301,10 +7395,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>5737</v>
-      </c>
-      <c r="B406" s="8" t="s">
-        <v>390</v>
+        <v>90708</v>
+      </c>
+      <c r="B406" t="s">
+        <v>322</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7315,34 +7409,468 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>60295</v>
-      </c>
-      <c r="B407" s="8" t="s">
-        <v>385</v>
+        <v>90709</v>
+      </c>
+      <c r="B407" t="s">
+        <v>323</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D407" s="9" t="s">
-        <v>9</v>
+      <c r="D407" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
+        <v>90713</v>
+      </c>
+      <c r="B408" t="s">
+        <v>402</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D408" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A409" s="6">
+        <v>1218</v>
+      </c>
+      <c r="B409" t="s">
+        <v>382</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D409" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A410" s="6">
+        <v>1959</v>
+      </c>
+      <c r="B410" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D410" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A411" s="6">
+        <v>5625</v>
+      </c>
+      <c r="B411" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D411" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A412" s="6">
+        <v>1817</v>
+      </c>
+      <c r="B412" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D412" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A413" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B413" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D413" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B414" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D414" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A415" s="6">
         <v>1045</v>
       </c>
-      <c r="B408" s="8" t="s">
+      <c r="B415" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C408" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D408" s="9" t="s">
-        <v>5</v>
+      <c r="C415" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D415" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A416">
+        <v>1043</v>
+      </c>
+      <c r="B416" t="s">
+        <v>422</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D416" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A417">
+        <v>20340</v>
+      </c>
+      <c r="B417" t="s">
+        <v>423</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D417" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>40146</v>
+      </c>
+      <c r="B418" t="s">
+        <v>424</v>
+      </c>
+      <c r="C418" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D418" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>60260</v>
+      </c>
+      <c r="B419" t="s">
+        <v>425</v>
+      </c>
+      <c r="C419" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D419" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>1017</v>
+      </c>
+      <c r="B420" t="s">
+        <v>426</v>
+      </c>
+      <c r="C420" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D420" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>60300</v>
+      </c>
+      <c r="B421" t="s">
+        <v>427</v>
+      </c>
+      <c r="C421" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D421" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>20191</v>
+      </c>
+      <c r="B422" t="s">
+        <v>428</v>
+      </c>
+      <c r="C422" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D422" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>20399</v>
+      </c>
+      <c r="B423" t="s">
+        <v>429</v>
+      </c>
+      <c r="C423" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D423" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>60240</v>
+      </c>
+      <c r="B424" t="s">
+        <v>430</v>
+      </c>
+      <c r="C424" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D424" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>60244</v>
+      </c>
+      <c r="B425" t="s">
+        <v>431</v>
+      </c>
+      <c r="C425" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D425" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>60248</v>
+      </c>
+      <c r="B426" t="s">
+        <v>432</v>
+      </c>
+      <c r="C426" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D426" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>60288</v>
+      </c>
+      <c r="B427" t="s">
+        <v>433</v>
+      </c>
+      <c r="C427" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D427" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>90714</v>
+      </c>
+      <c r="B428" t="s">
+        <v>434</v>
+      </c>
+      <c r="C428" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D428" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>1014</v>
+      </c>
+      <c r="B429" t="s">
+        <v>435</v>
+      </c>
+      <c r="C429" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D429" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>1016</v>
+      </c>
+      <c r="B430" t="s">
+        <v>436</v>
+      </c>
+      <c r="C430" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D430" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>60301</v>
+      </c>
+      <c r="B431" t="s">
+        <v>437</v>
+      </c>
+      <c r="C431" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D431" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>1041</v>
+      </c>
+      <c r="B432" t="s">
+        <v>438</v>
+      </c>
+      <c r="C432" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D432" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>971</v>
+      </c>
+      <c r="B433" t="s">
+        <v>439</v>
+      </c>
+      <c r="C433" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D433" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>50610</v>
+      </c>
+      <c r="B434" t="s">
+        <v>440</v>
+      </c>
+      <c r="C434" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D434" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>943</v>
+      </c>
+      <c r="B435" t="s">
+        <v>441</v>
+      </c>
+      <c r="C435" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D435" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>20306</v>
+      </c>
+      <c r="B436" t="s">
+        <v>442</v>
+      </c>
+      <c r="C436" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D436" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>90630</v>
+      </c>
+      <c r="B437" t="s">
+        <v>443</v>
+      </c>
+      <c r="C437" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D437" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>1047</v>
+      </c>
+      <c r="B438" t="s">
+        <v>444</v>
+      </c>
+      <c r="C438" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D438" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>20398</v>
+      </c>
+      <c r="B439" t="s">
+        <v>445</v>
+      </c>
+      <c r="C439" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D439" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D351"/>
+  <autoFilter ref="A1:D415"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$415</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$416</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="447">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1360,6 +1360,9 @@
   </si>
   <si>
     <t>FERRETERIA JULIAN</t>
+  </si>
+  <si>
+    <t>FERRETERIA LUCKA</t>
   </si>
 </sst>
 </file>
@@ -1715,7 +1718,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D439"/>
+  <dimension ref="A1:D440"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6877,38 +6880,38 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B369" t="s">
-        <v>403</v>
+        <v>60305</v>
+      </c>
+      <c r="B369" s="18" t="s">
+        <v>446</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B370" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="15" t="s">
-        <v>5</v>
+      <c r="D370" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B371" t="s">
-        <v>415</v>
+        <v>293</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6919,24 +6922,24 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B372" t="s">
-        <v>294</v>
+        <v>415</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="12" t="s">
-        <v>8</v>
+      <c r="D372" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B373" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6947,10 +6950,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B374" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6961,10 +6964,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B375" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6975,52 +6978,52 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B376" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="15" t="s">
-        <v>5</v>
+      <c r="D376" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B377" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="12" t="s">
-        <v>8</v>
+      <c r="D377" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B378" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="15" t="s">
-        <v>5</v>
+      <c r="D378" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B379" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -7031,94 +7034,94 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B380" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="12" t="s">
-        <v>8</v>
+      <c r="D380" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B381" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="15" t="s">
-        <v>5</v>
+      <c r="D381" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B382" t="s">
-        <v>419</v>
+        <v>303</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D382" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B383" t="s">
-        <v>304</v>
+        <v>419</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="12" t="s">
+      <c r="D383" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B384" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D384" s="15" t="s">
-        <v>5</v>
+      <c r="D384" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B385" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="9" t="s">
-        <v>9</v>
+      <c r="D385" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B386" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7129,38 +7132,38 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B387" t="s">
-        <v>420</v>
+        <v>331</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D387" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70638</v>
+        <v>70116</v>
       </c>
       <c r="B388" t="s">
-        <v>306</v>
+        <v>420</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="12" t="s">
+      <c r="D388" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B389" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7171,10 +7174,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B390" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7185,10 +7188,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B391" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7199,10 +7202,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B392" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7213,10 +7216,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B393" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7227,52 +7230,52 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B394" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D394" s="15" t="s">
-        <v>5</v>
+      <c r="D394" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B395" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D395" s="12" t="s">
-        <v>8</v>
+      <c r="D395" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B396" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D396" s="9" t="s">
-        <v>5</v>
+      <c r="D396" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B397" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B397" t="s">
+        <v>333</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7283,24 +7286,24 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B398" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B398" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D398" s="12" t="s">
-        <v>8</v>
+      <c r="D398" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B399" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7311,10 +7314,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B400" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7325,10 +7328,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B401" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7339,10 +7342,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B402" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7353,10 +7356,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B403" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7367,10 +7370,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B404" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7381,10 +7384,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B405" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7395,10 +7398,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B406" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7409,10 +7412,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B407" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7423,38 +7426,38 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B408" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D408" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B409" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D409" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B410" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B410" t="s">
+        <v>382</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7465,10 +7468,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B411" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7479,10 +7482,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B412" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7493,10 +7496,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7507,68 +7510,68 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D414" s="9" t="s">
-        <v>9</v>
+      <c r="D414" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B415" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D415" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A416" s="6">
         <v>1045</v>
       </c>
-      <c r="B415" s="8" t="s">
+      <c r="B416" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C415" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D415" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A416">
-        <v>1043</v>
-      </c>
-      <c r="B416" t="s">
-        <v>422</v>
-      </c>
-      <c r="C416" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D416" t="s">
-        <v>8</v>
+      <c r="C416" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D416" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417">
+        <v>1043</v>
+      </c>
+      <c r="B417" t="s">
+        <v>422</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D417" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A418">
         <v>20340</v>
       </c>
-      <c r="B417" t="s">
+      <c r="B418" t="s">
         <v>423</v>
       </c>
-      <c r="C417" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D417" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="418" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A418">
-        <v>40146</v>
-      </c>
-      <c r="B418" t="s">
-        <v>424</v>
-      </c>
-      <c r="C418" s="14" t="s">
+      <c r="C418" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D418" t="s">
@@ -7577,24 +7580,24 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B419" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C419" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D419" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B420" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C420" s="14" t="s">
         <v>4</v>
@@ -7605,10 +7608,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B421" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C421" s="14" t="s">
         <v>4</v>
@@ -7619,66 +7622,66 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B422" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C422" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D422" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B423" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C423" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D423" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B424" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C424" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D424" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B425" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C425" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D425" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B426" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C426" s="14" t="s">
         <v>4</v>
@@ -7689,24 +7692,24 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B427" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C427" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D427" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B428" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
@@ -7717,10 +7720,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B429" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
@@ -7731,38 +7734,38 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B430" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D430" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B431" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D431" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B432" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
@@ -7773,10 +7776,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B433" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
@@ -7787,38 +7790,38 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B434" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D434" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B435" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B436" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
@@ -7829,24 +7832,24 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B437" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B438" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
@@ -7857,20 +7860,34 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
+        <v>1047</v>
+      </c>
+      <c r="B439" t="s">
+        <v>444</v>
+      </c>
+      <c r="C439" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D439" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A440">
         <v>20398</v>
       </c>
-      <c r="B439" t="s">
+      <c r="B440" t="s">
         <v>445</v>
       </c>
-      <c r="C439" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D439" t="s">
+      <c r="C440" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D440" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D415"/>
+  <autoFilter ref="A1:D416"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$416</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$417</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="448">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1363,6 +1363,9 @@
   </si>
   <si>
     <t>FERRETERIA LUCKA</t>
+  </si>
+  <si>
+    <t>FERRETERIA OROÑO</t>
   </si>
 </sst>
 </file>
@@ -1718,7 +1721,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D440"/>
+  <dimension ref="A1:D441"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3002,52 +3005,52 @@
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>1416</v>
-      </c>
-      <c r="B92" t="s">
-        <v>217</v>
+        <v>1051</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>447</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>8</v>
+      <c r="D92" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B93" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" t="s">
-        <v>9</v>
+      <c r="D93" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B94" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>8</v>
+      <c r="D94" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B95" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
@@ -3058,10 +3061,10 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
@@ -3072,108 +3075,108 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="13" t="s">
-        <v>5</v>
+      <c r="D97" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>8</v>
+      <c r="D98" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B99" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="13" t="s">
-        <v>5</v>
+      <c r="D99" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B100" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>8</v>
+      <c r="D100" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B101" t="s">
+        <v>19</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D101" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B102" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="13" t="s">
-        <v>5</v>
+      <c r="D102" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="17" t="s">
-        <v>9</v>
+      <c r="D103" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
@@ -3184,24 +3187,24 @@
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B105" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="10" t="s">
-        <v>8</v>
+      <c r="D105" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B106" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
@@ -3212,66 +3215,66 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B107" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B108" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>8</v>
+      <c r="D108" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B110" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B111" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3282,80 +3285,80 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B112" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="D112" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B113" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B114" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="13" t="s">
-        <v>5</v>
+      <c r="D114" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B115" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D115" s="10" t="s">
-        <v>8</v>
+      <c r="D115" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B116" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B117" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
@@ -3366,10 +3369,10 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B118" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
@@ -3380,10 +3383,10 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B119" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
@@ -3394,10 +3397,10 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B120" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
@@ -3408,10 +3411,10 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B121" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3422,38 +3425,38 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B122" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B123" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B124" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3464,52 +3467,52 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B125" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B126" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="3" t="s">
-        <v>5</v>
+      <c r="D126" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B127" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="13" t="s">
+      <c r="D127" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B128" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
@@ -3520,24 +3523,24 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B129" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>8</v>
+      <c r="D129" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B130" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
@@ -3548,10 +3551,10 @@
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B131" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
@@ -3562,52 +3565,52 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B132" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="D132" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B133" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="17" t="s">
-        <v>9</v>
+      <c r="D133" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B134" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="10" t="s">
-        <v>8</v>
+      <c r="D134" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B135" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
@@ -3618,52 +3621,52 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B136" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" t="s">
-        <v>9</v>
+      <c r="D136" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B137" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="10" t="s">
-        <v>8</v>
+      <c r="D137" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B138" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B139" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
@@ -3674,38 +3677,38 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B140" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="10" t="s">
+      <c r="D140" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B141" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B142" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
@@ -3716,80 +3719,80 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B143" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" t="s">
-        <v>9</v>
+      <c r="D143" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B144" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="1" t="s">
-        <v>8</v>
+      <c r="D144" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B145" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="14" t="s">
-        <v>5</v>
+      <c r="D145" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B146" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="1" t="s">
-        <v>8</v>
+      <c r="D146" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B147" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="13" t="s">
-        <v>5</v>
+      <c r="D147" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
@@ -3800,150 +3803,150 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B149" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="10" t="s">
-        <v>8</v>
+      <c r="D149" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B150" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>9</v>
+      <c r="D150" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B151" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="10" t="s">
-        <v>8</v>
+      <c r="D151" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B152" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="D152" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B153" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="10" t="s">
+      <c r="D153" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B154" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="13" t="s">
-        <v>5</v>
+      <c r="D154" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B155" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="10" t="s">
-        <v>8</v>
+      <c r="D155" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B156" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="13" t="s">
-        <v>5</v>
+      <c r="D156" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B157" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="D157" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B158" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="13" t="s">
+      <c r="D158" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B159" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
@@ -3954,24 +3957,24 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B160" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="10" t="s">
-        <v>8</v>
+      <c r="D160" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B161" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
@@ -3982,108 +3985,108 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B162" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="13" t="s">
-        <v>5</v>
+      <c r="D162" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B163" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="10" t="s">
-        <v>8</v>
+      <c r="D163" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B164" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="D164" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B165" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="17" t="s">
-        <v>9</v>
+      <c r="D165" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B166" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>8</v>
+      <c r="D166" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B167" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>5</v>
+      <c r="D167" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B168" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="10" t="s">
-        <v>8</v>
+      <c r="D168" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B169" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
@@ -4094,206 +4097,206 @@
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B170" t="s">
-        <v>401</v>
+        <v>92</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B171" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>8</v>
+      <c r="D171" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B172" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="13" t="s">
-        <v>5</v>
+      <c r="D172" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B173" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>8</v>
+      <c r="D173" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B174" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="13" t="s">
-        <v>5</v>
+      <c r="D174" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B175" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="1" t="s">
-        <v>8</v>
+      <c r="D175" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B176" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="3" t="s">
-        <v>5</v>
+      <c r="D176" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B177" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="1" t="s">
-        <v>9</v>
+      <c r="D177" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B178" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="17" t="s">
+      <c r="D178" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B179" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>8</v>
+      <c r="D179" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B180" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="3" t="s">
-        <v>5</v>
+      <c r="D180" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B181" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="1" t="s">
-        <v>8</v>
+      <c r="D181" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B182" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="10" t="s">
+      <c r="D182" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B183" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="13" t="s">
-        <v>5</v>
+      <c r="D183" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B184" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
@@ -4304,52 +4307,52 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B185" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="10" t="s">
-        <v>8</v>
+      <c r="D185" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B186" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="13" t="s">
-        <v>5</v>
+      <c r="D186" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B187" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="1" t="s">
-        <v>8</v>
+      <c r="D187" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B188" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
@@ -4360,10 +4363,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B189" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
@@ -4374,10 +4377,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B190" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4388,24 +4391,24 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B191" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="13" t="s">
-        <v>5</v>
+      <c r="D191" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B192" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
@@ -4416,52 +4419,52 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B193" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>8</v>
+      <c r="D193" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B194" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="10" t="s">
+      <c r="D194" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B195" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="D195" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B196" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4472,10 +4475,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B197" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4486,38 +4489,38 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B198" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="13" t="s">
-        <v>5</v>
+      <c r="D198" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B199" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="1" t="s">
-        <v>8</v>
+      <c r="D199" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B200" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4528,10 +4531,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B201" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4542,66 +4545,66 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B202" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="13" t="s">
-        <v>5</v>
+      <c r="D202" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B203" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="1" t="s">
-        <v>8</v>
+      <c r="D203" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B204" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="13" t="s">
-        <v>5</v>
+      <c r="D204" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B205" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="10" t="s">
-        <v>8</v>
+      <c r="D205" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B206" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
@@ -4612,38 +4615,38 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B207" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="13" t="s">
-        <v>5</v>
+      <c r="D207" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B208" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="1" t="s">
-        <v>8</v>
+      <c r="D208" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B209" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
@@ -4654,10 +4657,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B210" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
@@ -4668,10 +4671,10 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B211" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
@@ -4682,52 +4685,52 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B212" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="10" t="s">
+      <c r="D212" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B213" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="D213" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B214" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="10" t="s">
+      <c r="D214" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B215" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4738,66 +4741,66 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B216" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="13" t="s">
-        <v>5</v>
+      <c r="D216" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B217" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="1" t="s">
-        <v>8</v>
+      <c r="D217" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B218" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="10" t="s">
+      <c r="D218" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B219" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="D219" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B220" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
@@ -4808,66 +4811,66 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B221" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="10" t="s">
+      <c r="D221" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B222" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="D222" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B223" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="10" t="s">
+      <c r="D223" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B224" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="1" t="s">
+      <c r="D224" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B225" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
@@ -4878,52 +4881,52 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B226" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B226" t="s">
+        <v>330</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="11" t="s">
-        <v>5</v>
+      <c r="D226" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B227" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B227" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="1" t="s">
-        <v>8</v>
+      <c r="D227" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B228" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="13" t="s">
-        <v>5</v>
+      <c r="D228" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B229" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
@@ -4934,24 +4937,24 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B230" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="1" t="s">
-        <v>8</v>
+      <c r="D230" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B231" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
@@ -4962,24 +4965,24 @@
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B232" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="10" t="s">
+      <c r="D232" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B233" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
@@ -4990,66 +4993,66 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B234" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="D234" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B235" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="13" t="s">
-        <v>5</v>
+      <c r="D235" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B236" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="10" t="s">
-        <v>8</v>
+      <c r="D236" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B237" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="13" t="s">
-        <v>5</v>
+      <c r="D237" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B238" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
@@ -5060,206 +5063,206 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B239" t="s">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="19" t="s">
-        <v>8</v>
+      <c r="D239" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B240" t="s">
-        <v>221</v>
+        <v>405</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="10" t="s">
+      <c r="D240" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B241" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="D241" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B242" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="13" t="s">
-        <v>5</v>
+      <c r="D242" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B243" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="1" t="s">
-        <v>8</v>
+      <c r="D243" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B244" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="10" t="s">
+      <c r="D244" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B245" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="3" t="s">
-        <v>5</v>
+      <c r="D245" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B246" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="1" t="s">
-        <v>8</v>
+      <c r="D246" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B247" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="11" t="s">
-        <v>5</v>
+      <c r="D247" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B248" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="13" t="s">
+      <c r="D248" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B249" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>8</v>
+      <c r="D249" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B250" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B250" t="s">
+        <v>177</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="14" t="s">
+      <c r="D250" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B251" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="16" t="s">
+      <c r="D251" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B252" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="10" t="s">
+      <c r="D252" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B253" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
@@ -5270,94 +5273,94 @@
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B254" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="1" t="s">
-        <v>5</v>
+      <c r="D254" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B255" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="14" t="s">
-        <v>8</v>
+      <c r="D255" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B256" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="1" t="s">
+      <c r="D256" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B257" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="10" t="s">
+      <c r="D257" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B258" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="1" t="s">
+      <c r="D258" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B259" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="13" t="s">
-        <v>5</v>
+      <c r="D259" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B260" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
@@ -5368,24 +5371,24 @@
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B261" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="1" t="s">
-        <v>8</v>
+      <c r="D261" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B262" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
@@ -5396,80 +5399,80 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B263" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="17" t="s">
-        <v>9</v>
+      <c r="D263" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B264" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="10" t="s">
-        <v>8</v>
+      <c r="D264" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B265" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="1" t="s">
+      <c r="D265" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B266" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="13" t="s">
-        <v>5</v>
+      <c r="D266" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B267" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="10" t="s">
-        <v>8</v>
+      <c r="D267" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B268" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5480,66 +5483,66 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B269" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="1" t="s">
+      <c r="D269" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B270" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="17" t="s">
-        <v>9</v>
+      <c r="D270" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B271" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="13" t="s">
-        <v>5</v>
+      <c r="D271" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B272" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="10" t="s">
-        <v>8</v>
+      <c r="D272" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B273" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
@@ -5550,24 +5553,24 @@
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B274" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="1" t="s">
+      <c r="D274" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B275" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
@@ -5578,136 +5581,136 @@
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B276" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="11" t="s">
+      <c r="D276" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B277" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B278" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B278" t="s">
+        <v>351</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D278" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D279" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B280" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50231</v>
+        <v>50230</v>
       </c>
       <c r="B281" s="8" t="s">
-        <v>421</v>
+        <v>379</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D281" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B282" t="s">
-        <v>237</v>
+        <v>50231</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>421</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="13" t="s">
-        <v>5</v>
+      <c r="D282" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B283" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="11" t="s">
-        <v>9</v>
+      <c r="D283" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B284" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="13" t="s">
-        <v>5</v>
+      <c r="D284" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B285" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
@@ -5718,80 +5721,80 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B286" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="10" t="s">
-        <v>8</v>
+      <c r="D286" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B287" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="3" t="s">
-        <v>5</v>
+      <c r="D287" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B288" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="1" t="s">
-        <v>8</v>
+      <c r="D288" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B289" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="13" t="s">
-        <v>5</v>
+      <c r="D289" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B290" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="1" t="s">
-        <v>8</v>
+      <c r="D290" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B291" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
@@ -5802,10 +5805,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B292" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
@@ -5816,10 +5819,10 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B293" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
@@ -5830,10 +5833,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B294" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
@@ -5844,10 +5847,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B295" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5858,66 +5861,66 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B296" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="13" t="s">
-        <v>5</v>
+      <c r="D296" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B297" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="10" t="s">
-        <v>8</v>
+      <c r="D297" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B298" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="1" t="s">
+      <c r="D298" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B299" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="13" t="s">
-        <v>5</v>
+      <c r="D299" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B300" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5928,24 +5931,24 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B301" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="1" t="s">
-        <v>8</v>
+      <c r="D301" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B302" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -5956,52 +5959,52 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B303" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B303" t="s">
+        <v>255</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="11" t="s">
+      <c r="D303" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B304" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="1" t="s">
+      <c r="D304" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B305" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="13" t="s">
-        <v>5</v>
+      <c r="D305" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B306" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -6012,52 +6015,52 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B307" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="1" t="s">
-        <v>8</v>
+      <c r="D307" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B308" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="10" t="s">
+      <c r="D308" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B309" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="1" t="s">
+      <c r="D309" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B310" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -6068,24 +6071,24 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B311" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="10" t="s">
+      <c r="D311" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B312" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
@@ -6096,10 +6099,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B313" s="18" t="s">
-        <v>410</v>
+        <v>60192</v>
+      </c>
+      <c r="B313" t="s">
+        <v>264</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -6110,10 +6113,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B314" t="s">
-        <v>265</v>
+        <v>60194</v>
+      </c>
+      <c r="B314" s="18" t="s">
+        <v>410</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
@@ -6124,10 +6127,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B315" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
@@ -6138,10 +6141,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B316" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
@@ -6152,52 +6155,52 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B317" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" t="s">
-        <v>9</v>
+      <c r="D317" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B318" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="13" t="s">
-        <v>5</v>
+      <c r="D318" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B319" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="1" t="s">
-        <v>8</v>
+      <c r="D319" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B320" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
@@ -6208,10 +6211,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B321" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
@@ -6222,192 +6225,192 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B322" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="10" t="s">
+      <c r="D322" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B323" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="1" t="s">
+      <c r="D323" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B324" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="10" t="s">
+      <c r="D324" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B325" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D325" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B326" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D326" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B327" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="1" t="s">
+      <c r="D327" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B328" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="10" t="s">
-        <v>5</v>
+      <c r="D328" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B329" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="17" t="s">
-        <v>9</v>
+      <c r="D329" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B330" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="10" t="s">
-        <v>8</v>
+      <c r="D330" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B331" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B331" t="s">
+        <v>280</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="7" t="s">
-        <v>9</v>
+      <c r="D331" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D332" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B333" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D333" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D334" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6418,10 +6421,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B336" s="18" t="s">
-        <v>408</v>
+        <v>60246</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
@@ -6432,38 +6435,38 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B337" s="8" t="s">
-        <v>339</v>
+        <v>60249</v>
+      </c>
+      <c r="B337" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="11" t="s">
-        <v>8</v>
+      <c r="D337" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B338" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="1" t="s">
+      <c r="D338" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B339" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
@@ -6474,10 +6477,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B340" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6488,10 +6491,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B341" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6502,66 +6505,66 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B342" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B342" t="s">
+        <v>284</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="11" t="s">
+      <c r="D342" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B343" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="10" t="s">
+      <c r="D343" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B344" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="1" t="s">
-        <v>9</v>
+      <c r="D344" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B345" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B346" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
@@ -6572,10 +6575,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B347" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6586,10 +6589,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B348" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6600,38 +6603,38 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B349" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="13" t="s">
+      <c r="D349" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B350" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="1" t="s">
-        <v>5</v>
+      <c r="D350" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B351" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6642,66 +6645,66 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B352" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B352" t="s">
+        <v>292</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D352" s="11" t="s">
-        <v>9</v>
+      <c r="D352" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D353" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B354" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B354" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="1" t="s">
-        <v>8</v>
+      <c r="D354" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B355" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B355" t="s">
+        <v>378</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="9" t="s">
-        <v>5</v>
+      <c r="D355" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B356" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6712,10 +6715,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6726,52 +6729,52 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B358" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B358" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="12" t="s">
+      <c r="D358" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B359" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B360" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B361" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6782,66 +6785,66 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B362" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B362" t="s">
+        <v>376</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D362" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60293</v>
+        <v>60292</v>
       </c>
       <c r="B363" s="18" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B364" t="s">
-        <v>391</v>
+        <v>60293</v>
+      </c>
+      <c r="B364" s="18" t="s">
+        <v>418</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D364" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B365" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B366" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6852,10 +6855,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B367" s="18" t="s">
-        <v>411</v>
+        <v>60299</v>
+      </c>
+      <c r="B367" t="s">
+        <v>388</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6866,10 +6869,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B368" s="18" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6880,10 +6883,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60305</v>
+        <v>60303</v>
       </c>
       <c r="B369" s="18" t="s">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6894,38 +6897,38 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B370" t="s">
-        <v>403</v>
+        <v>60305</v>
+      </c>
+      <c r="B370" s="18" t="s">
+        <v>446</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D370" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B371" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="15" t="s">
-        <v>5</v>
+      <c r="D371" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B372" t="s">
-        <v>415</v>
+        <v>293</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6936,24 +6939,24 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B373" t="s">
-        <v>294</v>
+        <v>415</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="12" t="s">
-        <v>8</v>
+      <c r="D373" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B374" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6964,10 +6967,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B375" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6978,10 +6981,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B376" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6992,52 +6995,52 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B377" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="15" t="s">
-        <v>5</v>
+      <c r="D377" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B378" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="12" t="s">
-        <v>8</v>
+      <c r="D378" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B379" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="15" t="s">
-        <v>5</v>
+      <c r="D379" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B380" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -7048,94 +7051,94 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B381" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="12" t="s">
-        <v>8</v>
+      <c r="D381" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B382" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="15" t="s">
-        <v>5</v>
+      <c r="D382" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B383" t="s">
-        <v>419</v>
+        <v>303</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D383" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B384" t="s">
-        <v>304</v>
+        <v>419</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D384" s="12" t="s">
+      <c r="D384" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B385" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="15" t="s">
-        <v>5</v>
+      <c r="D385" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B386" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="9" t="s">
-        <v>9</v>
+      <c r="D386" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B387" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7146,38 +7149,38 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B388" t="s">
-        <v>420</v>
+        <v>331</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D388" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70638</v>
+        <v>70116</v>
       </c>
       <c r="B389" t="s">
-        <v>306</v>
+        <v>420</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="12" t="s">
+      <c r="D389" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B390" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7188,10 +7191,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B391" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7202,10 +7205,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B392" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7216,10 +7219,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B393" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7230,10 +7233,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B394" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7244,52 +7247,52 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B395" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D395" s="15" t="s">
-        <v>5</v>
+      <c r="D395" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B396" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D396" s="12" t="s">
-        <v>8</v>
+      <c r="D396" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B397" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D397" s="9" t="s">
-        <v>5</v>
+      <c r="D397" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B398" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B398" t="s">
+        <v>333</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7300,24 +7303,24 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B399" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B399" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D399" s="12" t="s">
-        <v>8</v>
+      <c r="D399" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B400" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7328,10 +7331,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B401" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7342,10 +7345,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B402" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7356,10 +7359,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B403" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7370,10 +7373,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B404" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7384,10 +7387,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B405" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7398,10 +7401,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B406" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7412,10 +7415,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B407" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7426,10 +7429,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B408" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7440,38 +7443,38 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B409" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D409" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B410" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D410" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B411" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B411" t="s">
+        <v>382</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7482,10 +7485,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B412" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7496,10 +7499,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7510,10 +7513,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7524,68 +7527,68 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B415" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D415" s="9" t="s">
-        <v>9</v>
+      <c r="D415" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B416" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D416" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A417" s="6">
         <v>1045</v>
       </c>
-      <c r="B416" s="8" t="s">
+      <c r="B417" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C416" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D416" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="417" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A417">
-        <v>1043</v>
-      </c>
-      <c r="B417" t="s">
-        <v>422</v>
-      </c>
-      <c r="C417" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D417" t="s">
-        <v>8</v>
+      <c r="C417" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D417" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418">
+        <v>1043</v>
+      </c>
+      <c r="B418" t="s">
+        <v>422</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D418" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A419">
         <v>20340</v>
       </c>
-      <c r="B418" t="s">
+      <c r="B419" t="s">
         <v>423</v>
       </c>
-      <c r="C418" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D418" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="419" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A419">
-        <v>40146</v>
-      </c>
-      <c r="B419" t="s">
-        <v>424</v>
-      </c>
-      <c r="C419" s="14" t="s">
+      <c r="C419" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D419" t="s">
@@ -7594,24 +7597,24 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B420" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C420" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D420" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B421" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C421" s="14" t="s">
         <v>4</v>
@@ -7622,10 +7625,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B422" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C422" s="14" t="s">
         <v>4</v>
@@ -7636,66 +7639,66 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B423" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C423" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D423" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B424" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C424" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D424" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B425" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C425" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D425" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B426" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C426" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D426" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B427" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C427" s="14" t="s">
         <v>4</v>
@@ -7706,24 +7709,24 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B428" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D428" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B429" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
@@ -7734,10 +7737,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B430" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
@@ -7748,38 +7751,38 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B431" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D431" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B432" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B433" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
@@ -7790,10 +7793,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B434" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7804,38 +7807,38 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B435" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B436" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B437" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
@@ -7846,24 +7849,24 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B438" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D438" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B439" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
@@ -7874,20 +7877,34 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
+        <v>1047</v>
+      </c>
+      <c r="B440" t="s">
+        <v>444</v>
+      </c>
+      <c r="C440" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D440" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A441">
         <v>20398</v>
       </c>
-      <c r="B440" t="s">
+      <c r="B441" t="s">
         <v>445</v>
       </c>
-      <c r="C440" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D440" t="s">
+      <c r="C441" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D441" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D416"/>
+  <autoFilter ref="A1:D417"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$417</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$418</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="449">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1366,6 +1366,9 @@
   </si>
   <si>
     <t>FERRETERIA OROÑO</t>
+  </si>
+  <si>
+    <t>FERRETERIA LORENA</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1724,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D441"/>
+  <dimension ref="A1:D442"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6435,10 +6438,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B337" s="18" t="s">
-        <v>408</v>
+        <v>60247</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>448</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
@@ -6449,38 +6452,38 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B338" s="8" t="s">
-        <v>339</v>
+        <v>60249</v>
+      </c>
+      <c r="B338" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="11" t="s">
-        <v>8</v>
+      <c r="D338" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B339" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="1" t="s">
+      <c r="D339" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B340" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6491,10 +6494,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B341" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6505,10 +6508,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B342" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6519,66 +6522,66 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B343" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B343" t="s">
+        <v>284</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="11" t="s">
+      <c r="D343" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B344" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B344" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="10" t="s">
+      <c r="D344" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B345" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="1" t="s">
-        <v>9</v>
+      <c r="D345" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B346" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B347" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6589,10 +6592,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B348" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6603,10 +6606,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B349" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6617,38 +6620,38 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B350" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="13" t="s">
+      <c r="D350" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B351" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="1" t="s">
-        <v>5</v>
+      <c r="D351" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B352" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6659,66 +6662,66 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B353" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B353" t="s">
+        <v>292</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="11" t="s">
-        <v>9</v>
+      <c r="D353" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B355" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B355" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="1" t="s">
-        <v>8</v>
+      <c r="D355" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B356" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B356" t="s">
+        <v>378</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="9" t="s">
-        <v>5</v>
+      <c r="D356" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6729,10 +6732,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6743,52 +6746,52 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B359" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B359" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="12" t="s">
+      <c r="D359" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B360" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B361" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D361" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B362" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6799,66 +6802,66 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B363" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B363" t="s">
+        <v>376</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60293</v>
+        <v>60292</v>
       </c>
       <c r="B364" s="18" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D364" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B365" t="s">
-        <v>391</v>
+        <v>60293</v>
+      </c>
+      <c r="B365" s="18" t="s">
+        <v>418</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B366" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B367" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6869,10 +6872,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B368" s="18" t="s">
-        <v>411</v>
+        <v>60299</v>
+      </c>
+      <c r="B368" t="s">
+        <v>388</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6883,10 +6886,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B369" s="18" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6897,10 +6900,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60305</v>
+        <v>60303</v>
       </c>
       <c r="B370" s="18" t="s">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6911,38 +6914,38 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B371" t="s">
-        <v>403</v>
+        <v>60305</v>
+      </c>
+      <c r="B371" s="18" t="s">
+        <v>446</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D371" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B372" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="15" t="s">
-        <v>5</v>
+      <c r="D372" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B373" t="s">
-        <v>415</v>
+        <v>293</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6953,24 +6956,24 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B374" t="s">
-        <v>294</v>
+        <v>415</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="12" t="s">
-        <v>8</v>
+      <c r="D374" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B375" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6981,10 +6984,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B376" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6995,10 +6998,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B377" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -7009,52 +7012,52 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B378" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="15" t="s">
-        <v>5</v>
+      <c r="D378" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B379" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="12" t="s">
-        <v>8</v>
+      <c r="D379" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B380" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="15" t="s">
-        <v>5</v>
+      <c r="D380" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B381" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -7065,94 +7068,94 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B382" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="12" t="s">
-        <v>8</v>
+      <c r="D382" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B383" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="15" t="s">
-        <v>5</v>
+      <c r="D383" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B384" t="s">
-        <v>419</v>
+        <v>303</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D384" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B385" t="s">
-        <v>304</v>
+        <v>419</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="12" t="s">
+      <c r="D385" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B386" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="15" t="s">
-        <v>5</v>
+      <c r="D386" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B387" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="9" t="s">
-        <v>9</v>
+      <c r="D387" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B388" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7163,38 +7166,38 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B389" t="s">
-        <v>420</v>
+        <v>331</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D389" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70638</v>
+        <v>70116</v>
       </c>
       <c r="B390" t="s">
-        <v>306</v>
+        <v>420</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D390" s="12" t="s">
+      <c r="D390" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B391" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7205,10 +7208,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B392" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7219,10 +7222,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B393" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7233,10 +7236,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B394" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7247,10 +7250,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B395" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7261,52 +7264,52 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B396" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D396" s="15" t="s">
-        <v>5</v>
+      <c r="D396" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B397" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D397" s="12" t="s">
-        <v>8</v>
+      <c r="D397" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B398" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D398" s="9" t="s">
-        <v>5</v>
+      <c r="D398" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B399" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B399" t="s">
+        <v>333</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7317,24 +7320,24 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B400" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B400" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D400" s="12" t="s">
-        <v>8</v>
+      <c r="D400" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B401" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7345,10 +7348,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B402" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7359,10 +7362,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B403" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7373,10 +7376,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B404" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7387,10 +7390,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B405" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7401,10 +7404,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B406" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7415,10 +7418,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B407" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7429,10 +7432,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B408" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7443,10 +7446,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B409" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
@@ -7457,38 +7460,38 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B410" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D410" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B411" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D411" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B412" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B412" t="s">
+        <v>382</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7499,10 +7502,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7513,10 +7516,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7527,10 +7530,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B415" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7541,68 +7544,68 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D416" s="9" t="s">
-        <v>9</v>
+      <c r="D416" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B417" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D417" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A418" s="6">
         <v>1045</v>
       </c>
-      <c r="B417" s="8" t="s">
+      <c r="B418" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C417" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D417" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="418" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A418">
-        <v>1043</v>
-      </c>
-      <c r="B418" t="s">
-        <v>422</v>
-      </c>
-      <c r="C418" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D418" t="s">
-        <v>8</v>
+      <c r="C418" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D418" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419">
+        <v>1043</v>
+      </c>
+      <c r="B419" t="s">
+        <v>422</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D419" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A420">
         <v>20340</v>
       </c>
-      <c r="B419" t="s">
+      <c r="B420" t="s">
         <v>423</v>
       </c>
-      <c r="C419" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D419" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="420" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A420">
-        <v>40146</v>
-      </c>
-      <c r="B420" t="s">
-        <v>424</v>
-      </c>
-      <c r="C420" s="14" t="s">
+      <c r="C420" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D420" t="s">
@@ -7611,24 +7614,24 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B421" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C421" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D421" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B422" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C422" s="14" t="s">
         <v>4</v>
@@ -7639,10 +7642,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B423" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C423" s="14" t="s">
         <v>4</v>
@@ -7653,66 +7656,66 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B424" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C424" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D424" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B425" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C425" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D425" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B426" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C426" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D426" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B427" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C427" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D427" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B428" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
@@ -7723,24 +7726,24 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B429" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D429" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B430" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
@@ -7751,10 +7754,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B431" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
@@ -7765,38 +7768,38 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B432" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B433" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D433" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B434" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7807,10 +7810,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B435" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
@@ -7821,38 +7824,38 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B436" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B437" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B438" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
@@ -7863,24 +7866,24 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B439" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B440" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
@@ -7891,20 +7894,34 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
+        <v>1047</v>
+      </c>
+      <c r="B441" t="s">
+        <v>444</v>
+      </c>
+      <c r="C441" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D441" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A442">
         <v>20398</v>
       </c>
-      <c r="B441" t="s">
+      <c r="B442" t="s">
         <v>445</v>
       </c>
-      <c r="C441" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D441" t="s">
+      <c r="C442" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D442" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D417"/>
+  <autoFilter ref="A1:D418"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -5985,7 +5985,7 @@
         <v>4</v>
       </c>
       <c r="D304" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6853,7 +6853,7 @@
         <v>4</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -6517,7 +6517,7 @@
         <v>4</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6825,7 +6825,7 @@
         <v>4</v>
       </c>
       <c r="D364" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$418</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$420</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="451">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1369,6 +1369,12 @@
   </si>
   <si>
     <t>FERRETERIA LORENA</t>
+  </si>
+  <si>
+    <t>MATIAS OFICINA</t>
+  </si>
+  <si>
+    <t>JOCO OFICINA</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1730,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D442"/>
+  <dimension ref="A1:D444"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2065,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3036,52 +3042,52 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10107</v>
+        <v>1987</v>
       </c>
       <c r="B94" t="s">
-        <v>96</v>
+        <v>449</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" t="s">
-        <v>9</v>
+      <c r="D94" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10137</v>
+        <v>1988</v>
       </c>
       <c r="B95" t="s">
-        <v>123</v>
+        <v>450</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10157</v>
+        <v>10107</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>8</v>
+      <c r="D96" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10158</v>
+        <v>10137</v>
       </c>
       <c r="B97" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
@@ -3092,24 +3098,24 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10160</v>
+        <v>10157</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="13" t="s">
-        <v>5</v>
+      <c r="D98" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10162</v>
+        <v>10158</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
@@ -3120,10 +3126,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>10163</v>
+        <v>10160</v>
       </c>
       <c r="B100" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
@@ -3134,10 +3140,10 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>10165</v>
+        <v>10162</v>
       </c>
       <c r="B101" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
@@ -3148,136 +3154,136 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>348</v>
+        <v>10163</v>
+      </c>
+      <c r="B102" t="s">
+        <v>90</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="11" t="s">
-        <v>8</v>
+      <c r="D102" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>10167</v>
+        <v>10165</v>
       </c>
       <c r="B103" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="13" t="s">
-        <v>5</v>
+      <c r="D103" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>10424</v>
-      </c>
-      <c r="B104" t="s">
-        <v>12</v>
+        <v>10166</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="17" t="s">
-        <v>9</v>
+      <c r="D104" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>10425</v>
+        <v>10167</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="17" t="s">
-        <v>9</v>
+      <c r="D105" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20094</v>
+        <v>10424</v>
       </c>
       <c r="B106" t="s">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="10" t="s">
-        <v>8</v>
+      <c r="D106" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20095</v>
+        <v>10425</v>
       </c>
       <c r="B107" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="10" t="s">
-        <v>8</v>
+      <c r="D107" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20096</v>
+        <v>20094</v>
       </c>
       <c r="B108" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20100</v>
+        <v>20095</v>
       </c>
       <c r="B109" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20101</v>
+        <v>20096</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20103</v>
+        <v>20100</v>
       </c>
       <c r="B111" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3288,38 +3294,38 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20106</v>
+        <v>20101</v>
       </c>
       <c r="B112" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20108</v>
+        <v>20103</v>
       </c>
       <c r="B113" t="s">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="D113" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20109</v>
+        <v>20106</v>
       </c>
       <c r="B114" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3330,66 +3336,66 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20110</v>
+        <v>20108</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>219</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D115" s="13" t="s">
-        <v>5</v>
+      <c r="D115" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20113</v>
+        <v>20109</v>
       </c>
       <c r="B116" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="D116" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20114</v>
+        <v>20110</v>
       </c>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>8</v>
+      <c r="D117" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20116</v>
+        <v>20113</v>
       </c>
       <c r="B118" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20117</v>
+        <v>20114</v>
       </c>
       <c r="B119" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
@@ -3400,10 +3406,10 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20118</v>
+        <v>20116</v>
       </c>
       <c r="B120" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
@@ -3414,10 +3420,10 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20120</v>
+        <v>20117</v>
       </c>
       <c r="B121" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3428,10 +3434,10 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20121</v>
+        <v>20118</v>
       </c>
       <c r="B122" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3442,24 +3448,24 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20125</v>
+        <v>20120</v>
       </c>
       <c r="B123" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20127</v>
+        <v>20121</v>
       </c>
       <c r="B124" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3470,108 +3476,108 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20128</v>
+        <v>20125</v>
       </c>
       <c r="B125" t="s">
-        <v>208</v>
+        <v>88</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20129</v>
+        <v>20127</v>
       </c>
       <c r="B126" t="s">
-        <v>326</v>
+        <v>168</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20137</v>
+        <v>20128</v>
       </c>
       <c r="B127" t="s">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>5</v>
+      <c r="D127" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20138</v>
+        <v>20129</v>
       </c>
       <c r="B128" t="s">
-        <v>113</v>
+        <v>326</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="13" t="s">
-        <v>5</v>
+      <c r="D128" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20140</v>
+        <v>20137</v>
       </c>
       <c r="B129" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="13" t="s">
+      <c r="D129" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20142</v>
+        <v>20138</v>
       </c>
       <c r="B130" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>8</v>
+      <c r="D130" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20146</v>
+        <v>20140</v>
       </c>
       <c r="B131" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>8</v>
+      <c r="D131" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20148</v>
+        <v>20142</v>
       </c>
       <c r="B132" t="s">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
@@ -3582,38 +3588,38 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20156</v>
+        <v>20146</v>
       </c>
       <c r="B133" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="D133" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20159</v>
+        <v>20148</v>
       </c>
       <c r="B134" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="17" t="s">
-        <v>9</v>
+      <c r="D134" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20160</v>
+        <v>20156</v>
       </c>
       <c r="B135" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
@@ -3624,38 +3630,38 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20163</v>
+        <v>20159</v>
       </c>
       <c r="B136" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="10" t="s">
-        <v>8</v>
+      <c r="D136" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20164</v>
+        <v>20160</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" t="s">
-        <v>9</v>
+      <c r="D137" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20165</v>
+        <v>20163</v>
       </c>
       <c r="B138" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
@@ -3666,52 +3672,52 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20166</v>
+        <v>20164</v>
       </c>
       <c r="B139" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>8</v>
+      <c r="D139" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20169</v>
+        <v>20165</v>
       </c>
       <c r="B140" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="D140" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20173</v>
+        <v>20166</v>
       </c>
       <c r="B141" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="10" t="s">
+      <c r="D141" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20174</v>
+        <v>20169</v>
       </c>
       <c r="B142" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
@@ -3722,38 +3728,38 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20178</v>
+        <v>20173</v>
       </c>
       <c r="B143" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20179</v>
+        <v>20174</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" t="s">
-        <v>9</v>
+      <c r="D144" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20180</v>
+        <v>20178</v>
       </c>
       <c r="B145" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
@@ -3764,24 +3770,24 @@
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20183</v>
+        <v>20179</v>
       </c>
       <c r="B146" t="s">
-        <v>370</v>
+        <v>171</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="14" t="s">
-        <v>5</v>
+      <c r="D146" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20189</v>
+        <v>20180</v>
       </c>
       <c r="B147" t="s">
-        <v>329</v>
+        <v>149</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
@@ -3792,66 +3798,66 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20200</v>
+        <v>20183</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>370</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="13" t="s">
+      <c r="D148" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20201</v>
+        <v>20189</v>
       </c>
       <c r="B149" t="s">
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="13" t="s">
-        <v>5</v>
+      <c r="D149" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20204</v>
+        <v>20200</v>
       </c>
       <c r="B150" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="10" t="s">
-        <v>8</v>
+      <c r="D150" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20205</v>
+        <v>20201</v>
       </c>
       <c r="B151" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>9</v>
+      <c r="D151" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20211</v>
+        <v>20204</v>
       </c>
       <c r="B152" t="s">
-        <v>190</v>
+        <v>57</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
@@ -3862,24 +3868,24 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20224</v>
+        <v>20205</v>
       </c>
       <c r="B153" t="s">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20227</v>
+        <v>20211</v>
       </c>
       <c r="B154" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
@@ -3890,24 +3896,24 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20228</v>
+        <v>20224</v>
       </c>
       <c r="B155" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="13" t="s">
-        <v>5</v>
+      <c r="D155" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20230</v>
+        <v>20227</v>
       </c>
       <c r="B156" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
@@ -3918,10 +3924,10 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20234</v>
+        <v>20228</v>
       </c>
       <c r="B157" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
@@ -3932,24 +3938,24 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20236</v>
+        <v>20230</v>
       </c>
       <c r="B158" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="3" t="s">
-        <v>5</v>
+      <c r="D158" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20238</v>
+        <v>20234</v>
       </c>
       <c r="B159" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
@@ -3960,66 +3966,66 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20241</v>
+        <v>20236</v>
       </c>
       <c r="B160" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="13" t="s">
+      <c r="D160" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20242</v>
+        <v>20238</v>
       </c>
       <c r="B161" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="10" t="s">
-        <v>8</v>
+      <c r="D161" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20244</v>
+        <v>20241</v>
       </c>
       <c r="B162" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="10" t="s">
-        <v>8</v>
+      <c r="D162" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20246</v>
+        <v>20242</v>
       </c>
       <c r="B163" t="s">
-        <v>14</v>
+        <v>216</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="13" t="s">
-        <v>5</v>
+      <c r="D163" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20249</v>
+        <v>20244</v>
       </c>
       <c r="B164" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
@@ -4030,38 +4036,38 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20256</v>
+        <v>20246</v>
       </c>
       <c r="B165" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="1" t="s">
-        <v>8</v>
+      <c r="D165" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20257</v>
+        <v>20249</v>
       </c>
       <c r="B166" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="17" t="s">
-        <v>9</v>
+      <c r="D166" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20258</v>
+        <v>20256</v>
       </c>
       <c r="B167" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
@@ -4072,94 +4078,94 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20260</v>
+        <v>20257</v>
       </c>
       <c r="B168" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="13" t="s">
-        <v>5</v>
+      <c r="D168" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20261</v>
+        <v>20258</v>
       </c>
       <c r="B169" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="10" t="s">
+      <c r="D169" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20262</v>
+        <v>20260</v>
       </c>
       <c r="B170" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="10" t="s">
-        <v>8</v>
+      <c r="D170" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20267</v>
+        <v>20261</v>
       </c>
       <c r="B171" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20268</v>
+        <v>20262</v>
       </c>
       <c r="B172" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="D172" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20271</v>
+        <v>20267</v>
       </c>
       <c r="B173" t="s">
-        <v>34</v>
+        <v>401</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="13" t="s">
+      <c r="D173" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20272</v>
+        <v>20268</v>
       </c>
       <c r="B174" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
@@ -4170,10 +4176,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20275</v>
+        <v>20271</v>
       </c>
       <c r="B175" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
@@ -4184,10 +4190,10 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20277</v>
+        <v>20272</v>
       </c>
       <c r="B176" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
@@ -4198,80 +4204,80 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20281</v>
+        <v>20275</v>
       </c>
       <c r="B177" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="3" t="s">
+      <c r="D177" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20282</v>
+        <v>20277</v>
       </c>
       <c r="B178" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20284</v>
+        <v>20281</v>
       </c>
       <c r="B179" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="17" t="s">
-        <v>9</v>
+      <c r="D179" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20285</v>
+        <v>20282</v>
       </c>
       <c r="B180" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20289</v>
+        <v>20284</v>
       </c>
       <c r="B181" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="3" t="s">
-        <v>5</v>
+      <c r="D181" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20290</v>
+        <v>20285</v>
       </c>
       <c r="B182" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
@@ -4282,66 +4288,66 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20291</v>
+        <v>20289</v>
       </c>
       <c r="B183" t="s">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="10" t="s">
-        <v>8</v>
+      <c r="D183" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20292</v>
+        <v>20290</v>
       </c>
       <c r="B184" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="13" t="s">
-        <v>5</v>
+      <c r="D184" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20293</v>
+        <v>20291</v>
       </c>
       <c r="B185" t="s">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="13" t="s">
-        <v>5</v>
+      <c r="D185" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20294</v>
+        <v>20292</v>
       </c>
       <c r="B186" t="s">
-        <v>202</v>
+        <v>32</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="10" t="s">
-        <v>8</v>
+      <c r="D186" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20296</v>
+        <v>20293</v>
       </c>
       <c r="B187" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
@@ -4352,38 +4358,38 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20298</v>
+        <v>20294</v>
       </c>
       <c r="B188" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="D188" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20299</v>
+        <v>20296</v>
       </c>
       <c r="B189" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="1" t="s">
-        <v>8</v>
+      <c r="D189" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20301</v>
+        <v>20298</v>
       </c>
       <c r="B190" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4394,10 +4400,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20303</v>
+        <v>20299</v>
       </c>
       <c r="B191" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4408,66 +4414,66 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20309</v>
+        <v>20301</v>
       </c>
       <c r="B192" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="13" t="s">
-        <v>5</v>
+      <c r="D192" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20310</v>
+        <v>20303</v>
       </c>
       <c r="B193" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="13" t="s">
-        <v>5</v>
+      <c r="D193" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20318</v>
+        <v>20309</v>
       </c>
       <c r="B194" t="s">
-        <v>209</v>
+        <v>28</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="1" t="s">
-        <v>8</v>
+      <c r="D194" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20319</v>
+        <v>20310</v>
       </c>
       <c r="B195" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="10" t="s">
-        <v>8</v>
+      <c r="D195" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20320</v>
+        <v>20318</v>
       </c>
       <c r="B196" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4478,24 +4484,24 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20324</v>
+        <v>20319</v>
       </c>
       <c r="B197" t="s">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="D197" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20331</v>
+        <v>20320</v>
       </c>
       <c r="B198" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
@@ -4506,24 +4512,24 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20333</v>
+        <v>20324</v>
       </c>
       <c r="B199" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="13" t="s">
-        <v>5</v>
+      <c r="D199" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20337</v>
+        <v>20331</v>
       </c>
       <c r="B200" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4534,24 +4540,24 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20343</v>
+        <v>20333</v>
       </c>
       <c r="B201" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="1" t="s">
-        <v>8</v>
+      <c r="D201" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20344</v>
+        <v>20337</v>
       </c>
       <c r="B202" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4562,24 +4568,24 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20351</v>
+        <v>20343</v>
       </c>
       <c r="B203" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="13" t="s">
-        <v>5</v>
+      <c r="D203" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20357</v>
+        <v>20344</v>
       </c>
       <c r="B204" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4590,10 +4596,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20361</v>
+        <v>20351</v>
       </c>
       <c r="B205" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
@@ -4604,80 +4610,80 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20362</v>
+        <v>20357</v>
       </c>
       <c r="B206" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="10" t="s">
+      <c r="D206" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20363</v>
+        <v>20361</v>
       </c>
       <c r="B207" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="10" t="s">
-        <v>8</v>
+      <c r="D207" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20364</v>
+        <v>20362</v>
       </c>
       <c r="B208" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="13" t="s">
-        <v>5</v>
+      <c r="D208" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20366</v>
+        <v>20363</v>
       </c>
       <c r="B209" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="D209" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20367</v>
+        <v>20364</v>
       </c>
       <c r="B210" t="s">
-        <v>47</v>
+        <v>196</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="1" t="s">
-        <v>8</v>
+      <c r="D210" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20369</v>
+        <v>20366</v>
       </c>
       <c r="B211" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
@@ -4688,10 +4694,10 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20371</v>
+        <v>20367</v>
       </c>
       <c r="B212" t="s">
-        <v>223</v>
+        <v>47</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
@@ -4702,24 +4708,24 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20372</v>
+        <v>20369</v>
       </c>
       <c r="B213" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="D213" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20374</v>
+        <v>20371</v>
       </c>
       <c r="B214" t="s">
-        <v>61</v>
+        <v>223</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4730,10 +4736,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20377</v>
+        <v>20372</v>
       </c>
       <c r="B215" t="s">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4744,66 +4750,66 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20379</v>
+        <v>20374</v>
       </c>
       <c r="B216" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="10" t="s">
+      <c r="D216" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20380</v>
+        <v>20377</v>
       </c>
       <c r="B217" t="s">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="13" t="s">
-        <v>5</v>
+      <c r="D217" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20381</v>
+        <v>20379</v>
       </c>
       <c r="B218" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D218" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20384</v>
+        <v>20380</v>
       </c>
       <c r="B219" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="10" t="s">
-        <v>8</v>
+      <c r="D219" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20385</v>
+        <v>20381</v>
       </c>
       <c r="B220" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
@@ -4814,38 +4820,38 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20386</v>
+        <v>20384</v>
       </c>
       <c r="B221" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="D221" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20388</v>
+        <v>20385</v>
       </c>
       <c r="B222" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="10" t="s">
+      <c r="D222" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20391</v>
+        <v>20386</v>
       </c>
       <c r="B223" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
@@ -4856,10 +4862,10 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20394</v>
+        <v>20388</v>
       </c>
       <c r="B224" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
@@ -4870,10 +4876,10 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20395</v>
+        <v>20391</v>
       </c>
       <c r="B225" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
@@ -4884,38 +4890,38 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20396</v>
+        <v>20394</v>
       </c>
       <c r="B226" t="s">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="1" t="s">
+      <c r="D226" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B227" s="8" t="s">
-        <v>344</v>
+        <v>20395</v>
+      </c>
+      <c r="B227" t="s">
+        <v>161</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="11" t="s">
-        <v>5</v>
+      <c r="D227" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>30101</v>
+        <v>20396</v>
       </c>
       <c r="B228" t="s">
-        <v>167</v>
+        <v>330</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
@@ -4926,136 +4932,136 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40124</v>
-      </c>
-      <c r="B229" t="s">
-        <v>24</v>
+        <v>20397</v>
+      </c>
+      <c r="B229" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="13" t="s">
+      <c r="D229" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40125</v>
+        <v>30101</v>
       </c>
       <c r="B230" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="13" t="s">
-        <v>5</v>
+      <c r="D230" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40127</v>
+        <v>40124</v>
       </c>
       <c r="B231" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="1" t="s">
-        <v>8</v>
+      <c r="D231" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40129</v>
+        <v>40125</v>
       </c>
       <c r="B232" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="1" t="s">
-        <v>8</v>
+      <c r="D232" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40137</v>
+        <v>40127</v>
       </c>
       <c r="B233" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="10" t="s">
+      <c r="D233" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40139</v>
+        <v>40129</v>
       </c>
       <c r="B234" t="s">
-        <v>327</v>
+        <v>138</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="10" t="s">
+      <c r="D234" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40140</v>
+        <v>40137</v>
       </c>
       <c r="B235" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="1" t="s">
+      <c r="D235" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40141</v>
+        <v>40139</v>
       </c>
       <c r="B236" t="s">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="13" t="s">
-        <v>5</v>
+      <c r="D236" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40143</v>
+        <v>40140</v>
       </c>
       <c r="B237" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="10" t="s">
+      <c r="D237" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40144</v>
+        <v>40141</v>
       </c>
       <c r="B238" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
@@ -5066,80 +5072,80 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40145</v>
+        <v>40143</v>
       </c>
       <c r="B239" t="s">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="13" t="s">
-        <v>5</v>
+      <c r="D239" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40147</v>
+        <v>40144</v>
       </c>
       <c r="B240" t="s">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="19" t="s">
-        <v>8</v>
+      <c r="D240" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40150</v>
+        <v>40145</v>
       </c>
       <c r="B241" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="10" t="s">
-        <v>8</v>
+      <c r="D241" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>40151</v>
+        <v>40147</v>
       </c>
       <c r="B242" t="s">
-        <v>54</v>
+        <v>405</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="D242" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50102</v>
+        <v>40150</v>
       </c>
       <c r="B243" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="13" t="s">
-        <v>5</v>
+      <c r="D243" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50222</v>
+        <v>40151</v>
       </c>
       <c r="B244" t="s">
-        <v>215</v>
+        <v>54</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
@@ -5150,206 +5156,206 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50223</v>
+        <v>50102</v>
       </c>
       <c r="B245" t="s">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="10" t="s">
-        <v>8</v>
+      <c r="D245" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50224</v>
+        <v>50222</v>
       </c>
       <c r="B246" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="3" t="s">
-        <v>5</v>
+      <c r="D246" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50444</v>
+        <v>50223</v>
       </c>
       <c r="B247" t="s">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="D247" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50445</v>
+        <v>50224</v>
       </c>
       <c r="B248" t="s">
-        <v>354</v>
+        <v>42</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="11" t="s">
+      <c r="D248" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50607</v>
+        <v>50444</v>
       </c>
       <c r="B249" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="13" t="s">
-        <v>5</v>
+      <c r="D249" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50608</v>
+        <v>50445</v>
       </c>
       <c r="B250" t="s">
-        <v>177</v>
+        <v>354</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
-        <v>8</v>
+      <c r="D250" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B251" s="8" t="s">
-        <v>347</v>
+        <v>50607</v>
+      </c>
+      <c r="B251" t="s">
+        <v>76</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="14" t="s">
-        <v>8</v>
+      <c r="D251" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50622</v>
+        <v>50608</v>
       </c>
       <c r="B252" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="16" t="s">
+      <c r="D252" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50623</v>
-      </c>
-      <c r="B253" t="s">
-        <v>110</v>
+        <v>50611</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="10" t="s">
+      <c r="D253" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50625</v>
+        <v>50622</v>
       </c>
       <c r="B254" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="10" t="s">
+      <c r="D254" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50629</v>
+        <v>50623</v>
       </c>
       <c r="B255" t="s">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="1" t="s">
-        <v>5</v>
+      <c r="D255" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50630</v>
+        <v>50625</v>
       </c>
       <c r="B256" t="s">
-        <v>360</v>
+        <v>204</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="14" t="s">
+      <c r="D256" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50803</v>
+        <v>50629</v>
       </c>
       <c r="B257" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50805</v>
+        <v>50630</v>
       </c>
       <c r="B258" t="s">
-        <v>135</v>
+        <v>360</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="10" t="s">
+      <c r="D258" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50806</v>
+        <v>50803</v>
       </c>
       <c r="B259" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
@@ -5360,304 +5366,304 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50808</v>
+        <v>50805</v>
       </c>
       <c r="B260" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="13" t="s">
-        <v>5</v>
+      <c r="D260" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50809</v>
+        <v>50806</v>
       </c>
       <c r="B261" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="13" t="s">
-        <v>5</v>
+      <c r="D261" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50810</v>
+        <v>50808</v>
       </c>
       <c r="B262" t="s">
-        <v>175</v>
+        <v>16</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="1" t="s">
-        <v>8</v>
+      <c r="D262" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50812</v>
+        <v>50809</v>
       </c>
       <c r="B263" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="1" t="s">
-        <v>8</v>
+      <c r="D263" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50813</v>
+        <v>50810</v>
       </c>
       <c r="B264" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="17" t="s">
-        <v>9</v>
+      <c r="D264" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50815</v>
+        <v>50812</v>
       </c>
       <c r="B265" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="10" t="s">
+      <c r="D265" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50816</v>
+        <v>50813</v>
       </c>
       <c r="B266" t="s">
-        <v>205</v>
+        <v>71</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="1" t="s">
-        <v>8</v>
+      <c r="D266" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50818</v>
+        <v>50815</v>
       </c>
       <c r="B267" t="s">
-        <v>227</v>
+        <v>114</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="13" t="s">
-        <v>5</v>
+      <c r="D267" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50819</v>
+        <v>50816</v>
       </c>
       <c r="B268" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="10" t="s">
+      <c r="D268" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50820</v>
+        <v>50818</v>
       </c>
       <c r="B269" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="10" t="s">
-        <v>8</v>
+      <c r="D269" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50821</v>
+        <v>50819</v>
       </c>
       <c r="B270" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="1" t="s">
+      <c r="D270" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50823</v>
+        <v>50820</v>
       </c>
       <c r="B271" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="17" t="s">
-        <v>9</v>
+      <c r="D271" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50824</v>
+        <v>50821</v>
       </c>
       <c r="B272" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="13" t="s">
-        <v>5</v>
+      <c r="D272" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50825</v>
+        <v>50823</v>
       </c>
       <c r="B273" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="10" t="s">
-        <v>8</v>
+      <c r="D273" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50826</v>
+        <v>50824</v>
       </c>
       <c r="B274" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="10" t="s">
-        <v>8</v>
+      <c r="D274" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50827</v>
+        <v>50825</v>
       </c>
       <c r="B275" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="1" t="s">
+      <c r="D275" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50829</v>
+        <v>50826</v>
       </c>
       <c r="B276" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="1" t="s">
+      <c r="D276" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50830</v>
+        <v>50827</v>
       </c>
       <c r="B277" t="s">
-        <v>366</v>
+        <v>235</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="11" t="s">
+      <c r="D277" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50831</v>
+        <v>50829</v>
       </c>
       <c r="B278" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="11" t="s">
-        <v>9</v>
+      <c r="D278" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B279" s="8" t="s">
-        <v>349</v>
+        <v>50830</v>
+      </c>
+      <c r="B279" t="s">
+        <v>366</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D279" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50833</v>
-      </c>
-      <c r="B280" s="8" t="s">
-        <v>397</v>
+        <v>50831</v>
+      </c>
+      <c r="B280" t="s">
+        <v>351</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50230</v>
+        <v>50832</v>
       </c>
       <c r="B281" s="8" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5668,10 +5674,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>50231</v>
+        <v>50833</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5682,38 +5688,38 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B283" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="13" t="s">
+      <c r="D283" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60109</v>
-      </c>
-      <c r="B284" t="s">
-        <v>328</v>
+        <v>50231</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>421</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60124</v>
+        <v>60103</v>
       </c>
       <c r="B285" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
@@ -5724,80 +5730,80 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60125</v>
+        <v>60109</v>
       </c>
       <c r="B286" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="13" t="s">
-        <v>5</v>
+      <c r="D286" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60126</v>
+        <v>60124</v>
       </c>
       <c r="B287" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="10" t="s">
-        <v>8</v>
+      <c r="D287" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60128</v>
+        <v>60125</v>
       </c>
       <c r="B288" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="3" t="s">
+      <c r="D288" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60130</v>
+        <v>60126</v>
       </c>
       <c r="B289" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="1" t="s">
+      <c r="D289" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60133</v>
+        <v>60128</v>
       </c>
       <c r="B290" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="13" t="s">
+      <c r="D290" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60134</v>
+        <v>60130</v>
       </c>
       <c r="B291" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
@@ -5808,24 +5814,24 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60137</v>
+        <v>60133</v>
       </c>
       <c r="B292" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="1" t="s">
-        <v>8</v>
+      <c r="D292" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60139</v>
+        <v>60134</v>
       </c>
       <c r="B293" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
@@ -5836,10 +5842,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60142</v>
+        <v>60137</v>
       </c>
       <c r="B294" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
@@ -5850,10 +5856,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60148</v>
+        <v>60139</v>
       </c>
       <c r="B295" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5864,10 +5870,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60149</v>
+        <v>60142</v>
       </c>
       <c r="B296" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5878,122 +5884,122 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60150</v>
+        <v>60148</v>
       </c>
       <c r="B297" t="s">
-        <v>332</v>
+        <v>248</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="13" t="s">
-        <v>5</v>
+      <c r="D297" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60158</v>
+        <v>60149</v>
       </c>
       <c r="B298" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="10" t="s">
+      <c r="D298" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60159</v>
+        <v>60150</v>
       </c>
       <c r="B299" t="s">
-        <v>251</v>
+        <v>332</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="1" t="s">
-        <v>8</v>
+      <c r="D299" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60162</v>
+        <v>60158</v>
       </c>
       <c r="B300" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="13" t="s">
-        <v>5</v>
+      <c r="D300" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60163</v>
+        <v>60159</v>
       </c>
       <c r="B301" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="13" t="s">
-        <v>5</v>
+      <c r="D301" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60165</v>
+        <v>60162</v>
       </c>
       <c r="B302" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="1" t="s">
-        <v>8</v>
+      <c r="D302" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60169</v>
+        <v>60163</v>
       </c>
       <c r="B303" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="1" t="s">
-        <v>8</v>
+      <c r="D303" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B304" s="8" t="s">
-        <v>337</v>
+        <v>60165</v>
+      </c>
+      <c r="B304" t="s">
+        <v>254</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="11" t="s">
-        <v>5</v>
+      <c r="D304" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60172</v>
+        <v>60169</v>
       </c>
       <c r="B305" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -6004,66 +6010,66 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60174</v>
-      </c>
-      <c r="B306" t="s">
-        <v>257</v>
+        <v>60170</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="13" t="s">
+      <c r="D306" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60176</v>
+        <v>60172</v>
       </c>
       <c r="B307" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="13" t="s">
-        <v>5</v>
+      <c r="D307" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60178</v>
+        <v>60174</v>
       </c>
       <c r="B308" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="1" t="s">
-        <v>8</v>
+      <c r="D308" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60180</v>
+        <v>60176</v>
       </c>
       <c r="B309" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="10" t="s">
-        <v>8</v>
+      <c r="D309" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60184</v>
+        <v>60178</v>
       </c>
       <c r="B310" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -6074,52 +6080,52 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60190</v>
+        <v>60180</v>
       </c>
       <c r="B311" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="1" t="s">
+      <c r="D311" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60191</v>
+        <v>60184</v>
       </c>
       <c r="B312" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="10" t="s">
+      <c r="D312" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60192</v>
+        <v>60190</v>
       </c>
       <c r="B313" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="10" t="s">
+      <c r="D313" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B314" s="18" t="s">
-        <v>410</v>
+        <v>60191</v>
+      </c>
+      <c r="B314" t="s">
+        <v>263</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
@@ -6130,10 +6136,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B315" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
@@ -6144,10 +6150,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60196</v>
-      </c>
-      <c r="B316" t="s">
-        <v>266</v>
+        <v>60194</v>
+      </c>
+      <c r="B316" s="18" t="s">
+        <v>410</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
@@ -6158,10 +6164,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60198</v>
+        <v>60195</v>
       </c>
       <c r="B317" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
@@ -6172,66 +6178,66 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60201</v>
+        <v>60196</v>
       </c>
       <c r="B318" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" t="s">
-        <v>9</v>
+      <c r="D318" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60202</v>
+        <v>60198</v>
       </c>
       <c r="B319" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="13" t="s">
-        <v>5</v>
+      <c r="D319" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60204</v>
+        <v>60201</v>
       </c>
       <c r="B320" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" s="1" t="s">
-        <v>8</v>
+      <c r="D320" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60205</v>
+        <v>60202</v>
       </c>
       <c r="B321" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="1" t="s">
-        <v>8</v>
+      <c r="D321" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60206</v>
+        <v>60204</v>
       </c>
       <c r="B322" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
@@ -6242,24 +6248,24 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60209</v>
+        <v>60205</v>
       </c>
       <c r="B323" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="10" t="s">
+      <c r="D323" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60211</v>
+        <v>60206</v>
       </c>
       <c r="B324" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
@@ -6270,10 +6276,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60215</v>
+        <v>60209</v>
       </c>
       <c r="B325" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
@@ -6284,24 +6290,24 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60216</v>
+        <v>60211</v>
       </c>
       <c r="B326" t="s">
-        <v>381</v>
+        <v>274</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="10" t="s">
-        <v>9</v>
+      <c r="D326" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60217</v>
+        <v>60215</v>
       </c>
       <c r="B327" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
@@ -6312,94 +6318,94 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60219</v>
+        <v>60216</v>
       </c>
       <c r="B328" t="s">
-        <v>277</v>
+        <v>381</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="1" t="s">
-        <v>8</v>
+      <c r="D328" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60222</v>
+        <v>60217</v>
       </c>
       <c r="B329" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D329" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60225</v>
+        <v>60219</v>
       </c>
       <c r="B330" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="17" t="s">
-        <v>9</v>
+      <c r="D330" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60230</v>
+        <v>60222</v>
       </c>
       <c r="B331" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D331" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B332" s="8" t="s">
-        <v>338</v>
+        <v>60225</v>
+      </c>
+      <c r="B332" t="s">
+        <v>279</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="7" t="s">
+      <c r="D332" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60242</v>
-      </c>
-      <c r="B333" s="8" t="s">
-        <v>341</v>
+        <v>60230</v>
+      </c>
+      <c r="B333" t="s">
+        <v>280</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="7" t="s">
-        <v>5</v>
+      <c r="D333" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60243</v>
+        <v>60241</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>395</v>
+        <v>338</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6410,10 +6416,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60245</v>
+        <v>60242</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>387</v>
+        <v>341</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6424,24 +6430,24 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60246</v>
+        <v>60243</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D336" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60247</v>
+        <v>60245</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>448</v>
+        <v>387</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
@@ -6452,10 +6458,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B338" s="18" t="s">
-        <v>408</v>
+        <v>60246</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
@@ -6466,66 +6472,66 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60250</v>
+        <v>60247</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>339</v>
+        <v>448</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="11" t="s">
-        <v>8</v>
+      <c r="D339" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B340" t="s">
-        <v>281</v>
+        <v>60249</v>
+      </c>
+      <c r="B340" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="1" t="s">
-        <v>8</v>
+      <c r="D340" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60254</v>
-      </c>
-      <c r="B341" t="s">
-        <v>282</v>
+        <v>60250</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="1" t="s">
+      <c r="D341" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60257</v>
+        <v>60253</v>
       </c>
       <c r="B342" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60258</v>
+        <v>60254</v>
       </c>
       <c r="B343" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6536,80 +6542,80 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B344" s="8" t="s">
-        <v>343</v>
+        <v>60257</v>
+      </c>
+      <c r="B344" t="s">
+        <v>283</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="11" t="s">
-        <v>8</v>
+      <c r="D344" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60269</v>
+        <v>60258</v>
       </c>
       <c r="B345" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="10" t="s">
+      <c r="D345" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60270</v>
-      </c>
-      <c r="B346" t="s">
-        <v>286</v>
+        <v>60266</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="1" t="s">
-        <v>9</v>
+      <c r="D346" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60272</v>
+        <v>60269</v>
       </c>
       <c r="B347" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="1" t="s">
+      <c r="D347" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60274</v>
+        <v>60270</v>
       </c>
       <c r="B348" t="s">
-        <v>380</v>
+        <v>286</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60275</v>
+        <v>60272</v>
       </c>
       <c r="B349" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6620,10 +6626,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60276</v>
+        <v>60274</v>
       </c>
       <c r="B350" t="s">
-        <v>289</v>
+        <v>380</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6634,122 +6640,122 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60278</v>
+        <v>60275</v>
       </c>
       <c r="B351" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="13" t="s">
+      <c r="D351" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60279</v>
+        <v>60276</v>
       </c>
       <c r="B352" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60280</v>
+        <v>60278</v>
       </c>
       <c r="B353" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="1" t="s">
-        <v>5</v>
+      <c r="D353" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B354" s="8" t="s">
-        <v>336</v>
+        <v>60279</v>
+      </c>
+      <c r="B354" t="s">
+        <v>291</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="11" t="s">
-        <v>9</v>
+      <c r="D354" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60282</v>
-      </c>
-      <c r="B355" s="8" t="s">
-        <v>340</v>
+        <v>60280</v>
+      </c>
+      <c r="B355" t="s">
+        <v>292</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="11" t="s">
+      <c r="D355" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B356" t="s">
-        <v>378</v>
+        <v>60281</v>
+      </c>
+      <c r="B356" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="1" t="s">
-        <v>8</v>
+      <c r="D356" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60284</v>
+        <v>60282</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="9" t="s">
+      <c r="D357" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60285</v>
-      </c>
-      <c r="B358" s="8" t="s">
-        <v>350</v>
+        <v>60283</v>
+      </c>
+      <c r="B358" t="s">
+        <v>378</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="9" t="s">
-        <v>5</v>
+      <c r="D358" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60286</v>
+        <v>60284</v>
       </c>
       <c r="B359" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6760,38 +6766,38 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B360" t="s">
-        <v>377</v>
+        <v>60285</v>
+      </c>
+      <c r="B360" s="8" t="s">
+        <v>350</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="12" t="s">
+      <c r="D360" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60289</v>
-      </c>
-      <c r="B361" t="s">
-        <v>374</v>
+        <v>60286</v>
+      </c>
+      <c r="B361" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="12" t="s">
-        <v>9</v>
+      <c r="D361" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60290</v>
+        <v>60287</v>
       </c>
       <c r="B362" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6802,24 +6808,24 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60291</v>
+        <v>60289</v>
       </c>
       <c r="B363" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B364" s="18" t="s">
-        <v>400</v>
+        <v>60290</v>
+      </c>
+      <c r="B364" t="s">
+        <v>375</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6830,10 +6836,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60293</v>
-      </c>
-      <c r="B365" s="18" t="s">
-        <v>418</v>
+        <v>60291</v>
+      </c>
+      <c r="B365" t="s">
+        <v>376</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6844,10 +6850,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B366" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B366" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6858,10 +6864,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60297</v>
-      </c>
-      <c r="B367" t="s">
-        <v>392</v>
+        <v>60293</v>
+      </c>
+      <c r="B367" s="18" t="s">
+        <v>418</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6872,10 +6878,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60299</v>
+        <v>60296</v>
       </c>
       <c r="B368" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6886,10 +6892,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B369" s="18" t="s">
-        <v>411</v>
+        <v>60297</v>
+      </c>
+      <c r="B369" t="s">
+        <v>392</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6900,10 +6906,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60303</v>
-      </c>
-      <c r="B370" s="18" t="s">
-        <v>412</v>
+        <v>60299</v>
+      </c>
+      <c r="B370" t="s">
+        <v>388</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6914,10 +6920,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>60305</v>
+        <v>60302</v>
       </c>
       <c r="B371" s="18" t="s">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6928,80 +6934,80 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B372" t="s">
-        <v>403</v>
+        <v>60303</v>
+      </c>
+      <c r="B372" s="18" t="s">
+        <v>412</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D372" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>61004</v>
-      </c>
-      <c r="B373" t="s">
-        <v>293</v>
+        <v>60305</v>
+      </c>
+      <c r="B373" s="18" t="s">
+        <v>446</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="15" t="s">
+      <c r="D373" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>61007</v>
+        <v>61001</v>
       </c>
       <c r="B374" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="15" t="s">
-        <v>5</v>
+      <c r="D374" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B375" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="12" t="s">
-        <v>8</v>
+      <c r="D375" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>61012</v>
+        <v>61007</v>
       </c>
       <c r="B376" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="12" t="s">
-        <v>8</v>
+      <c r="D376" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>61018</v>
+        <v>61009</v>
       </c>
       <c r="B377" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -7012,10 +7018,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>61102</v>
+        <v>61012</v>
       </c>
       <c r="B378" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -7026,24 +7032,24 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>61205</v>
+        <v>61018</v>
       </c>
       <c r="B379" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="15" t="s">
-        <v>5</v>
+      <c r="D379" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>70100</v>
+        <v>61102</v>
       </c>
       <c r="B380" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -7054,10 +7060,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>70101</v>
+        <v>61205</v>
       </c>
       <c r="B381" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -7068,38 +7074,38 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>70102</v>
+        <v>70100</v>
       </c>
       <c r="B382" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="15" t="s">
-        <v>5</v>
+      <c r="D382" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>70103</v>
+        <v>70101</v>
       </c>
       <c r="B383" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="12" t="s">
-        <v>8</v>
+      <c r="D383" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>70106</v>
+        <v>70102</v>
       </c>
       <c r="B384" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7110,122 +7116,122 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>70107</v>
+        <v>70103</v>
       </c>
       <c r="B385" t="s">
-        <v>419</v>
+        <v>302</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="15" t="s">
+      <c r="D385" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B386" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="12" t="s">
-        <v>8</v>
+      <c r="D386" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70113</v>
+        <v>70107</v>
       </c>
       <c r="B387" t="s">
-        <v>305</v>
+        <v>419</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D387" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70114</v>
+        <v>70109</v>
       </c>
       <c r="B388" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="9" t="s">
-        <v>9</v>
+      <c r="D388" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70115</v>
+        <v>70113</v>
       </c>
       <c r="B389" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="9" t="s">
-        <v>9</v>
+      <c r="D389" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70116</v>
+        <v>70114</v>
       </c>
       <c r="B390" t="s">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D390" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B391" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D391" s="12" t="s">
-        <v>8</v>
+      <c r="D391" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70639</v>
+        <v>70116</v>
       </c>
       <c r="B392" t="s">
-        <v>307</v>
+        <v>420</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D392" s="12" t="s">
+      <c r="D392" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70640</v>
+        <v>70638</v>
       </c>
       <c r="B393" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7236,10 +7242,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70642</v>
+        <v>70639</v>
       </c>
       <c r="B394" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7250,10 +7256,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90504</v>
+        <v>70640</v>
       </c>
       <c r="B395" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7264,10 +7270,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90509</v>
+        <v>70642</v>
       </c>
       <c r="B396" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7278,24 +7284,24 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90602</v>
+        <v>90504</v>
       </c>
       <c r="B397" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D397" s="15" t="s">
-        <v>5</v>
+      <c r="D397" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90621</v>
+        <v>90509</v>
       </c>
       <c r="B398" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7306,66 +7312,66 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90622</v>
+        <v>90602</v>
       </c>
       <c r="B399" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D399" s="9" t="s">
+      <c r="D399" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B400" s="8" t="s">
-        <v>342</v>
+        <v>90621</v>
+      </c>
+      <c r="B400" t="s">
+        <v>313</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D400" s="9" t="s">
-        <v>5</v>
+      <c r="D400" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90658</v>
+        <v>90622</v>
       </c>
       <c r="B401" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D401" s="12" t="s">
-        <v>8</v>
+      <c r="D401" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90660</v>
-      </c>
-      <c r="B402" t="s">
-        <v>315</v>
+        <v>90631</v>
+      </c>
+      <c r="B402" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D402" s="12" t="s">
-        <v>8</v>
+      <c r="D402" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90668</v>
+        <v>90658</v>
       </c>
       <c r="B403" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7376,10 +7382,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90671</v>
+        <v>90660</v>
       </c>
       <c r="B404" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7390,10 +7396,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90679</v>
+        <v>90668</v>
       </c>
       <c r="B405" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7404,10 +7410,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90683</v>
+        <v>90671</v>
       </c>
       <c r="B406" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7418,10 +7424,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90705</v>
+        <v>90679</v>
       </c>
       <c r="B407" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7432,10 +7438,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90706</v>
+        <v>90683</v>
       </c>
       <c r="B408" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7446,10 +7452,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90708</v>
+        <v>90705</v>
       </c>
       <c r="B409" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
@@ -7460,10 +7466,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="B410" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7474,24 +7480,24 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90713</v>
+        <v>90708</v>
       </c>
       <c r="B411" t="s">
-        <v>402</v>
+        <v>322</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D411" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>1218</v>
+        <v>90709</v>
       </c>
       <c r="B412" t="s">
-        <v>382</v>
+        <v>323</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7502,24 +7508,24 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B413" s="8" t="s">
-        <v>383</v>
+        <v>90713</v>
+      </c>
+      <c r="B413" t="s">
+        <v>402</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D413" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B414" s="8" t="s">
-        <v>384</v>
+        <v>1218</v>
+      </c>
+      <c r="B414" t="s">
+        <v>382</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7530,10 +7536,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>1817</v>
+        <v>1959</v>
       </c>
       <c r="B415" s="8" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7544,10 +7550,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>5737</v>
+        <v>5625</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7558,108 +7564,108 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>60295</v>
+        <v>1817</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D417" s="9" t="s">
-        <v>9</v>
+      <c r="D417" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B418" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D418" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A419" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B419" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D419" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A420" s="6">
         <v>1045</v>
       </c>
-      <c r="B418" s="8" t="s">
+      <c r="B420" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C418" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D418" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="419" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A419">
+      <c r="C420" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D420" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A421">
         <v>1043</v>
       </c>
-      <c r="B419" t="s">
+      <c r="B421" t="s">
         <v>422</v>
       </c>
-      <c r="C419" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D419" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="420" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A420">
+      <c r="C421" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D421" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A422">
         <v>20340</v>
       </c>
-      <c r="B420" t="s">
+      <c r="B422" t="s">
         <v>423</v>
       </c>
-      <c r="C420" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D420" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="421" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A421">
-        <v>40146</v>
-      </c>
-      <c r="B421" t="s">
-        <v>424</v>
-      </c>
-      <c r="C421" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D421" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A422">
-        <v>60260</v>
-      </c>
-      <c r="B422" t="s">
-        <v>425</v>
-      </c>
-      <c r="C422" s="14" t="s">
+      <c r="C422" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D422" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423">
-        <v>1017</v>
+        <v>40146</v>
       </c>
       <c r="B423" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C423" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D423" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>60300</v>
+        <v>60260</v>
       </c>
       <c r="B424" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C424" s="14" t="s">
         <v>4</v>
@@ -7670,24 +7676,24 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>20191</v>
+        <v>1017</v>
       </c>
       <c r="B425" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C425" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D425" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>20399</v>
+        <v>60300</v>
       </c>
       <c r="B426" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C426" s="14" t="s">
         <v>4</v>
@@ -7698,10 +7704,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>60240</v>
+        <v>20191</v>
       </c>
       <c r="B427" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C427" s="14" t="s">
         <v>4</v>
@@ -7712,10 +7718,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>60244</v>
+        <v>20399</v>
       </c>
       <c r="B428" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
@@ -7726,52 +7732,52 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>60248</v>
+        <v>60240</v>
       </c>
       <c r="B429" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D429" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>60288</v>
+        <v>60244</v>
       </c>
       <c r="B430" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D430" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>90714</v>
+        <v>60248</v>
       </c>
       <c r="B431" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D431" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>1014</v>
+        <v>60288</v>
       </c>
       <c r="B432" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
@@ -7782,24 +7788,24 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>1016</v>
+        <v>90714</v>
       </c>
       <c r="B433" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D433" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>60301</v>
+        <v>1014</v>
       </c>
       <c r="B434" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7810,24 +7816,24 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>1041</v>
+        <v>1016</v>
       </c>
       <c r="B435" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>971</v>
+        <v>60301</v>
       </c>
       <c r="B436" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
@@ -7838,24 +7844,24 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>50610</v>
+        <v>1041</v>
       </c>
       <c r="B437" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>943</v>
+        <v>971</v>
       </c>
       <c r="B438" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
@@ -7866,62 +7872,90 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>20306</v>
+        <v>50610</v>
       </c>
       <c r="B439" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>90630</v>
+        <v>943</v>
       </c>
       <c r="B440" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D440" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>1047</v>
+        <v>20306</v>
       </c>
       <c r="B441" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D441" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
+        <v>90630</v>
+      </c>
+      <c r="B442" t="s">
+        <v>443</v>
+      </c>
+      <c r="C442" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D442" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>1047</v>
+      </c>
+      <c r="B443" t="s">
+        <v>444</v>
+      </c>
+      <c r="C443" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D443" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A444">
         <v>20398</v>
       </c>
-      <c r="B442" t="s">
+      <c r="B444" t="s">
         <v>445</v>
       </c>
-      <c r="C442" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D442" t="s">
+      <c r="C444" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D444" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D418"/>
+  <autoFilter ref="A1:D420"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$420</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -1380,7 +1380,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -6159,7 +6159,7 @@
         <v>4</v>
       </c>
       <c r="D316" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$420</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$421</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="452">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1375,6 +1375,9 @@
   </si>
   <si>
     <t>JOCO OFICINA</t>
+  </si>
+  <si>
+    <t>FERRETERIA UNIVERSO</t>
   </si>
 </sst>
 </file>
@@ -1730,7 +1733,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D444"/>
+  <dimension ref="A1:D445"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3210,24 +3213,24 @@
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>10424</v>
+        <v>10168</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>451</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="17" t="s">
-        <v>9</v>
+      <c r="D106" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
@@ -3238,24 +3241,24 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B108" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="10" t="s">
-        <v>8</v>
+      <c r="D108" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B109" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
@@ -3266,66 +3269,66 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B110" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B111" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>8</v>
+      <c r="D111" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B112" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B113" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B114" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3336,80 +3339,80 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B115" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="D115" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B116" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="13" t="s">
-        <v>5</v>
+      <c r="D117" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B118" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="10" t="s">
-        <v>8</v>
+      <c r="D118" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B119" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B120" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
@@ -3420,10 +3423,10 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B121" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3434,10 +3437,10 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B122" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3448,10 +3451,10 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B123" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
@@ -3462,10 +3465,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B124" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3476,38 +3479,38 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B125" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B126" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B127" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
@@ -3518,52 +3521,52 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B128" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="D128" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B129" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>5</v>
+      <c r="D129" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B130" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="13" t="s">
+      <c r="D130" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B131" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
@@ -3574,24 +3577,24 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B132" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>8</v>
+      <c r="D132" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B133" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
@@ -3602,10 +3605,10 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B134" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
@@ -3616,52 +3619,52 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B135" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="10" t="s">
+      <c r="D135" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B136" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="17" t="s">
-        <v>9</v>
+      <c r="D136" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B137" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="10" t="s">
-        <v>8</v>
+      <c r="D137" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B138" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
@@ -3672,52 +3675,52 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" t="s">
-        <v>9</v>
+      <c r="D139" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B140" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="10" t="s">
-        <v>8</v>
+      <c r="D140" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B141" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B142" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
@@ -3728,38 +3731,38 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B143" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="10" t="s">
+      <c r="D143" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B144" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B145" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
@@ -3770,80 +3773,80 @@
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B146" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" t="s">
-        <v>9</v>
+      <c r="D146" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B147" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="1" t="s">
-        <v>8</v>
+      <c r="D147" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B148" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="14" t="s">
-        <v>5</v>
+      <c r="D148" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B149" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>8</v>
+      <c r="D149" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B150" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="13" t="s">
-        <v>5</v>
+      <c r="D150" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B151" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
@@ -3854,150 +3857,150 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B152" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="10" t="s">
-        <v>8</v>
+      <c r="D152" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B153" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="1" t="s">
-        <v>9</v>
+      <c r="D153" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B154" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="10" t="s">
-        <v>8</v>
+      <c r="D154" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B155" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="D155" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B156" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="10" t="s">
+      <c r="D156" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B157" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="13" t="s">
-        <v>5</v>
+      <c r="D157" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B158" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="10" t="s">
-        <v>8</v>
+      <c r="D158" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B159" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="13" t="s">
-        <v>5</v>
+      <c r="D159" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B160" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="D160" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B161" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="13" t="s">
+      <c r="D161" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B162" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
@@ -4008,24 +4011,24 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B163" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="10" t="s">
-        <v>8</v>
+      <c r="D163" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B164" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
@@ -4036,108 +4039,108 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B165" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="13" t="s">
-        <v>5</v>
+      <c r="D165" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B166" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="10" t="s">
-        <v>8</v>
+      <c r="D166" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B167" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="D167" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B168" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="17" t="s">
-        <v>9</v>
+      <c r="D168" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B169" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>8</v>
+      <c r="D169" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B170" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="13" t="s">
-        <v>5</v>
+      <c r="D170" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B171" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="10" t="s">
-        <v>8</v>
+      <c r="D171" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B172" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
@@ -4148,206 +4151,206 @@
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B173" t="s">
-        <v>401</v>
+        <v>92</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D173" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B174" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="1" t="s">
-        <v>8</v>
+      <c r="D174" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B175" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="13" t="s">
-        <v>5</v>
+      <c r="D175" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B176" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>8</v>
+      <c r="D176" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B177" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="13" t="s">
-        <v>5</v>
+      <c r="D177" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B178" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>8</v>
+      <c r="D178" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B179" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="3" t="s">
-        <v>5</v>
+      <c r="D179" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B180" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="1" t="s">
-        <v>9</v>
+      <c r="D180" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B181" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="17" t="s">
+      <c r="D181" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B182" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="1" t="s">
-        <v>8</v>
+      <c r="D182" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B183" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="3" t="s">
-        <v>5</v>
+      <c r="D183" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B184" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="1" t="s">
-        <v>8</v>
+      <c r="D184" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B185" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="10" t="s">
+      <c r="D185" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B186" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="13" t="s">
-        <v>5</v>
+      <c r="D186" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B187" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
@@ -4358,52 +4361,52 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B188" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="10" t="s">
-        <v>8</v>
+      <c r="D188" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B189" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="13" t="s">
-        <v>5</v>
+      <c r="D189" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B190" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="1" t="s">
-        <v>8</v>
+      <c r="D190" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B191" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4414,10 +4417,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B192" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
@@ -4428,10 +4431,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B193" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4442,24 +4445,24 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B194" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="13" t="s">
-        <v>5</v>
+      <c r="D194" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B195" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
@@ -4470,52 +4473,52 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B196" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="1" t="s">
-        <v>8</v>
+      <c r="D196" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B197" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="10" t="s">
+      <c r="D197" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B198" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="D198" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B199" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
@@ -4526,10 +4529,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B200" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4540,38 +4543,38 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B201" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="13" t="s">
-        <v>5</v>
+      <c r="D201" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B202" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="1" t="s">
-        <v>8</v>
+      <c r="D202" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B203" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
@@ -4582,10 +4585,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B204" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4596,66 +4599,66 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B205" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="13" t="s">
-        <v>5</v>
+      <c r="D205" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B206" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="1" t="s">
-        <v>8</v>
+      <c r="D206" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B207" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="13" t="s">
-        <v>5</v>
+      <c r="D207" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B208" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="10" t="s">
-        <v>8</v>
+      <c r="D208" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B209" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
@@ -4666,38 +4669,38 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B210" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="13" t="s">
-        <v>5</v>
+      <c r="D210" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B211" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="1" t="s">
-        <v>8</v>
+      <c r="D211" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B212" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
@@ -4708,10 +4711,10 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B213" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
@@ -4722,10 +4725,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B214" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4736,52 +4739,52 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B215" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="10" t="s">
+      <c r="D215" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B216" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="D216" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B217" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="10" t="s">
+      <c r="D217" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B218" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
@@ -4792,66 +4795,66 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B219" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="13" t="s">
-        <v>5</v>
+      <c r="D219" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B220" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="1" t="s">
-        <v>8</v>
+      <c r="D220" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B221" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="10" t="s">
+      <c r="D221" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B222" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="D222" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B223" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
@@ -4862,66 +4865,66 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B224" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="10" t="s">
+      <c r="D224" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B225" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="D225" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B226" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="10" t="s">
+      <c r="D226" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B227" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="D227" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B228" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
@@ -4932,52 +4935,52 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B229" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B229" t="s">
+        <v>330</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="11" t="s">
-        <v>5</v>
+      <c r="D229" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B230" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B230" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="1" t="s">
-        <v>8</v>
+      <c r="D230" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B231" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="13" t="s">
-        <v>5</v>
+      <c r="D231" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B232" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
@@ -4988,24 +4991,24 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B233" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="1" t="s">
-        <v>8</v>
+      <c r="D233" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B234" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
@@ -5016,24 +5019,24 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B235" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="10" t="s">
+      <c r="D235" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B236" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
@@ -5044,66 +5047,66 @@
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B237" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="1" t="s">
+      <c r="D237" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B238" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="13" t="s">
-        <v>5</v>
+      <c r="D238" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B239" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="10" t="s">
-        <v>8</v>
+      <c r="D239" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B240" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="13" t="s">
-        <v>5</v>
+      <c r="D240" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B241" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
@@ -5114,206 +5117,206 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B242" t="s">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="19" t="s">
-        <v>8</v>
+      <c r="D242" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B243" t="s">
-        <v>221</v>
+        <v>405</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="10" t="s">
+      <c r="D243" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B244" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="1" t="s">
+      <c r="D244" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B245" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="13" t="s">
-        <v>5</v>
+      <c r="D245" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B246" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="1" t="s">
-        <v>8</v>
+      <c r="D246" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B247" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="10" t="s">
+      <c r="D247" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B248" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="3" t="s">
-        <v>5</v>
+      <c r="D248" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B249" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>8</v>
+      <c r="D249" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B250" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="11" t="s">
-        <v>5</v>
+      <c r="D250" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B251" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="13" t="s">
+      <c r="D251" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B252" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>8</v>
+      <c r="D252" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B253" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B253" t="s">
+        <v>177</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="14" t="s">
+      <c r="D253" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B254" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="16" t="s">
+      <c r="D254" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B255" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="10" t="s">
+      <c r="D255" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B256" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
@@ -5324,94 +5327,94 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B257" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="1" t="s">
-        <v>5</v>
+      <c r="D257" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B258" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="14" t="s">
-        <v>8</v>
+      <c r="D258" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B259" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="1" t="s">
+      <c r="D259" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B260" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="10" t="s">
+      <c r="D260" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B261" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="1" t="s">
+      <c r="D261" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B262" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="13" t="s">
-        <v>5</v>
+      <c r="D262" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B263" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
@@ -5422,24 +5425,24 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B264" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="1" t="s">
-        <v>8</v>
+      <c r="D264" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B265" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
@@ -5450,80 +5453,80 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B266" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="17" t="s">
-        <v>9</v>
+      <c r="D266" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B267" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="10" t="s">
-        <v>8</v>
+      <c r="D267" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B268" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="1" t="s">
+      <c r="D268" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B269" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="13" t="s">
-        <v>5</v>
+      <c r="D269" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B270" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="10" t="s">
-        <v>8</v>
+      <c r="D270" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B271" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
@@ -5534,66 +5537,66 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B272" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="1" t="s">
+      <c r="D272" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B273" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="17" t="s">
-        <v>9</v>
+      <c r="D273" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B274" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="13" t="s">
-        <v>5</v>
+      <c r="D274" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B275" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="10" t="s">
-        <v>8</v>
+      <c r="D275" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B276" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
@@ -5604,24 +5607,24 @@
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B277" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="1" t="s">
+      <c r="D277" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B278" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
@@ -5632,136 +5635,136 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B279" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="11" t="s">
+      <c r="D279" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B280" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B281" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B281" t="s">
+        <v>351</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D281" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D283" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>50231</v>
+        <v>50230</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>421</v>
+        <v>379</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B285" t="s">
-        <v>237</v>
+        <v>50231</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>421</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="13" t="s">
-        <v>5</v>
+      <c r="D285" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B286" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="11" t="s">
-        <v>9</v>
+      <c r="D286" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B287" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="13" t="s">
-        <v>5</v>
+      <c r="D287" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B288" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5772,80 +5775,80 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B289" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="10" t="s">
-        <v>8</v>
+      <c r="D289" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B290" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="3" t="s">
-        <v>5</v>
+      <c r="D290" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B291" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="1" t="s">
-        <v>8</v>
+      <c r="D291" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B292" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="13" t="s">
-        <v>5</v>
+      <c r="D292" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B293" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="1" t="s">
-        <v>8</v>
+      <c r="D293" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B294" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
@@ -5856,10 +5859,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B295" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5870,10 +5873,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B296" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5884,10 +5887,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B297" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5898,10 +5901,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B298" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5912,66 +5915,66 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B299" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="13" t="s">
-        <v>5</v>
+      <c r="D299" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B300" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="10" t="s">
-        <v>8</v>
+      <c r="D300" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B301" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="1" t="s">
+      <c r="D301" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B302" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="13" t="s">
-        <v>5</v>
+      <c r="D302" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B303" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -5982,24 +5985,24 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B304" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="1" t="s">
-        <v>8</v>
+      <c r="D304" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B305" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -6010,52 +6013,52 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B306" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B306" t="s">
+        <v>255</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="11" t="s">
-        <v>5</v>
+      <c r="D306" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B307" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="1" t="s">
-        <v>8</v>
+      <c r="D307" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B308" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="13" t="s">
-        <v>5</v>
+      <c r="D308" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B309" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -6066,52 +6069,52 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B310" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="1" t="s">
-        <v>8</v>
+      <c r="D310" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B311" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="10" t="s">
+      <c r="D311" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B312" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="1" t="s">
+      <c r="D312" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B313" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -6122,24 +6125,24 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B314" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="10" t="s">
+      <c r="D314" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B315" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
@@ -6150,38 +6153,38 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B316" s="18" t="s">
-        <v>410</v>
+        <v>60192</v>
+      </c>
+      <c r="B316" t="s">
+        <v>264</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D316" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B317" t="s">
-        <v>265</v>
+        <v>60194</v>
+      </c>
+      <c r="B317" s="18" t="s">
+        <v>410</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B318" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
@@ -6192,10 +6195,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B319" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
@@ -6206,52 +6209,52 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B320" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" t="s">
-        <v>9</v>
+      <c r="D320" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B321" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="13" t="s">
-        <v>5</v>
+      <c r="D321" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B322" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="1" t="s">
-        <v>8</v>
+      <c r="D322" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B323" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
@@ -6262,10 +6265,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B324" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
@@ -6276,192 +6279,192 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B325" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="10" t="s">
+      <c r="D325" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B326" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="1" t="s">
+      <c r="D326" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B327" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="10" t="s">
+      <c r="D327" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B328" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D328" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B329" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D329" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B330" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="1" t="s">
+      <c r="D330" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B331" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="10" t="s">
-        <v>5</v>
+      <c r="D331" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B332" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="17" t="s">
-        <v>9</v>
+      <c r="D332" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B333" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="10" t="s">
-        <v>8</v>
+      <c r="D333" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B334" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B334" t="s">
+        <v>280</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="7" t="s">
-        <v>9</v>
+      <c r="D334" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D335" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D336" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D337" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
@@ -6472,10 +6475,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60247</v>
+        <v>60246</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>448</v>
+        <v>407</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
@@ -6486,10 +6489,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B340" s="18" t="s">
-        <v>408</v>
+        <v>60247</v>
+      </c>
+      <c r="B340" s="8" t="s">
+        <v>448</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6500,38 +6503,38 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B341" s="8" t="s">
-        <v>339</v>
+        <v>60249</v>
+      </c>
+      <c r="B341" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="11" t="s">
-        <v>8</v>
+      <c r="D341" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B342" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B342" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="1" t="s">
+      <c r="D342" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B343" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6542,94 +6545,94 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B344" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B345" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B346" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B346" t="s">
+        <v>284</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="11" t="s">
+      <c r="D346" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B347" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B347" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="10" t="s">
+      <c r="D347" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B348" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="1" t="s">
-        <v>9</v>
+      <c r="D348" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B349" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B350" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6640,10 +6643,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B351" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6654,10 +6657,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B352" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6668,38 +6671,38 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B353" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="13" t="s">
+      <c r="D353" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B354" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="1" t="s">
-        <v>5</v>
+      <c r="D354" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B355" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6710,66 +6713,66 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B356" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B356" t="s">
+        <v>292</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="11" t="s">
-        <v>9</v>
+      <c r="D356" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D357" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B358" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B358" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="1" t="s">
-        <v>8</v>
+      <c r="D358" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B359" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B359" t="s">
+        <v>378</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="9" t="s">
-        <v>5</v>
+      <c r="D359" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
@@ -6780,10 +6783,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6794,52 +6797,52 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B362" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B362" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="12" t="s">
+      <c r="D362" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B363" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B364" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D364" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B365" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6850,10 +6853,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B366" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B366" t="s">
+        <v>376</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6864,10 +6867,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60293</v>
+        <v>60292</v>
       </c>
       <c r="B367" s="18" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6878,10 +6881,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B368" t="s">
-        <v>391</v>
+        <v>60293</v>
+      </c>
+      <c r="B368" s="18" t="s">
+        <v>418</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6892,10 +6895,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B369" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6906,10 +6909,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B370" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6920,10 +6923,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B371" s="18" t="s">
-        <v>411</v>
+        <v>60299</v>
+      </c>
+      <c r="B371" t="s">
+        <v>388</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6934,10 +6937,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B372" s="18" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6948,10 +6951,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>60305</v>
+        <v>60303</v>
       </c>
       <c r="B373" s="18" t="s">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6962,38 +6965,38 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B374" t="s">
-        <v>403</v>
+        <v>60305</v>
+      </c>
+      <c r="B374" s="18" t="s">
+        <v>446</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D374" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B375" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="15" t="s">
-        <v>5</v>
+      <c r="D375" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B376" t="s">
-        <v>415</v>
+        <v>293</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -7004,24 +7007,24 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B377" t="s">
-        <v>294</v>
+        <v>415</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="12" t="s">
-        <v>8</v>
+      <c r="D377" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B378" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -7032,10 +7035,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B379" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -7046,10 +7049,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B380" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -7060,52 +7063,52 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B381" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="15" t="s">
-        <v>5</v>
+      <c r="D381" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B382" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="12" t="s">
-        <v>8</v>
+      <c r="D382" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B383" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="15" t="s">
-        <v>5</v>
+      <c r="D383" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B384" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7116,94 +7119,94 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B385" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="12" t="s">
-        <v>8</v>
+      <c r="D385" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B386" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="15" t="s">
-        <v>5</v>
+      <c r="D386" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B387" t="s">
-        <v>419</v>
+        <v>303</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D387" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B388" t="s">
-        <v>304</v>
+        <v>419</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="12" t="s">
+      <c r="D388" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B389" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="15" t="s">
-        <v>5</v>
+      <c r="D389" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B390" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D390" s="9" t="s">
-        <v>9</v>
+      <c r="D390" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B391" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7214,38 +7217,38 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B392" t="s">
-        <v>420</v>
+        <v>331</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D392" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70638</v>
+        <v>70116</v>
       </c>
       <c r="B393" t="s">
-        <v>306</v>
+        <v>420</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D393" s="12" t="s">
+      <c r="D393" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B394" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7256,10 +7259,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B395" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7270,10 +7273,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B396" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7284,10 +7287,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B397" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7298,10 +7301,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B398" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7312,52 +7315,52 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B399" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D399" s="15" t="s">
-        <v>5</v>
+      <c r="D399" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B400" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D400" s="12" t="s">
-        <v>8</v>
+      <c r="D400" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B401" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D401" s="9" t="s">
-        <v>5</v>
+      <c r="D401" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B402" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B402" t="s">
+        <v>333</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7368,24 +7371,24 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B403" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B403" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D403" s="12" t="s">
-        <v>8</v>
+      <c r="D403" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B404" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7396,10 +7399,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B405" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7410,10 +7413,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B406" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7424,10 +7427,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B407" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7438,10 +7441,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B408" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7452,10 +7455,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B409" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
@@ -7466,10 +7469,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B410" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7480,10 +7483,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B411" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7494,10 +7497,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B412" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7508,38 +7511,38 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B413" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D413" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B414" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D414" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B415" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B415" t="s">
+        <v>382</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7550,10 +7553,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7564,10 +7567,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
@@ -7578,10 +7581,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B418" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
@@ -7592,68 +7595,68 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D419" s="9" t="s">
-        <v>9</v>
+      <c r="D419" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B420" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D420" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A421" s="6">
         <v>1045</v>
       </c>
-      <c r="B420" s="8" t="s">
+      <c r="B421" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C420" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D420" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="421" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A421">
-        <v>1043</v>
-      </c>
-      <c r="B421" t="s">
-        <v>422</v>
-      </c>
-      <c r="C421" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D421" t="s">
-        <v>8</v>
+      <c r="C421" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D421" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422">
+        <v>1043</v>
+      </c>
+      <c r="B422" t="s">
+        <v>422</v>
+      </c>
+      <c r="C422" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D422" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A423">
         <v>20340</v>
       </c>
-      <c r="B422" t="s">
+      <c r="B423" t="s">
         <v>423</v>
       </c>
-      <c r="C422" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D422" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A423">
-        <v>40146</v>
-      </c>
-      <c r="B423" t="s">
-        <v>424</v>
-      </c>
-      <c r="C423" s="14" t="s">
+      <c r="C423" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D423" t="s">
@@ -7662,24 +7665,24 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B424" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C424" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D424" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B425" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C425" s="14" t="s">
         <v>4</v>
@@ -7690,10 +7693,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B426" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C426" s="14" t="s">
         <v>4</v>
@@ -7704,66 +7707,66 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B427" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C427" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D427" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B428" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D428" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B429" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D429" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B430" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D430" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B431" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
@@ -7774,24 +7777,24 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B432" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B433" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
@@ -7802,10 +7805,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B434" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7816,38 +7819,38 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B435" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B436" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B437" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
@@ -7858,10 +7861,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B438" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
@@ -7872,38 +7875,38 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B439" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B440" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D440" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B441" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7914,24 +7917,24 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B442" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B443" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
@@ -7942,20 +7945,34 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
+        <v>1047</v>
+      </c>
+      <c r="B444" t="s">
+        <v>444</v>
+      </c>
+      <c r="C444" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D444" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A445">
         <v>20398</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B445" t="s">
         <v>445</v>
       </c>
-      <c r="C444" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D444" t="s">
+      <c r="C445" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D445" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D420"/>
+  <autoFilter ref="A1:D421"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$421</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$445</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
@@ -168,9 +168,6 @@
     <t>LEONARDO FERRETERIA</t>
   </si>
   <si>
-    <t>ALEJANDRO (KM 44)</t>
-  </si>
-  <si>
     <t>NUNE FERRETERIA</t>
   </si>
   <si>
@@ -261,9 +258,6 @@
     <t>LOS 22 FERRETERIA</t>
   </si>
   <si>
-    <t>CABOT CORRALON d/MAT.</t>
-  </si>
-  <si>
     <t>LA HERRADURA FERRETERIA</t>
   </si>
   <si>
@@ -330,9 +324,6 @@
     <t>LU-MI FERRETERIA</t>
   </si>
   <si>
-    <t>ROMA'S FERRETERIA</t>
-  </si>
-  <si>
     <t>CONSTRUCTORA SYS SA</t>
   </si>
   <si>
@@ -405,9 +396,6 @@
     <t>CASA GABY CERAMICA</t>
   </si>
   <si>
-    <t>FERRETERIA LUIS ROLDAN</t>
-  </si>
-  <si>
     <t>EL 44 FERRETERIA</t>
   </si>
   <si>
@@ -570,9 +558,6 @@
     <t>CORRALON IBERA</t>
   </si>
   <si>
-    <t>CORRADO AGUSTINA</t>
-  </si>
-  <si>
     <t>ITATI CORRALON</t>
   </si>
   <si>
@@ -876,9 +861,6 @@
     <t>FERRETERIA EL PAISA</t>
   </si>
   <si>
-    <t>FERRETERIA MIGUEL</t>
-  </si>
-  <si>
     <t>FERRETERIA MAKANA</t>
   </si>
   <si>
@@ -1074,18 +1056,12 @@
     <t>LAS 3 HERMANAS</t>
   </si>
   <si>
-    <t>FERRETERIA MATEO</t>
-  </si>
-  <si>
     <t>FERRETERIA MYM</t>
   </si>
   <si>
     <t>FERRETERIA LOCK</t>
   </si>
   <si>
-    <t>FERRETERIA ML 2</t>
-  </si>
-  <si>
     <t>FERRETERIA ALAN</t>
   </si>
   <si>
@@ -1167,9 +1143,6 @@
     <t>ELECTRICA LOLY</t>
   </si>
   <si>
-    <t>MANOLO FERRETERIA</t>
-  </si>
-  <si>
     <t>ROBERTO FERRIN</t>
   </si>
   <si>
@@ -1251,9 +1224,6 @@
     <t>FERRETERIA GUATEMALA</t>
   </si>
   <si>
-    <t>FERRETERIA BM</t>
-  </si>
-  <si>
     <t>EL BUHO FERRETERIA</t>
   </si>
   <si>
@@ -1378,12 +1348,42 @@
   </si>
   <si>
     <t>FERRETERIA UNIVERSO</t>
+  </si>
+  <si>
+    <t>UNIMOK (MANOLO)</t>
+  </si>
+  <si>
+    <t>COR.CORRADO AGUSTINA</t>
+  </si>
+  <si>
+    <t>FERRETERIA MUJICA</t>
+  </si>
+  <si>
+    <t>FERRETERIA MAGNASCO</t>
+  </si>
+  <si>
+    <t>FERRETERIA SENILLOSA</t>
+  </si>
+  <si>
+    <t>FERRETERIA LAURA</t>
+  </si>
+  <si>
+    <t>FERRETERIA VILLARUBIA</t>
+  </si>
+  <si>
+    <t>FERRETERIA IMPERIO</t>
+  </si>
+  <si>
+    <t>COR. DE MAT. CABOT</t>
+  </si>
+  <si>
+    <t>FERRETERIA CLAUDIO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1760,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -1774,7 +1774,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -1788,7 +1788,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1802,7 +1802,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -1816,7 +1816,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -1830,7 +1830,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -1844,7 +1844,7 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -1872,7 +1872,7 @@
         <v>233</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>449</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1886,7 +1886,7 @@
         <v>237</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1900,7 +1900,7 @@
         <v>246</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1928,7 +1928,7 @@
         <v>265</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1956,7 +1956,7 @@
         <v>916</v>
       </c>
       <c r="B16" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1970,7 +1970,7 @@
         <v>920</v>
       </c>
       <c r="B17" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -1984,7 +1984,7 @@
         <v>921</v>
       </c>
       <c r="B18" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1998,7 +1998,7 @@
         <v>933</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -2012,7 +2012,7 @@
         <v>936</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -2026,7 +2026,7 @@
         <v>938</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -2054,7 +2054,7 @@
         <v>940</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -2082,7 +2082,7 @@
         <v>947</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -2124,7 +2124,7 @@
         <v>951</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -2138,7 +2138,7 @@
         <v>952</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -2152,7 +2152,7 @@
         <v>954</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -2166,7 +2166,7 @@
         <v>955</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>448</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -2180,7 +2180,7 @@
         <v>956</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -2208,7 +2208,7 @@
         <v>961</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -2222,7 +2222,7 @@
         <v>962</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -2264,7 +2264,7 @@
         <v>969</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -2278,7 +2278,7 @@
         <v>970</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -2292,7 +2292,7 @@
         <v>972</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -2306,7 +2306,7 @@
         <v>973</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -2320,7 +2320,7 @@
         <v>974</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -2334,7 +2334,7 @@
         <v>980</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -2348,7 +2348,7 @@
         <v>982</v>
       </c>
       <c r="B44" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -2362,7 +2362,7 @@
         <v>987</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -2376,7 +2376,7 @@
         <v>989</v>
       </c>
       <c r="B46" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -2390,7 +2390,7 @@
         <v>990</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -2404,7 +2404,7 @@
         <v>991</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -2418,7 +2418,7 @@
         <v>992</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -2432,7 +2432,7 @@
         <v>993</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -2446,7 +2446,7 @@
         <v>994</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -2474,7 +2474,7 @@
         <v>998</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -2488,7 +2488,7 @@
         <v>999</v>
       </c>
       <c r="B54" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -2502,7 +2502,7 @@
         <v>1000</v>
       </c>
       <c r="B55" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -2516,7 +2516,7 @@
         <v>1001</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -2544,7 +2544,7 @@
         <v>1005</v>
       </c>
       <c r="B58" t="s">
-        <v>182</v>
+        <v>443</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
@@ -2558,7 +2558,7 @@
         <v>1006</v>
       </c>
       <c r="B59" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -2572,7 +2572,7 @@
         <v>1007</v>
       </c>
       <c r="B60" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
@@ -2586,7 +2586,7 @@
         <v>1009</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
@@ -2600,7 +2600,7 @@
         <v>1010</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
@@ -2614,7 +2614,7 @@
         <v>1012</v>
       </c>
       <c r="B63" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
@@ -2628,7 +2628,7 @@
         <v>1013</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
@@ -2656,7 +2656,7 @@
         <v>1018</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
@@ -2670,7 +2670,7 @@
         <v>1020</v>
       </c>
       <c r="B67" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
@@ -2684,7 +2684,7 @@
         <v>1021</v>
       </c>
       <c r="B68" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
@@ -2698,7 +2698,7 @@
         <v>1023</v>
       </c>
       <c r="B69" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
@@ -2712,7 +2712,7 @@
         <v>1024</v>
       </c>
       <c r="B70" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
@@ -2726,7 +2726,7 @@
         <v>1025</v>
       </c>
       <c r="B71" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
@@ -2740,7 +2740,7 @@
         <v>1026</v>
       </c>
       <c r="B72" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
@@ -2754,7 +2754,7 @@
         <v>1027</v>
       </c>
       <c r="B73" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
@@ -2768,7 +2768,7 @@
         <v>1028</v>
       </c>
       <c r="B74" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
@@ -2782,7 +2782,7 @@
         <v>1029</v>
       </c>
       <c r="B75" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
@@ -2796,7 +2796,7 @@
         <v>1030</v>
       </c>
       <c r="B76" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
@@ -2810,7 +2810,7 @@
         <v>1031</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
@@ -2824,7 +2824,7 @@
         <v>1032</v>
       </c>
       <c r="B78" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
@@ -2838,7 +2838,7 @@
         <v>1033</v>
       </c>
       <c r="B79" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
@@ -2852,7 +2852,7 @@
         <v>1034</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
@@ -2866,7 +2866,7 @@
         <v>1035</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
@@ -2880,7 +2880,7 @@
         <v>1036</v>
       </c>
       <c r="B82" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
@@ -2894,7 +2894,7 @@
         <v>1037</v>
       </c>
       <c r="B83" t="s">
-        <v>353</v>
+        <v>447</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
@@ -2908,7 +2908,7 @@
         <v>1038</v>
       </c>
       <c r="B84" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
@@ -2922,7 +2922,7 @@
         <v>1039</v>
       </c>
       <c r="B85" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
@@ -2936,7 +2936,7 @@
         <v>1040</v>
       </c>
       <c r="B86" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
@@ -2950,7 +2950,7 @@
         <v>1044</v>
       </c>
       <c r="B87" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
@@ -2964,7 +2964,7 @@
         <v>1046</v>
       </c>
       <c r="B88" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
@@ -2978,7 +2978,7 @@
         <v>1048</v>
       </c>
       <c r="B89" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
@@ -2992,7 +2992,7 @@
         <v>1049</v>
       </c>
       <c r="B90" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
@@ -3006,7 +3006,7 @@
         <v>1050</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
@@ -3020,7 +3020,7 @@
         <v>1051</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
@@ -3034,7 +3034,7 @@
         <v>1416</v>
       </c>
       <c r="B93" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
@@ -3048,7 +3048,7 @@
         <v>1987</v>
       </c>
       <c r="B94" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
@@ -3062,7 +3062,7 @@
         <v>1988</v>
       </c>
       <c r="B95" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
@@ -3076,7 +3076,7 @@
         <v>10107</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
@@ -3090,7 +3090,7 @@
         <v>10137</v>
       </c>
       <c r="B97" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
@@ -3104,7 +3104,7 @@
         <v>10157</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
@@ -3118,7 +3118,7 @@
         <v>10158</v>
       </c>
       <c r="B99" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
@@ -3132,7 +3132,7 @@
         <v>10160</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
@@ -3146,7 +3146,7 @@
         <v>10162</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
@@ -3160,7 +3160,7 @@
         <v>10163</v>
       </c>
       <c r="B102" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
@@ -3188,7 +3188,7 @@
         <v>10166</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
@@ -3216,7 +3216,7 @@
         <v>10168</v>
       </c>
       <c r="B106" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
@@ -3258,7 +3258,7 @@
         <v>20094</v>
       </c>
       <c r="B109" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
@@ -3272,7 +3272,7 @@
         <v>20095</v>
       </c>
       <c r="B110" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
@@ -3286,7 +3286,7 @@
         <v>20096</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3300,7 +3300,7 @@
         <v>20100</v>
       </c>
       <c r="B112" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
@@ -3328,7 +3328,7 @@
         <v>20103</v>
       </c>
       <c r="B114" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3342,7 +3342,7 @@
         <v>20106</v>
       </c>
       <c r="B115" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
@@ -3356,7 +3356,7 @@
         <v>20108</v>
       </c>
       <c r="B116" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
@@ -3370,7 +3370,7 @@
         <v>20109</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
@@ -3398,7 +3398,7 @@
         <v>20113</v>
       </c>
       <c r="B119" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
@@ -3412,7 +3412,7 @@
         <v>20114</v>
       </c>
       <c r="B120" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
@@ -3426,7 +3426,7 @@
         <v>20116</v>
       </c>
       <c r="B121" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3440,7 +3440,7 @@
         <v>20117</v>
       </c>
       <c r="B122" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3454,7 +3454,7 @@
         <v>20118</v>
       </c>
       <c r="B123" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
@@ -3468,7 +3468,7 @@
         <v>20120</v>
       </c>
       <c r="B124" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3482,7 +3482,7 @@
         <v>20121</v>
       </c>
       <c r="B125" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3496,7 +3496,7 @@
         <v>20125</v>
       </c>
       <c r="B126" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
@@ -3510,7 +3510,7 @@
         <v>20127</v>
       </c>
       <c r="B127" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
@@ -3524,7 +3524,7 @@
         <v>20128</v>
       </c>
       <c r="B128" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
@@ -3538,7 +3538,7 @@
         <v>20129</v>
       </c>
       <c r="B129" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
@@ -3552,7 +3552,7 @@
         <v>20137</v>
       </c>
       <c r="B130" t="s">
-        <v>79</v>
+        <v>450</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
@@ -3566,7 +3566,7 @@
         <v>20138</v>
       </c>
       <c r="B131" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
@@ -3580,7 +3580,7 @@
         <v>20140</v>
       </c>
       <c r="B132" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
@@ -3594,7 +3594,7 @@
         <v>20142</v>
       </c>
       <c r="B133" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
@@ -3608,7 +3608,7 @@
         <v>20146</v>
       </c>
       <c r="B134" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
@@ -3636,7 +3636,7 @@
         <v>20156</v>
       </c>
       <c r="B136" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
@@ -3650,7 +3650,7 @@
         <v>20159</v>
       </c>
       <c r="B137" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
@@ -3664,7 +3664,7 @@
         <v>20160</v>
       </c>
       <c r="B138" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
@@ -3706,7 +3706,7 @@
         <v>20165</v>
       </c>
       <c r="B141" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
@@ -3720,7 +3720,7 @@
         <v>20166</v>
       </c>
       <c r="B142" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
@@ -3734,7 +3734,7 @@
         <v>20169</v>
       </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
@@ -3748,7 +3748,7 @@
         <v>20173</v>
       </c>
       <c r="B144" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
@@ -3762,7 +3762,7 @@
         <v>20174</v>
       </c>
       <c r="B145" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
@@ -3776,7 +3776,7 @@
         <v>20178</v>
       </c>
       <c r="B146" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
@@ -3790,7 +3790,7 @@
         <v>20179</v>
       </c>
       <c r="B147" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
@@ -3804,7 +3804,7 @@
         <v>20180</v>
       </c>
       <c r="B148" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
@@ -3818,7 +3818,7 @@
         <v>20183</v>
       </c>
       <c r="B149" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
@@ -3832,7 +3832,7 @@
         <v>20189</v>
       </c>
       <c r="B150" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
@@ -3846,7 +3846,7 @@
         <v>20200</v>
       </c>
       <c r="B151" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
@@ -3860,7 +3860,7 @@
         <v>20201</v>
       </c>
       <c r="B152" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
@@ -3874,7 +3874,7 @@
         <v>20204</v>
       </c>
       <c r="B153" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
@@ -3888,7 +3888,7 @@
         <v>20205</v>
       </c>
       <c r="B154" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
@@ -3902,7 +3902,7 @@
         <v>20211</v>
       </c>
       <c r="B155" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
@@ -3916,7 +3916,7 @@
         <v>20224</v>
       </c>
       <c r="B156" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
@@ -3930,7 +3930,7 @@
         <v>20227</v>
       </c>
       <c r="B157" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
@@ -3944,7 +3944,7 @@
         <v>20228</v>
       </c>
       <c r="B158" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
@@ -3958,7 +3958,7 @@
         <v>20230</v>
       </c>
       <c r="B159" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
@@ -4000,7 +4000,7 @@
         <v>20238</v>
       </c>
       <c r="B162" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
@@ -4028,7 +4028,7 @@
         <v>20242</v>
       </c>
       <c r="B164" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
@@ -4042,7 +4042,7 @@
         <v>20244</v>
       </c>
       <c r="B165" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
@@ -4070,7 +4070,7 @@
         <v>20249</v>
       </c>
       <c r="B167" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
@@ -4084,7 +4084,7 @@
         <v>20256</v>
       </c>
       <c r="B168" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
@@ -4098,7 +4098,7 @@
         <v>20257</v>
       </c>
       <c r="B169" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
@@ -4112,7 +4112,7 @@
         <v>20258</v>
       </c>
       <c r="B170" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
@@ -4126,7 +4126,7 @@
         <v>20260</v>
       </c>
       <c r="B171" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
@@ -4140,7 +4140,7 @@
         <v>20261</v>
       </c>
       <c r="B172" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
@@ -4154,7 +4154,7 @@
         <v>20262</v>
       </c>
       <c r="B173" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
@@ -4168,7 +4168,7 @@
         <v>20267</v>
       </c>
       <c r="B174" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
@@ -4182,7 +4182,7 @@
         <v>20268</v>
       </c>
       <c r="B175" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
@@ -4210,7 +4210,7 @@
         <v>20272</v>
       </c>
       <c r="B177" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
@@ -4224,7 +4224,7 @@
         <v>20275</v>
       </c>
       <c r="B178" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
@@ -4238,7 +4238,7 @@
         <v>20277</v>
       </c>
       <c r="B179" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
@@ -4252,7 +4252,7 @@
         <v>20281</v>
       </c>
       <c r="B180" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
@@ -4266,7 +4266,7 @@
         <v>20282</v>
       </c>
       <c r="B181" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
@@ -4294,7 +4294,7 @@
         <v>20285</v>
       </c>
       <c r="B183" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
@@ -4308,7 +4308,7 @@
         <v>20289</v>
       </c>
       <c r="B184" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
@@ -4322,7 +4322,7 @@
         <v>20290</v>
       </c>
       <c r="B185" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
@@ -4336,7 +4336,7 @@
         <v>20291</v>
       </c>
       <c r="B186" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
@@ -4378,7 +4378,7 @@
         <v>20294</v>
       </c>
       <c r="B189" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
@@ -4392,7 +4392,7 @@
         <v>20296</v>
       </c>
       <c r="B190" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4406,7 +4406,7 @@
         <v>20298</v>
       </c>
       <c r="B191" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4420,7 +4420,7 @@
         <v>20299</v>
       </c>
       <c r="B192" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
@@ -4434,7 +4434,7 @@
         <v>20301</v>
       </c>
       <c r="B193" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4476,7 +4476,7 @@
         <v>20310</v>
       </c>
       <c r="B196" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4490,7 +4490,7 @@
         <v>20318</v>
       </c>
       <c r="B197" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4504,7 +4504,7 @@
         <v>20319</v>
       </c>
       <c r="B198" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
@@ -4518,7 +4518,7 @@
         <v>20320</v>
       </c>
       <c r="B199" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
@@ -4532,7 +4532,7 @@
         <v>20324</v>
       </c>
       <c r="B200" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4546,7 +4546,7 @@
         <v>20331</v>
       </c>
       <c r="B201" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4560,7 +4560,7 @@
         <v>20333</v>
       </c>
       <c r="B202" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4574,7 +4574,7 @@
         <v>20337</v>
       </c>
       <c r="B203" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
@@ -4588,7 +4588,7 @@
         <v>20343</v>
       </c>
       <c r="B204" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4602,7 +4602,7 @@
         <v>20344</v>
       </c>
       <c r="B205" t="s">
-        <v>127</v>
+        <v>445</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
@@ -4630,7 +4630,7 @@
         <v>20357</v>
       </c>
       <c r="B207" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
@@ -4644,7 +4644,7 @@
         <v>20361</v>
       </c>
       <c r="B208" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
@@ -4672,7 +4672,7 @@
         <v>20363</v>
       </c>
       <c r="B210" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
@@ -4686,7 +4686,7 @@
         <v>20364</v>
       </c>
       <c r="B211" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
@@ -4700,7 +4700,7 @@
         <v>20366</v>
       </c>
       <c r="B212" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
@@ -4728,7 +4728,7 @@
         <v>20369</v>
       </c>
       <c r="B214" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4742,7 +4742,7 @@
         <v>20371</v>
       </c>
       <c r="B215" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4756,7 +4756,7 @@
         <v>20372</v>
       </c>
       <c r="B216" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
@@ -4770,7 +4770,7 @@
         <v>20374</v>
       </c>
       <c r="B217" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
@@ -4784,7 +4784,7 @@
         <v>20377</v>
       </c>
       <c r="B218" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
@@ -4798,7 +4798,7 @@
         <v>20379</v>
       </c>
       <c r="B219" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
@@ -4826,7 +4826,7 @@
         <v>20381</v>
       </c>
       <c r="B221" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
@@ -4840,7 +4840,7 @@
         <v>20384</v>
       </c>
       <c r="B222" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
@@ -4868,7 +4868,7 @@
         <v>20386</v>
       </c>
       <c r="B224" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
@@ -4882,7 +4882,7 @@
         <v>20388</v>
       </c>
       <c r="B225" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
@@ -4896,7 +4896,7 @@
         <v>20391</v>
       </c>
       <c r="B226" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
@@ -4910,7 +4910,7 @@
         <v>20394</v>
       </c>
       <c r="B227" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
@@ -4924,7 +4924,7 @@
         <v>20395</v>
       </c>
       <c r="B228" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
@@ -4938,7 +4938,7 @@
         <v>20396</v>
       </c>
       <c r="B229" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
@@ -4952,7 +4952,7 @@
         <v>20397</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
@@ -4966,7 +4966,7 @@
         <v>30101</v>
       </c>
       <c r="B231" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
@@ -4994,7 +4994,7 @@
         <v>40125</v>
       </c>
       <c r="B233" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
@@ -5008,7 +5008,7 @@
         <v>40127</v>
       </c>
       <c r="B234" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
@@ -5022,7 +5022,7 @@
         <v>40129</v>
       </c>
       <c r="B235" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
@@ -5036,7 +5036,7 @@
         <v>40137</v>
       </c>
       <c r="B236" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
@@ -5050,7 +5050,7 @@
         <v>40139</v>
       </c>
       <c r="B237" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
@@ -5064,7 +5064,7 @@
         <v>40140</v>
       </c>
       <c r="B238" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
@@ -5078,7 +5078,7 @@
         <v>40141</v>
       </c>
       <c r="B239" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
@@ -5092,7 +5092,7 @@
         <v>40143</v>
       </c>
       <c r="B240" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
@@ -5106,7 +5106,7 @@
         <v>40144</v>
       </c>
       <c r="B241" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
@@ -5120,7 +5120,7 @@
         <v>40145</v>
       </c>
       <c r="B242" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
@@ -5134,7 +5134,7 @@
         <v>40147</v>
       </c>
       <c r="B243" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
@@ -5148,7 +5148,7 @@
         <v>40150</v>
       </c>
       <c r="B244" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
@@ -5162,7 +5162,7 @@
         <v>40151</v>
       </c>
       <c r="B245" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
@@ -5176,7 +5176,7 @@
         <v>50102</v>
       </c>
       <c r="B246" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
@@ -5190,7 +5190,7 @@
         <v>50222</v>
       </c>
       <c r="B247" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
@@ -5204,7 +5204,7 @@
         <v>50223</v>
       </c>
       <c r="B248" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
@@ -5232,7 +5232,7 @@
         <v>50444</v>
       </c>
       <c r="B250" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
@@ -5246,7 +5246,7 @@
         <v>50445</v>
       </c>
       <c r="B251" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
@@ -5260,7 +5260,7 @@
         <v>50607</v>
       </c>
       <c r="B252" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
@@ -5274,7 +5274,7 @@
         <v>50608</v>
       </c>
       <c r="B253" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
@@ -5288,7 +5288,7 @@
         <v>50611</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
@@ -5302,7 +5302,7 @@
         <v>50622</v>
       </c>
       <c r="B255" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
@@ -5316,7 +5316,7 @@
         <v>50623</v>
       </c>
       <c r="B256" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
@@ -5330,7 +5330,7 @@
         <v>50625</v>
       </c>
       <c r="B257" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
@@ -5344,7 +5344,7 @@
         <v>50629</v>
       </c>
       <c r="B258" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
@@ -5358,7 +5358,7 @@
         <v>50630</v>
       </c>
       <c r="B259" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
@@ -5372,7 +5372,7 @@
         <v>50803</v>
       </c>
       <c r="B260" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
@@ -5386,7 +5386,7 @@
         <v>50805</v>
       </c>
       <c r="B261" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
@@ -5400,7 +5400,7 @@
         <v>50806</v>
       </c>
       <c r="B262" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
@@ -5428,7 +5428,7 @@
         <v>50809</v>
       </c>
       <c r="B264" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
@@ -5442,7 +5442,7 @@
         <v>50810</v>
       </c>
       <c r="B265" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
@@ -5456,7 +5456,7 @@
         <v>50812</v>
       </c>
       <c r="B266" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
@@ -5470,7 +5470,7 @@
         <v>50813</v>
       </c>
       <c r="B267" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
@@ -5484,7 +5484,7 @@
         <v>50815</v>
       </c>
       <c r="B268" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5498,7 +5498,7 @@
         <v>50816</v>
       </c>
       <c r="B269" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
@@ -5512,7 +5512,7 @@
         <v>50818</v>
       </c>
       <c r="B270" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
@@ -5526,7 +5526,7 @@
         <v>50819</v>
       </c>
       <c r="B271" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
@@ -5540,7 +5540,7 @@
         <v>50820</v>
       </c>
       <c r="B272" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
@@ -5554,7 +5554,7 @@
         <v>50821</v>
       </c>
       <c r="B273" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
@@ -5568,7 +5568,7 @@
         <v>50823</v>
       </c>
       <c r="B274" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
@@ -5582,7 +5582,7 @@
         <v>50824</v>
       </c>
       <c r="B275" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
@@ -5596,7 +5596,7 @@
         <v>50825</v>
       </c>
       <c r="B276" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
@@ -5610,7 +5610,7 @@
         <v>50826</v>
       </c>
       <c r="B277" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
@@ -5624,7 +5624,7 @@
         <v>50827</v>
       </c>
       <c r="B278" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
@@ -5638,7 +5638,7 @@
         <v>50829</v>
       </c>
       <c r="B279" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
@@ -5652,7 +5652,7 @@
         <v>50830</v>
       </c>
       <c r="B280" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
@@ -5666,7 +5666,7 @@
         <v>50831</v>
       </c>
       <c r="B281" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5680,7 +5680,7 @@
         <v>50832</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5694,7 +5694,7 @@
         <v>50833</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
@@ -5708,7 +5708,7 @@
         <v>50230</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
@@ -5722,7 +5722,7 @@
         <v>50231</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
@@ -5736,7 +5736,7 @@
         <v>60103</v>
       </c>
       <c r="B286" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
@@ -5750,7 +5750,7 @@
         <v>60109</v>
       </c>
       <c r="B287" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
@@ -5764,7 +5764,7 @@
         <v>60124</v>
       </c>
       <c r="B288" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5778,7 +5778,7 @@
         <v>60125</v>
       </c>
       <c r="B289" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
@@ -5792,7 +5792,7 @@
         <v>60126</v>
       </c>
       <c r="B290" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
@@ -5806,7 +5806,7 @@
         <v>60128</v>
       </c>
       <c r="B291" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
@@ -5820,7 +5820,7 @@
         <v>60130</v>
       </c>
       <c r="B292" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
@@ -5834,7 +5834,7 @@
         <v>60133</v>
       </c>
       <c r="B293" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
@@ -5848,7 +5848,7 @@
         <v>60134</v>
       </c>
       <c r="B294" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
@@ -5862,7 +5862,7 @@
         <v>60137</v>
       </c>
       <c r="B295" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5876,7 +5876,7 @@
         <v>60139</v>
       </c>
       <c r="B296" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5890,7 +5890,7 @@
         <v>60142</v>
       </c>
       <c r="B297" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5904,7 +5904,7 @@
         <v>60148</v>
       </c>
       <c r="B298" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5918,7 +5918,7 @@
         <v>60149</v>
       </c>
       <c r="B299" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5932,7 +5932,7 @@
         <v>60150</v>
       </c>
       <c r="B300" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5946,7 +5946,7 @@
         <v>60158</v>
       </c>
       <c r="B301" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5960,7 +5960,7 @@
         <v>60159</v>
       </c>
       <c r="B302" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -5974,7 +5974,7 @@
         <v>60162</v>
       </c>
       <c r="B303" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -5988,7 +5988,7 @@
         <v>60163</v>
       </c>
       <c r="B304" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -6002,7 +6002,7 @@
         <v>60165</v>
       </c>
       <c r="B305" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -6016,7 +6016,7 @@
         <v>60169</v>
       </c>
       <c r="B306" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -6030,7 +6030,7 @@
         <v>60170</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -6044,7 +6044,7 @@
         <v>60172</v>
       </c>
       <c r="B308" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -6058,7 +6058,7 @@
         <v>60174</v>
       </c>
       <c r="B309" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -6072,7 +6072,7 @@
         <v>60176</v>
       </c>
       <c r="B310" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -6086,7 +6086,7 @@
         <v>60178</v>
       </c>
       <c r="B311" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
@@ -6100,7 +6100,7 @@
         <v>60180</v>
       </c>
       <c r="B312" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
@@ -6114,7 +6114,7 @@
         <v>60184</v>
       </c>
       <c r="B313" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -6128,7 +6128,7 @@
         <v>60190</v>
       </c>
       <c r="B314" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
@@ -6142,7 +6142,7 @@
         <v>60191</v>
       </c>
       <c r="B315" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
@@ -6156,7 +6156,7 @@
         <v>60192</v>
       </c>
       <c r="B316" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
@@ -6170,7 +6170,7 @@
         <v>60194</v>
       </c>
       <c r="B317" s="18" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
@@ -6184,7 +6184,7 @@
         <v>60195</v>
       </c>
       <c r="B318" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
@@ -6198,7 +6198,7 @@
         <v>60196</v>
       </c>
       <c r="B319" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
@@ -6212,7 +6212,7 @@
         <v>60198</v>
       </c>
       <c r="B320" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
@@ -6226,7 +6226,7 @@
         <v>60201</v>
       </c>
       <c r="B321" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
@@ -6240,7 +6240,7 @@
         <v>60202</v>
       </c>
       <c r="B322" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
@@ -6254,7 +6254,7 @@
         <v>60204</v>
       </c>
       <c r="B323" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
@@ -6268,7 +6268,7 @@
         <v>60205</v>
       </c>
       <c r="B324" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
@@ -6282,7 +6282,7 @@
         <v>60206</v>
       </c>
       <c r="B325" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
@@ -6296,7 +6296,7 @@
         <v>60209</v>
       </c>
       <c r="B326" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
@@ -6310,7 +6310,7 @@
         <v>60211</v>
       </c>
       <c r="B327" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
@@ -6324,7 +6324,7 @@
         <v>60215</v>
       </c>
       <c r="B328" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6338,7 +6338,7 @@
         <v>60216</v>
       </c>
       <c r="B329" t="s">
-        <v>381</v>
+        <v>442</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
@@ -6352,7 +6352,7 @@
         <v>60217</v>
       </c>
       <c r="B330" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6366,7 +6366,7 @@
         <v>60219</v>
       </c>
       <c r="B331" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
@@ -6380,7 +6380,7 @@
         <v>60222</v>
       </c>
       <c r="B332" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6394,7 +6394,7 @@
         <v>60225</v>
       </c>
       <c r="B333" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
@@ -6408,7 +6408,7 @@
         <v>60230</v>
       </c>
       <c r="B334" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6422,7 +6422,7 @@
         <v>60241</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6436,7 +6436,7 @@
         <v>60242</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
@@ -6450,7 +6450,7 @@
         <v>60243</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
@@ -6464,7 +6464,7 @@
         <v>60245</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
@@ -6478,7 +6478,7 @@
         <v>60246</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
@@ -6492,7 +6492,7 @@
         <v>60247</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6506,7 +6506,7 @@
         <v>60249</v>
       </c>
       <c r="B341" s="18" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6520,7 +6520,7 @@
         <v>60250</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6534,7 +6534,7 @@
         <v>60253</v>
       </c>
       <c r="B343" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6548,7 +6548,7 @@
         <v>60254</v>
       </c>
       <c r="B344" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
@@ -6562,7 +6562,7 @@
         <v>60257</v>
       </c>
       <c r="B345" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
@@ -6576,7 +6576,7 @@
         <v>60258</v>
       </c>
       <c r="B346" t="s">
-        <v>284</v>
+        <v>451</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
@@ -6590,7 +6590,7 @@
         <v>60266</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>60269</v>
       </c>
       <c r="B348" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6618,7 +6618,7 @@
         <v>60270</v>
       </c>
       <c r="B349" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6632,7 +6632,7 @@
         <v>60272</v>
       </c>
       <c r="B350" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6646,7 +6646,7 @@
         <v>60274</v>
       </c>
       <c r="B351" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6660,7 +6660,7 @@
         <v>60275</v>
       </c>
       <c r="B352" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6674,7 +6674,7 @@
         <v>60276</v>
       </c>
       <c r="B353" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6688,7 +6688,7 @@
         <v>60278</v>
       </c>
       <c r="B354" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6702,7 +6702,7 @@
         <v>60279</v>
       </c>
       <c r="B355" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6716,7 +6716,7 @@
         <v>60280</v>
       </c>
       <c r="B356" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6730,7 +6730,7 @@
         <v>60281</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6744,7 +6744,7 @@
         <v>60282</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6758,7 +6758,7 @@
         <v>60283</v>
       </c>
       <c r="B359" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6772,7 +6772,7 @@
         <v>60284</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
@@ -6786,7 +6786,7 @@
         <v>60285</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>350</v>
+        <v>444</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6800,7 +6800,7 @@
         <v>60286</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6814,7 +6814,7 @@
         <v>60287</v>
       </c>
       <c r="B363" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6828,7 +6828,7 @@
         <v>60289</v>
       </c>
       <c r="B364" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6842,7 +6842,7 @@
         <v>60290</v>
       </c>
       <c r="B365" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6856,7 +6856,7 @@
         <v>60291</v>
       </c>
       <c r="B366" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6870,7 +6870,7 @@
         <v>60292</v>
       </c>
       <c r="B367" s="18" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6884,7 +6884,7 @@
         <v>60293</v>
       </c>
       <c r="B368" s="18" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6898,7 +6898,7 @@
         <v>60296</v>
       </c>
       <c r="B369" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6912,7 +6912,7 @@
         <v>60297</v>
       </c>
       <c r="B370" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6926,7 +6926,7 @@
         <v>60299</v>
       </c>
       <c r="B371" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6940,7 +6940,7 @@
         <v>60302</v>
       </c>
       <c r="B372" s="18" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6954,7 +6954,7 @@
         <v>60303</v>
       </c>
       <c r="B373" s="18" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6968,7 +6968,7 @@
         <v>60305</v>
       </c>
       <c r="B374" s="18" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6982,7 +6982,7 @@
         <v>61001</v>
       </c>
       <c r="B375" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6996,7 +6996,7 @@
         <v>61004</v>
       </c>
       <c r="B376" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -7010,7 +7010,7 @@
         <v>61007</v>
       </c>
       <c r="B377" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -7024,7 +7024,7 @@
         <v>61009</v>
       </c>
       <c r="B378" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -7038,7 +7038,7 @@
         <v>61012</v>
       </c>
       <c r="B379" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -7052,7 +7052,7 @@
         <v>61018</v>
       </c>
       <c r="B380" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -7066,7 +7066,7 @@
         <v>61102</v>
       </c>
       <c r="B381" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -7080,7 +7080,7 @@
         <v>61205</v>
       </c>
       <c r="B382" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -7094,7 +7094,7 @@
         <v>70100</v>
       </c>
       <c r="B383" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -7108,7 +7108,7 @@
         <v>70101</v>
       </c>
       <c r="B384" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7122,7 +7122,7 @@
         <v>70102</v>
       </c>
       <c r="B385" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -7136,7 +7136,7 @@
         <v>70103</v>
       </c>
       <c r="B386" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7150,7 +7150,7 @@
         <v>70106</v>
       </c>
       <c r="B387" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7164,7 +7164,7 @@
         <v>70107</v>
       </c>
       <c r="B388" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7178,7 +7178,7 @@
         <v>70109</v>
       </c>
       <c r="B389" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7192,7 +7192,7 @@
         <v>70113</v>
       </c>
       <c r="B390" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7206,7 +7206,7 @@
         <v>70114</v>
       </c>
       <c r="B391" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7220,7 +7220,7 @@
         <v>70115</v>
       </c>
       <c r="B392" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7234,7 +7234,7 @@
         <v>70116</v>
       </c>
       <c r="B393" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7248,7 +7248,7 @@
         <v>70638</v>
       </c>
       <c r="B394" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7262,7 +7262,7 @@
         <v>70639</v>
       </c>
       <c r="B395" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7276,7 +7276,7 @@
         <v>70640</v>
       </c>
       <c r="B396" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7290,7 +7290,7 @@
         <v>70642</v>
       </c>
       <c r="B397" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7304,7 +7304,7 @@
         <v>90504</v>
       </c>
       <c r="B398" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7318,7 +7318,7 @@
         <v>90509</v>
       </c>
       <c r="B399" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7332,7 +7332,7 @@
         <v>90602</v>
       </c>
       <c r="B400" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7346,7 +7346,7 @@
         <v>90621</v>
       </c>
       <c r="B401" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7360,7 +7360,7 @@
         <v>90622</v>
       </c>
       <c r="B402" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7374,7 +7374,7 @@
         <v>90631</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7388,7 +7388,7 @@
         <v>90658</v>
       </c>
       <c r="B404" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7402,7 +7402,7 @@
         <v>90660</v>
       </c>
       <c r="B405" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7416,7 +7416,7 @@
         <v>90668</v>
       </c>
       <c r="B406" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7430,7 +7430,7 @@
         <v>90671</v>
       </c>
       <c r="B407" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7444,7 +7444,7 @@
         <v>90679</v>
       </c>
       <c r="B408" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7458,7 +7458,7 @@
         <v>90683</v>
       </c>
       <c r="B409" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
@@ -7472,7 +7472,7 @@
         <v>90705</v>
       </c>
       <c r="B410" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7486,7 +7486,7 @@
         <v>90706</v>
       </c>
       <c r="B411" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7500,7 +7500,7 @@
         <v>90708</v>
       </c>
       <c r="B412" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7514,7 +7514,7 @@
         <v>90709</v>
       </c>
       <c r="B413" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7528,7 +7528,7 @@
         <v>90713</v>
       </c>
       <c r="B414" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7542,7 +7542,7 @@
         <v>1218</v>
       </c>
       <c r="B415" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7556,7 +7556,7 @@
         <v>1959</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7570,7 +7570,7 @@
         <v>5625</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
@@ -7584,7 +7584,7 @@
         <v>1817</v>
       </c>
       <c r="B418" s="8" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
@@ -7598,7 +7598,7 @@
         <v>5737</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7612,7 +7612,7 @@
         <v>60295</v>
       </c>
       <c r="B420" s="8" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
@@ -7626,7 +7626,7 @@
         <v>1045</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
@@ -7640,7 +7640,7 @@
         <v>1043</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>4</v>
@@ -7654,7 +7654,7 @@
         <v>20340</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>4</v>
@@ -7668,7 +7668,7 @@
         <v>40146</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C424" s="14" t="s">
         <v>4</v>
@@ -7682,7 +7682,7 @@
         <v>60260</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C425" s="14" t="s">
         <v>4</v>
@@ -7696,7 +7696,7 @@
         <v>1017</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C426" s="14" t="s">
         <v>4</v>
@@ -7710,7 +7710,7 @@
         <v>60300</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C427" s="14" t="s">
         <v>4</v>
@@ -7724,7 +7724,7 @@
         <v>20191</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
@@ -7738,7 +7738,7 @@
         <v>20399</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
@@ -7752,7 +7752,7 @@
         <v>60240</v>
       </c>
       <c r="B430" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
@@ -7766,7 +7766,7 @@
         <v>60244</v>
       </c>
       <c r="B431" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
@@ -7780,7 +7780,7 @@
         <v>60248</v>
       </c>
       <c r="B432" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
@@ -7794,7 +7794,7 @@
         <v>60288</v>
       </c>
       <c r="B433" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
@@ -7808,7 +7808,7 @@
         <v>90714</v>
       </c>
       <c r="B434" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7822,7 +7822,7 @@
         <v>1014</v>
       </c>
       <c r="B435" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
@@ -7836,7 +7836,7 @@
         <v>1016</v>
       </c>
       <c r="B436" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
@@ -7850,7 +7850,7 @@
         <v>60301</v>
       </c>
       <c r="B437" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
@@ -7864,7 +7864,7 @@
         <v>1041</v>
       </c>
       <c r="B438" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
@@ -7878,7 +7878,7 @@
         <v>971</v>
       </c>
       <c r="B439" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
@@ -7892,7 +7892,7 @@
         <v>50610</v>
       </c>
       <c r="B440" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
@@ -7906,7 +7906,7 @@
         <v>943</v>
       </c>
       <c r="B441" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7920,7 +7920,7 @@
         <v>20306</v>
       </c>
       <c r="B442" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
@@ -7934,7 +7934,7 @@
         <v>90630</v>
       </c>
       <c r="B443" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
@@ -7948,7 +7948,7 @@
         <v>1047</v>
       </c>
       <c r="B444" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
@@ -7962,7 +7962,7 @@
         <v>20398</v>
       </c>
       <c r="B445" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C445" s="14" t="s">
         <v>4</v>
@@ -7972,7 +7972,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D421"/>
+  <autoFilter ref="A1:D445"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$445</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$447</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="454">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1378,12 +1378,18 @@
   </si>
   <si>
     <t>FERRETERIA CLAUDIO</t>
+  </si>
+  <si>
+    <t>FERRETERIA RyV</t>
+  </si>
+  <si>
+    <t>FERRETERIA A y J</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1733,7 +1739,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D445"/>
+  <dimension ref="A1:D447"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6979,80 +6985,80 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B375" t="s">
-        <v>394</v>
+        <v>60306</v>
+      </c>
+      <c r="B375" s="18" t="s">
+        <v>453</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D375" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>61004</v>
-      </c>
-      <c r="B376" t="s">
-        <v>287</v>
+        <v>60308</v>
+      </c>
+      <c r="B376" s="18" t="s">
+        <v>452</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="15" t="s">
-        <v>5</v>
+      <c r="D376" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>61007</v>
+        <v>61001</v>
       </c>
       <c r="B377" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="15" t="s">
-        <v>5</v>
+      <c r="D377" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B378" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="12" t="s">
-        <v>8</v>
+      <c r="D378" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>61012</v>
+        <v>61007</v>
       </c>
       <c r="B379" t="s">
-        <v>289</v>
+        <v>405</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="12" t="s">
-        <v>8</v>
+      <c r="D379" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>61018</v>
+        <v>61009</v>
       </c>
       <c r="B380" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -7063,10 +7069,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>61102</v>
+        <v>61012</v>
       </c>
       <c r="B381" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -7077,24 +7083,24 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>61205</v>
+        <v>61018</v>
       </c>
       <c r="B382" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="15" t="s">
-        <v>5</v>
+      <c r="D382" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>70100</v>
+        <v>61102</v>
       </c>
       <c r="B383" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -7105,10 +7111,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>70101</v>
+        <v>61205</v>
       </c>
       <c r="B384" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7119,38 +7125,38 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>70102</v>
+        <v>70100</v>
       </c>
       <c r="B385" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="15" t="s">
-        <v>5</v>
+      <c r="D385" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>70103</v>
+        <v>70101</v>
       </c>
       <c r="B386" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="12" t="s">
-        <v>8</v>
+      <c r="D386" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70106</v>
+        <v>70102</v>
       </c>
       <c r="B387" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7161,122 +7167,122 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70107</v>
+        <v>70103</v>
       </c>
       <c r="B388" t="s">
-        <v>409</v>
+        <v>296</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="15" t="s">
+      <c r="D388" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B389" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="12" t="s">
-        <v>8</v>
+      <c r="D389" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70113</v>
+        <v>70107</v>
       </c>
       <c r="B390" t="s">
-        <v>299</v>
+        <v>409</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D390" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70114</v>
+        <v>70109</v>
       </c>
       <c r="B391" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D391" s="9" t="s">
-        <v>9</v>
+      <c r="D391" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70115</v>
+        <v>70113</v>
       </c>
       <c r="B392" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D392" s="9" t="s">
-        <v>9</v>
+      <c r="D392" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70116</v>
+        <v>70114</v>
       </c>
       <c r="B393" t="s">
-        <v>410</v>
+        <v>319</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D393" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B394" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D394" s="12" t="s">
-        <v>8</v>
+      <c r="D394" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>70639</v>
+        <v>70116</v>
       </c>
       <c r="B395" t="s">
-        <v>301</v>
+        <v>410</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D395" s="12" t="s">
+      <c r="D395" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>70640</v>
+        <v>70638</v>
       </c>
       <c r="B396" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7287,10 +7293,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>70642</v>
+        <v>70639</v>
       </c>
       <c r="B397" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7301,10 +7307,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90504</v>
+        <v>70640</v>
       </c>
       <c r="B398" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7315,10 +7321,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90509</v>
+        <v>70642</v>
       </c>
       <c r="B399" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7329,24 +7335,24 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90602</v>
+        <v>90504</v>
       </c>
       <c r="B400" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D400" s="15" t="s">
-        <v>5</v>
+      <c r="D400" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90621</v>
+        <v>90509</v>
       </c>
       <c r="B401" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7357,66 +7363,66 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90622</v>
+        <v>90602</v>
       </c>
       <c r="B402" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D402" s="9" t="s">
+      <c r="D402" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B403" s="8" t="s">
-        <v>336</v>
+        <v>90621</v>
+      </c>
+      <c r="B403" t="s">
+        <v>307</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D403" s="9" t="s">
-        <v>5</v>
+      <c r="D403" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90658</v>
+        <v>90622</v>
       </c>
       <c r="B404" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D404" s="12" t="s">
-        <v>8</v>
+      <c r="D404" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90660</v>
-      </c>
-      <c r="B405" t="s">
-        <v>309</v>
+        <v>90631</v>
+      </c>
+      <c r="B405" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D405" s="12" t="s">
-        <v>8</v>
+      <c r="D405" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90668</v>
+        <v>90658</v>
       </c>
       <c r="B406" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7427,10 +7433,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90671</v>
+        <v>90660</v>
       </c>
       <c r="B407" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7441,10 +7447,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90679</v>
+        <v>90668</v>
       </c>
       <c r="B408" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7455,10 +7461,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90683</v>
+        <v>90671</v>
       </c>
       <c r="B409" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
@@ -7469,10 +7475,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90705</v>
+        <v>90679</v>
       </c>
       <c r="B410" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7483,10 +7489,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90706</v>
+        <v>90683</v>
       </c>
       <c r="B411" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7497,10 +7503,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90708</v>
+        <v>90705</v>
       </c>
       <c r="B412" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7511,10 +7517,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="B413" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7525,24 +7531,24 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>90713</v>
+        <v>90708</v>
       </c>
       <c r="B414" t="s">
-        <v>393</v>
+        <v>316</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D414" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>1218</v>
+        <v>90709</v>
       </c>
       <c r="B415" t="s">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7553,24 +7559,24 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B416" s="8" t="s">
-        <v>374</v>
+        <v>90713</v>
+      </c>
+      <c r="B416" t="s">
+        <v>393</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D416" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B417" s="8" t="s">
-        <v>375</v>
+        <v>1218</v>
+      </c>
+      <c r="B417" t="s">
+        <v>373</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
@@ -7581,10 +7587,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>1817</v>
+        <v>1959</v>
       </c>
       <c r="B418" s="8" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
@@ -7595,10 +7601,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>5737</v>
+        <v>5625</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7609,108 +7615,108 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
-        <v>60295</v>
+        <v>1817</v>
       </c>
       <c r="B420" s="8" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D420" s="9" t="s">
-        <v>9</v>
+      <c r="D420" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B421" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D421" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A422" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B422" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D422" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A423" s="6">
         <v>1045</v>
       </c>
-      <c r="B421" s="8" t="s">
+      <c r="B423" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C421" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D421" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A422">
+      <c r="C423" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D423" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A424">
         <v>1043</v>
       </c>
-      <c r="B422" t="s">
+      <c r="B424" t="s">
         <v>412</v>
       </c>
-      <c r="C422" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D422" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A423">
+      <c r="C424" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D424" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A425">
         <v>20340</v>
       </c>
-      <c r="B423" t="s">
+      <c r="B425" t="s">
         <v>413</v>
       </c>
-      <c r="C423" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D423" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A424">
-        <v>40146</v>
-      </c>
-      <c r="B424" t="s">
-        <v>414</v>
-      </c>
-      <c r="C424" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D424" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A425">
-        <v>60260</v>
-      </c>
-      <c r="B425" t="s">
-        <v>415</v>
-      </c>
-      <c r="C425" s="14" t="s">
+      <c r="C425" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D425" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>1017</v>
+        <v>40146</v>
       </c>
       <c r="B426" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C426" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D426" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>60300</v>
+        <v>60260</v>
       </c>
       <c r="B427" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C427" s="14" t="s">
         <v>4</v>
@@ -7721,24 +7727,24 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>20191</v>
+        <v>1017</v>
       </c>
       <c r="B428" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D428" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>20399</v>
+        <v>60300</v>
       </c>
       <c r="B429" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
@@ -7749,10 +7755,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>60240</v>
+        <v>20191</v>
       </c>
       <c r="B430" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
@@ -7763,10 +7769,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>60244</v>
+        <v>20399</v>
       </c>
       <c r="B431" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
@@ -7777,52 +7783,52 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>60248</v>
+        <v>60240</v>
       </c>
       <c r="B432" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>60288</v>
+        <v>60244</v>
       </c>
       <c r="B433" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D433" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>90714</v>
+        <v>60248</v>
       </c>
       <c r="B434" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D434" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>1014</v>
+        <v>60288</v>
       </c>
       <c r="B435" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
@@ -7833,24 +7839,24 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>1016</v>
+        <v>90714</v>
       </c>
       <c r="B436" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>60301</v>
+        <v>1014</v>
       </c>
       <c r="B437" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
@@ -7861,24 +7867,24 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>1041</v>
+        <v>1016</v>
       </c>
       <c r="B438" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D438" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>971</v>
+        <v>60301</v>
       </c>
       <c r="B439" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
@@ -7889,24 +7895,24 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>50610</v>
+        <v>1041</v>
       </c>
       <c r="B440" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D440" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>943</v>
+        <v>971</v>
       </c>
       <c r="B441" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7917,62 +7923,90 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>20306</v>
+        <v>50610</v>
       </c>
       <c r="B442" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>90630</v>
+        <v>943</v>
       </c>
       <c r="B443" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D443" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>1047</v>
+        <v>20306</v>
       </c>
       <c r="B444" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D444" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
+        <v>90630</v>
+      </c>
+      <c r="B445" t="s">
+        <v>433</v>
+      </c>
+      <c r="C445" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D445" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>1047</v>
+      </c>
+      <c r="B446" t="s">
+        <v>434</v>
+      </c>
+      <c r="C446" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D446" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A447">
         <v>20398</v>
       </c>
-      <c r="B445" t="s">
+      <c r="B447" t="s">
         <v>435</v>
       </c>
-      <c r="C445" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D445" t="s">
+      <c r="C447" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D447" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D445"/>
+  <autoFilter ref="A1:D447"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$447</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$448</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="455">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1384,6 +1384,9 @@
   </si>
   <si>
     <t>FERRETERIA A y J</t>
+  </si>
+  <si>
+    <t>FERRETERIA CLAY</t>
   </si>
 </sst>
 </file>
@@ -1739,7 +1742,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D447"/>
+  <dimension ref="A1:D448"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3340,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3849,24 +3852,24 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20200</v>
+        <v>20192</v>
       </c>
       <c r="B151" t="s">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="13" t="s">
+      <c r="D151" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B152" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
@@ -3877,150 +3880,150 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B153" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="10" t="s">
-        <v>8</v>
+      <c r="D153" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B154" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="1" t="s">
-        <v>9</v>
+      <c r="D154" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B155" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="10" t="s">
-        <v>8</v>
+      <c r="D155" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B156" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="D156" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B157" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="10" t="s">
+      <c r="D157" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B158" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="13" t="s">
-        <v>5</v>
+      <c r="D158" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B159" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="10" t="s">
-        <v>8</v>
+      <c r="D159" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B160" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="13" t="s">
-        <v>5</v>
+      <c r="D160" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B161" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="D161" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B162" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="13" t="s">
+      <c r="D162" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B163" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
@@ -4031,24 +4034,24 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B164" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="10" t="s">
-        <v>8</v>
+      <c r="D164" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B165" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
@@ -4059,108 +4062,108 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B166" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="13" t="s">
-        <v>5</v>
+      <c r="D166" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B167" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="10" t="s">
-        <v>8</v>
+      <c r="D167" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B168" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="1" t="s">
+      <c r="D168" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B169" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="17" t="s">
-        <v>9</v>
+      <c r="D169" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B170" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>8</v>
+      <c r="D170" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B171" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="13" t="s">
-        <v>5</v>
+      <c r="D171" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B172" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="10" t="s">
-        <v>8</v>
+      <c r="D172" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B173" t="s">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
@@ -4171,206 +4174,206 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B174" t="s">
-        <v>392</v>
+        <v>90</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D174" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B175" t="s">
-        <v>196</v>
+        <v>392</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="1" t="s">
-        <v>8</v>
+      <c r="D175" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B176" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="13" t="s">
-        <v>5</v>
+      <c r="D176" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B177" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="1" t="s">
-        <v>8</v>
+      <c r="D177" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B178" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="13" t="s">
-        <v>5</v>
+      <c r="D178" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B179" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>8</v>
+      <c r="D179" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B180" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="3" t="s">
-        <v>5</v>
+      <c r="D180" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B181" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="1" t="s">
-        <v>9</v>
+      <c r="D181" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B182" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="17" t="s">
+      <c r="D182" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B183" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="1" t="s">
-        <v>8</v>
+      <c r="D183" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B184" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="3" t="s">
-        <v>5</v>
+      <c r="D184" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B185" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="1" t="s">
-        <v>8</v>
+      <c r="D185" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B186" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="10" t="s">
+      <c r="D186" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B187" t="s">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="13" t="s">
-        <v>5</v>
+      <c r="D187" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
@@ -4381,52 +4384,52 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B189" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="10" t="s">
-        <v>8</v>
+      <c r="D189" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B190" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="13" t="s">
-        <v>5</v>
+      <c r="D190" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B191" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="1" t="s">
-        <v>8</v>
+      <c r="D191" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B192" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
@@ -4437,10 +4440,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B193" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4451,10 +4454,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B194" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
@@ -4465,24 +4468,24 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B195" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="13" t="s">
-        <v>5</v>
+      <c r="D195" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B196" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4493,52 +4496,52 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B197" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="1" t="s">
-        <v>8</v>
+      <c r="D197" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B198" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="10" t="s">
+      <c r="D198" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B199" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="D199" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B200" t="s">
-        <v>205</v>
+        <v>126</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4549,10 +4552,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B201" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4563,38 +4566,38 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B202" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="13" t="s">
-        <v>5</v>
+      <c r="D202" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B203" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="1" t="s">
-        <v>8</v>
+      <c r="D203" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B204" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4605,10 +4608,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B205" t="s">
-        <v>445</v>
+        <v>115</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
@@ -4619,66 +4622,66 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B206" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="13" t="s">
-        <v>5</v>
+      <c r="D206" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B207" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="1" t="s">
-        <v>8</v>
+      <c r="D207" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B208" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="13" t="s">
-        <v>5</v>
+      <c r="D208" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B209" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="10" t="s">
-        <v>8</v>
+      <c r="D209" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B210" t="s">
-        <v>208</v>
+        <v>45</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
@@ -4689,38 +4692,38 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B211" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="13" t="s">
-        <v>5</v>
+      <c r="D211" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B212" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="1" t="s">
-        <v>8</v>
+      <c r="D212" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B213" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
@@ -4731,10 +4734,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B214" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4745,10 +4748,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B215" t="s">
-        <v>218</v>
+        <v>62</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4759,52 +4762,52 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B216" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="10" t="s">
+      <c r="D216" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B217" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="D217" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B218" t="s">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="10" t="s">
+      <c r="D218" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B219" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
@@ -4815,66 +4818,66 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B220" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="13" t="s">
-        <v>5</v>
+      <c r="D220" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B221" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="1" t="s">
-        <v>8</v>
+      <c r="D221" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B222" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="10" t="s">
+      <c r="D222" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B223" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="1" t="s">
+      <c r="D223" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B224" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
@@ -4885,66 +4888,66 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B225" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="10" t="s">
+      <c r="D225" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B226" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="1" t="s">
+      <c r="D226" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B227" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="10" t="s">
+      <c r="D227" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B228" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="1" t="s">
+      <c r="D228" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B229" t="s">
-        <v>324</v>
+        <v>157</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
@@ -4955,52 +4958,52 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B230" s="8" t="s">
-        <v>338</v>
+        <v>20396</v>
+      </c>
+      <c r="B230" t="s">
+        <v>324</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="11" t="s">
-        <v>5</v>
+      <c r="D230" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B231" t="s">
-        <v>163</v>
+        <v>20397</v>
+      </c>
+      <c r="B231" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="1" t="s">
-        <v>8</v>
+      <c r="D231" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B232" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="13" t="s">
-        <v>5</v>
+      <c r="D232" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B233" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
@@ -5011,24 +5014,24 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B234" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="1" t="s">
-        <v>8</v>
+      <c r="D234" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B235" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
@@ -5039,24 +5042,24 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B236" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="10" t="s">
+      <c r="D236" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B237" t="s">
-        <v>321</v>
+        <v>118</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
@@ -5067,66 +5070,66 @@
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B238" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="1" t="s">
+      <c r="D238" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B239" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="13" t="s">
-        <v>5</v>
+      <c r="D239" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B240" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="10" t="s">
-        <v>8</v>
+      <c r="D240" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B241" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="13" t="s">
-        <v>5</v>
+      <c r="D241" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B242" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
@@ -5137,206 +5140,206 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B243" t="s">
-        <v>396</v>
+        <v>161</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="19" t="s">
-        <v>8</v>
+      <c r="D243" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B244" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="10" t="s">
+      <c r="D244" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B245" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="1" t="s">
+      <c r="D245" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B246" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="13" t="s">
-        <v>5</v>
+      <c r="D246" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B247" t="s">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="1" t="s">
-        <v>8</v>
+      <c r="D247" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B248" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="10" t="s">
+      <c r="D248" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B249" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="3" t="s">
-        <v>5</v>
+      <c r="D249" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B250" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
-        <v>8</v>
+      <c r="D250" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B251" t="s">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="11" t="s">
-        <v>5</v>
+      <c r="D251" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B252" t="s">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="13" t="s">
+      <c r="D252" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B253" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="1" t="s">
-        <v>8</v>
+      <c r="D253" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B254" s="8" t="s">
-        <v>341</v>
+        <v>50608</v>
+      </c>
+      <c r="B254" t="s">
+        <v>173</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="14" t="s">
+      <c r="D254" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B255" t="s">
-        <v>93</v>
+        <v>50611</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="16" t="s">
-        <v>8</v>
+      <c r="D255" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B256" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="10" t="s">
+      <c r="D256" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B257" t="s">
-        <v>199</v>
+        <v>107</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
@@ -5347,94 +5350,94 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B258" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="1" t="s">
-        <v>5</v>
+      <c r="D258" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B259" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="14" t="s">
-        <v>8</v>
+      <c r="D259" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B260" t="s">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="1" t="s">
+      <c r="D260" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B261" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="10" t="s">
+      <c r="D261" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B262" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="D262" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B263" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="13" t="s">
-        <v>5</v>
+      <c r="D263" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B264" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
@@ -5445,24 +5448,24 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B265" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="1" t="s">
-        <v>8</v>
+      <c r="D265" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B266" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
@@ -5473,80 +5476,80 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B267" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="17" t="s">
-        <v>9</v>
+      <c r="D267" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B268" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="10" t="s">
-        <v>8</v>
+      <c r="D268" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B269" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="1" t="s">
+      <c r="D269" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B270" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="13" t="s">
-        <v>5</v>
+      <c r="D270" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B271" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="10" t="s">
-        <v>8</v>
+      <c r="D271" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B272" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
@@ -5557,66 +5560,66 @@
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B273" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="1" t="s">
+      <c r="D273" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B274" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="17" t="s">
-        <v>9</v>
+      <c r="D274" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B275" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="13" t="s">
-        <v>5</v>
+      <c r="D275" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B276" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="10" t="s">
-        <v>8</v>
+      <c r="D276" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B277" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
@@ -5627,24 +5630,24 @@
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B278" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="1" t="s">
+      <c r="D278" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B279" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
@@ -5655,136 +5658,136 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B280" t="s">
-        <v>358</v>
+        <v>231</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="11" t="s">
+      <c r="D280" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B281" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D281" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B282" s="8" t="s">
-        <v>343</v>
+        <v>50831</v>
+      </c>
+      <c r="B282" t="s">
+        <v>344</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D283" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>50231</v>
+        <v>50230</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D285" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B286" t="s">
-        <v>232</v>
+        <v>50231</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="13" t="s">
-        <v>5</v>
+      <c r="D286" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B287" t="s">
-        <v>322</v>
+        <v>232</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="11" t="s">
-        <v>9</v>
+      <c r="D287" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B288" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="13" t="s">
-        <v>5</v>
+      <c r="D288" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B289" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
@@ -5795,80 +5798,80 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B290" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="10" t="s">
-        <v>8</v>
+      <c r="D290" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B291" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="3" t="s">
-        <v>5</v>
+      <c r="D291" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B292" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="1" t="s">
-        <v>8</v>
+      <c r="D292" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B293" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="13" t="s">
-        <v>5</v>
+      <c r="D293" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B294" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="1" t="s">
-        <v>8</v>
+      <c r="D294" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B295" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5879,10 +5882,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B296" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5893,10 +5896,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B297" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5907,10 +5910,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B298" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5921,10 +5924,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B299" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5935,66 +5938,66 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B300" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="13" t="s">
-        <v>5</v>
+      <c r="D300" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B301" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="10" t="s">
-        <v>8</v>
+      <c r="D301" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B302" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="1" t="s">
+      <c r="D302" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B303" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="13" t="s">
-        <v>5</v>
+      <c r="D303" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B304" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -6005,80 +6008,80 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B305" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="1" t="s">
-        <v>8</v>
+      <c r="D305" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B306" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B307" s="8" t="s">
-        <v>331</v>
+        <v>60169</v>
+      </c>
+      <c r="B307" t="s">
+        <v>250</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="11" t="s">
-        <v>5</v>
+      <c r="D307" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B308" t="s">
-        <v>251</v>
+        <v>60170</v>
+      </c>
+      <c r="B308" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="1" t="s">
-        <v>8</v>
+      <c r="D308" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B309" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="13" t="s">
-        <v>5</v>
+      <c r="D309" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B310" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -6089,52 +6092,52 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B311" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="1" t="s">
-        <v>8</v>
+      <c r="D311" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B312" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="10" t="s">
+      <c r="D312" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B313" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="1" t="s">
+      <c r="D313" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B314" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
@@ -6145,24 +6148,24 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B315" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="10" t="s">
+      <c r="D315" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B316" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
@@ -6173,38 +6176,38 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B317" s="18" t="s">
-        <v>400</v>
+        <v>60192</v>
+      </c>
+      <c r="B317" t="s">
+        <v>259</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B318" t="s">
-        <v>260</v>
+        <v>60194</v>
+      </c>
+      <c r="B318" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D318" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B319" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
@@ -6215,10 +6218,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B320" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
@@ -6229,52 +6232,52 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B321" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" t="s">
-        <v>9</v>
+      <c r="D321" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B322" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="13" t="s">
-        <v>5</v>
+      <c r="D322" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B323" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="1" t="s">
-        <v>8</v>
+      <c r="D323" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B324" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
@@ -6285,10 +6288,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B325" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
@@ -6299,192 +6302,192 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B326" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="10" t="s">
+      <c r="D326" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B327" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="1" t="s">
+      <c r="D327" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B328" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="10" t="s">
+      <c r="D328" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B329" t="s">
-        <v>442</v>
+        <v>270</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D329" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B330" t="s">
-        <v>271</v>
+        <v>442</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D330" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B331" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="1" t="s">
+      <c r="D331" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B332" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="10" t="s">
-        <v>5</v>
+      <c r="D332" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B333" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="17" t="s">
-        <v>9</v>
+      <c r="D333" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B334" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="10" t="s">
-        <v>8</v>
+      <c r="D334" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B335" s="8" t="s">
-        <v>332</v>
+        <v>60230</v>
+      </c>
+      <c r="B335" t="s">
+        <v>275</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="7" t="s">
-        <v>9</v>
+      <c r="D335" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D336" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D337" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D338" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
@@ -6495,10 +6498,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60247</v>
+        <v>60246</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6509,10 +6512,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B341" s="18" t="s">
-        <v>399</v>
+        <v>60247</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6523,38 +6526,38 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B342" s="8" t="s">
-        <v>333</v>
+        <v>60249</v>
+      </c>
+      <c r="B342" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="11" t="s">
-        <v>8</v>
+      <c r="D342" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B343" t="s">
-        <v>276</v>
+        <v>60250</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="1" t="s">
+      <c r="D343" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B344" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
@@ -6565,94 +6568,94 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B345" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B346" t="s">
-        <v>451</v>
+        <v>278</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B347" s="8" t="s">
-        <v>337</v>
+        <v>60258</v>
+      </c>
+      <c r="B347" t="s">
+        <v>451</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="11" t="s">
-        <v>8</v>
+      <c r="D347" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B348" t="s">
-        <v>279</v>
+        <v>60266</v>
+      </c>
+      <c r="B348" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="10" t="s">
+      <c r="D348" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B349" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="1" t="s">
-        <v>9</v>
+      <c r="D349" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B350" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B351" t="s">
-        <v>372</v>
+        <v>281</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6663,10 +6666,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B352" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6677,10 +6680,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B353" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6691,38 +6694,38 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B354" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="13" t="s">
+      <c r="D354" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B355" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="1" t="s">
-        <v>5</v>
+      <c r="D355" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B356" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6733,66 +6736,66 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B357" s="8" t="s">
-        <v>330</v>
+        <v>60280</v>
+      </c>
+      <c r="B357" t="s">
+        <v>286</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="11" t="s">
-        <v>9</v>
+      <c r="D357" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D358" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B359" t="s">
-        <v>370</v>
+        <v>60282</v>
+      </c>
+      <c r="B359" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="1" t="s">
-        <v>8</v>
+      <c r="D359" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B360" s="8" t="s">
-        <v>329</v>
+        <v>60283</v>
+      </c>
+      <c r="B360" t="s">
+        <v>370</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="9" t="s">
-        <v>5</v>
+      <c r="D360" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>444</v>
+        <v>329</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6803,10 +6806,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6817,52 +6820,52 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B363" t="s">
-        <v>369</v>
+        <v>60286</v>
+      </c>
+      <c r="B363" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="12" t="s">
+      <c r="D363" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B364" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D364" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B365" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B366" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6873,10 +6876,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B367" s="18" t="s">
-        <v>391</v>
+        <v>60291</v>
+      </c>
+      <c r="B367" t="s">
+        <v>368</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6887,10 +6890,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60293</v>
+        <v>60292</v>
       </c>
       <c r="B368" s="18" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6901,10 +6904,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B369" t="s">
-        <v>382</v>
+        <v>60293</v>
+      </c>
+      <c r="B369" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6915,10 +6918,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B370" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6929,10 +6932,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B371" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6943,10 +6946,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B372" s="18" t="s">
-        <v>401</v>
+        <v>60299</v>
+      </c>
+      <c r="B372" t="s">
+        <v>379</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6957,10 +6960,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B373" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6971,10 +6974,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>60305</v>
+        <v>60303</v>
       </c>
       <c r="B374" s="18" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6985,24 +6988,24 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>60306</v>
+        <v>60305</v>
       </c>
       <c r="B375" s="18" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D375" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>60308</v>
+        <v>60306</v>
       </c>
       <c r="B376" s="18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -7013,38 +7016,38 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B377" t="s">
-        <v>394</v>
+        <v>60308</v>
+      </c>
+      <c r="B377" s="18" t="s">
+        <v>452</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D377" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B378" t="s">
-        <v>287</v>
+        <v>394</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="15" t="s">
-        <v>5</v>
+      <c r="D378" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B379" t="s">
-        <v>405</v>
+        <v>287</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -7055,24 +7058,24 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B380" t="s">
-        <v>288</v>
+        <v>405</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="12" t="s">
-        <v>8</v>
+      <c r="D380" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B381" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -7083,10 +7086,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B382" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -7097,10 +7100,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B383" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -7111,52 +7114,52 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B384" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D384" s="15" t="s">
-        <v>5</v>
+      <c r="D384" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B385" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="12" t="s">
-        <v>8</v>
+      <c r="D385" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B386" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="15" t="s">
-        <v>5</v>
+      <c r="D386" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B387" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7167,94 +7170,94 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B388" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="12" t="s">
-        <v>8</v>
+      <c r="D388" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B389" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="15" t="s">
-        <v>5</v>
+      <c r="D389" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B390" t="s">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D390" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B391" t="s">
-        <v>298</v>
+        <v>409</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D391" s="12" t="s">
+      <c r="D391" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B392" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D392" s="15" t="s">
-        <v>5</v>
+      <c r="D392" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B393" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D393" s="9" t="s">
-        <v>9</v>
+      <c r="D393" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B394" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7265,38 +7268,38 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B395" t="s">
-        <v>410</v>
+        <v>325</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D395" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>70638</v>
+        <v>70116</v>
       </c>
       <c r="B396" t="s">
-        <v>300</v>
+        <v>410</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D396" s="12" t="s">
+      <c r="D396" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B397" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7307,10 +7310,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B398" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7321,10 +7324,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B399" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7335,10 +7338,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B400" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7349,10 +7352,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B401" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7363,52 +7366,52 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B402" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D402" s="15" t="s">
-        <v>5</v>
+      <c r="D402" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B403" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D403" s="12" t="s">
-        <v>8</v>
+      <c r="D403" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B404" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D404" s="9" t="s">
-        <v>5</v>
+      <c r="D404" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B405" s="8" t="s">
-        <v>336</v>
+        <v>90622</v>
+      </c>
+      <c r="B405" t="s">
+        <v>327</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7419,24 +7422,24 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B406" t="s">
-        <v>308</v>
+        <v>90631</v>
+      </c>
+      <c r="B406" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D406" s="12" t="s">
-        <v>8</v>
+      <c r="D406" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B407" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7447,10 +7450,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B408" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7461,10 +7464,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B409" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
@@ -7475,10 +7478,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B410" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7489,10 +7492,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B411" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7503,10 +7506,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B412" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7517,10 +7520,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B413" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7531,10 +7534,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B414" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7545,10 +7548,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B415" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7559,38 +7562,38 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B416" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D416" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B417" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D417" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B418" s="8" t="s">
-        <v>374</v>
+        <v>1218</v>
+      </c>
+      <c r="B418" t="s">
+        <v>373</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
@@ -7601,10 +7604,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7615,10 +7618,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B420" s="8" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
@@ -7629,10 +7632,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
@@ -7643,68 +7646,68 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D422" s="9" t="s">
-        <v>9</v>
+      <c r="D422" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B423" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D423" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A424" s="6">
         <v>1045</v>
       </c>
-      <c r="B423" s="8" t="s">
+      <c r="B424" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C423" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D423" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A424">
-        <v>1043</v>
-      </c>
-      <c r="B424" t="s">
-        <v>412</v>
-      </c>
-      <c r="C424" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D424" t="s">
-        <v>8</v>
+      <c r="C424" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D424" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425">
+        <v>1043</v>
+      </c>
+      <c r="B425" t="s">
+        <v>412</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D425" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A426">
         <v>20340</v>
       </c>
-      <c r="B425" t="s">
+      <c r="B426" t="s">
         <v>413</v>
       </c>
-      <c r="C425" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D425" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A426">
-        <v>40146</v>
-      </c>
-      <c r="B426" t="s">
-        <v>414</v>
-      </c>
-      <c r="C426" s="14" t="s">
+      <c r="C426" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D426" t="s">
@@ -7713,24 +7716,24 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B427" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C427" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D427" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B428" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
@@ -7741,10 +7744,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B429" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
@@ -7755,66 +7758,66 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B430" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D430" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B431" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D431" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B432" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B433" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D433" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B434" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7825,24 +7828,24 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B435" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B436" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
@@ -7853,10 +7856,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B437" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
@@ -7867,38 +7870,38 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B438" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D438" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B439" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B440" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
@@ -7909,10 +7912,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B441" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7923,38 +7926,38 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B442" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B443" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D443" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B444" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
@@ -7965,24 +7968,24 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B445" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C445" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D445" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B446" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C446" s="14" t="s">
         <v>4</v>
@@ -7993,20 +7996,34 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
+        <v>1047</v>
+      </c>
+      <c r="B447" t="s">
+        <v>434</v>
+      </c>
+      <c r="C447" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D447" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A448">
         <v>20398</v>
       </c>
-      <c r="B447" t="s">
+      <c r="B448" t="s">
         <v>435</v>
       </c>
-      <c r="C447" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D447" t="s">
+      <c r="C448" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D448" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D447"/>
+  <autoFilter ref="A1:D448"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$448</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$449</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="456">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1387,6 +1387,9 @@
   </si>
   <si>
     <t>FERRETERIA CLAY</t>
+  </si>
+  <si>
+    <t>DEPO P.BAJA</t>
   </si>
 </sst>
 </file>
@@ -1742,7 +1745,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D448"/>
+  <dimension ref="A1:D449"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3082,38 +3085,38 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10107</v>
-      </c>
-      <c r="B96" t="s">
-        <v>94</v>
+        <v>1989</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>455</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" t="s">
-        <v>9</v>
+      <c r="D96" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>8</v>
+      <c r="D97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B98" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
@@ -3124,10 +3127,10 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B99" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
@@ -3138,94 +3141,94 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B100" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="13" t="s">
-        <v>5</v>
+      <c r="D100" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>8</v>
+      <c r="D101" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B102" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="13" t="s">
-        <v>5</v>
+      <c r="D102" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B103" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>8</v>
+      <c r="D103" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>342</v>
+        <v>10165</v>
+      </c>
+      <c r="B104" t="s">
+        <v>19</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="11" t="s">
+      <c r="D104" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B105" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="13" t="s">
-        <v>5</v>
+      <c r="D105" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>10168</v>
+        <v>10167</v>
       </c>
       <c r="B106" t="s">
-        <v>441</v>
+        <v>39</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
@@ -3236,24 +3239,24 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>10424</v>
+        <v>10168</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>441</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="17" t="s">
-        <v>9</v>
+      <c r="D107" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
@@ -3264,24 +3267,24 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="10" t="s">
-        <v>8</v>
+      <c r="D109" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B110" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
@@ -3292,150 +3295,150 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B111" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B112" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>8</v>
+      <c r="D112" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B113" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B114" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B115" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B116" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="D116" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B117" t="s">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D117" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B118" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="13" t="s">
-        <v>5</v>
+      <c r="D118" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B119" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="10" t="s">
-        <v>8</v>
+      <c r="D119" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B120" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D120" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3446,10 +3449,10 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B122" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3460,10 +3463,10 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B123" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
@@ -3474,10 +3477,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B124" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3488,10 +3491,10 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B125" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3502,38 +3505,38 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B126" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B127" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B128" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
@@ -3544,52 +3547,52 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B129" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="D129" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B130" t="s">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>5</v>
+      <c r="D130" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B131" t="s">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="13" t="s">
+      <c r="D131" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B132" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
@@ -3600,24 +3603,24 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B133" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="1" t="s">
-        <v>8</v>
+      <c r="D133" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
@@ -3628,10 +3631,10 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B135" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
@@ -3642,52 +3645,52 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B136" t="s">
-        <v>175</v>
+        <v>38</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="10" t="s">
+      <c r="D136" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B137" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="17" t="s">
-        <v>9</v>
+      <c r="D137" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B138" t="s">
-        <v>219</v>
+        <v>117</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="10" t="s">
-        <v>8</v>
+      <c r="D138" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B139" t="s">
-        <v>23</v>
+        <v>219</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
@@ -3698,52 +3701,52 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B140" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" t="s">
-        <v>9</v>
+      <c r="D140" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B141" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="10" t="s">
-        <v>8</v>
+      <c r="D141" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B142" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
@@ -3754,38 +3757,38 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B144" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="D144" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B145" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D145" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B146" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
@@ -3796,94 +3799,94 @@
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B147" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" t="s">
-        <v>9</v>
+      <c r="D147" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="1" t="s">
-        <v>8</v>
+      <c r="D148" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B149" t="s">
-        <v>362</v>
+        <v>145</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="14" t="s">
-        <v>5</v>
+      <c r="D149" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B150" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>8</v>
+      <c r="D150" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20192</v>
+        <v>20189</v>
       </c>
       <c r="B151" t="s">
-        <v>454</v>
+        <v>323</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20200</v>
+        <v>20192</v>
       </c>
       <c r="B152" t="s">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="13" t="s">
+      <c r="D152" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B153" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
@@ -3894,150 +3897,150 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B154" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="10" t="s">
-        <v>8</v>
+      <c r="D154" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B155" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="1" t="s">
-        <v>9</v>
+      <c r="D155" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B156" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="10" t="s">
-        <v>8</v>
+      <c r="D156" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B157" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="D157" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B158" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="10" t="s">
+      <c r="D158" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B159" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="13" t="s">
-        <v>5</v>
+      <c r="D159" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B160" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="10" t="s">
-        <v>8</v>
+      <c r="D160" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B161" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="13" t="s">
-        <v>5</v>
+      <c r="D161" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B162" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="3" t="s">
+      <c r="D162" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B163" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="13" t="s">
+      <c r="D163" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B164" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
@@ -4048,24 +4051,24 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B165" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="10" t="s">
-        <v>8</v>
+      <c r="D165" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B166" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
@@ -4076,108 +4079,108 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B167" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>5</v>
+      <c r="D167" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B168" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="10" t="s">
-        <v>8</v>
+      <c r="D168" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B169" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="D169" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B170" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="17" t="s">
-        <v>9</v>
+      <c r="D170" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B171" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>8</v>
+      <c r="D171" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B172" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="13" t="s">
-        <v>5</v>
+      <c r="D172" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B173" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="10" t="s">
-        <v>8</v>
+      <c r="D173" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B174" t="s">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
@@ -4188,206 +4191,206 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B175" t="s">
-        <v>392</v>
+        <v>90</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B176" t="s">
-        <v>196</v>
+        <v>392</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>8</v>
+      <c r="D176" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B177" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="13" t="s">
-        <v>5</v>
+      <c r="D177" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B178" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>8</v>
+      <c r="D178" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B179" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="13" t="s">
-        <v>5</v>
+      <c r="D179" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B180" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="1" t="s">
-        <v>8</v>
+      <c r="D180" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B181" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="3" t="s">
-        <v>5</v>
+      <c r="D181" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B182" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="1" t="s">
-        <v>9</v>
+      <c r="D182" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B183" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="17" t="s">
+      <c r="D183" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B184" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="1" t="s">
-        <v>8</v>
+      <c r="D184" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B185" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="3" t="s">
-        <v>5</v>
+      <c r="D185" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B186" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="1" t="s">
-        <v>8</v>
+      <c r="D186" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B187" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="10" t="s">
+      <c r="D187" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B188" t="s">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="13" t="s">
-        <v>5</v>
+      <c r="D188" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B189" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
@@ -4398,52 +4401,52 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B190" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="10" t="s">
-        <v>8</v>
+      <c r="D190" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B191" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="13" t="s">
-        <v>5</v>
+      <c r="D191" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B192" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="1" t="s">
-        <v>8</v>
+      <c r="D192" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B193" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4454,10 +4457,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B194" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
@@ -4468,10 +4471,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B195" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
@@ -4482,24 +4485,24 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B196" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="13" t="s">
-        <v>5</v>
+      <c r="D196" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B197" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4510,52 +4513,52 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B198" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>8</v>
+      <c r="D198" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B199" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="10" t="s">
+      <c r="D199" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B200" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="D200" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B201" t="s">
-        <v>205</v>
+        <v>126</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4566,10 +4569,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B202" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4580,38 +4583,38 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B203" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="13" t="s">
-        <v>5</v>
+      <c r="D203" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B204" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="1" t="s">
-        <v>8</v>
+      <c r="D204" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B205" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
@@ -4622,10 +4625,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B206" t="s">
-        <v>445</v>
+        <v>115</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
@@ -4636,66 +4639,66 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B207" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="13" t="s">
-        <v>5</v>
+      <c r="D207" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B208" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="1" t="s">
-        <v>8</v>
+      <c r="D208" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B209" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="13" t="s">
-        <v>5</v>
+      <c r="D209" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B210" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="10" t="s">
-        <v>8</v>
+      <c r="D210" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B211" t="s">
-        <v>208</v>
+        <v>45</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
@@ -4706,38 +4709,38 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B212" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="13" t="s">
-        <v>5</v>
+      <c r="D212" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B213" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="1" t="s">
-        <v>8</v>
+      <c r="D213" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B214" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4748,10 +4751,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B215" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4762,10 +4765,10 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B216" t="s">
-        <v>218</v>
+        <v>62</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
@@ -4776,52 +4779,52 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B217" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="10" t="s">
+      <c r="D217" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B218" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D218" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B219" t="s">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="10" t="s">
+      <c r="D219" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B220" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
@@ -4832,66 +4835,66 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B221" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="13" t="s">
-        <v>5</v>
+      <c r="D221" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B222" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="1" t="s">
-        <v>8</v>
+      <c r="D222" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B223" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="10" t="s">
+      <c r="D223" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B224" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="1" t="s">
+      <c r="D224" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B225" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
@@ -4902,66 +4905,66 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B226" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="10" t="s">
+      <c r="D226" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B227" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="D227" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B228" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="10" t="s">
+      <c r="D228" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B229" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="D229" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B230" t="s">
-        <v>324</v>
+        <v>157</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
@@ -4972,52 +4975,52 @@
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B231" s="8" t="s">
-        <v>338</v>
+        <v>20396</v>
+      </c>
+      <c r="B231" t="s">
+        <v>324</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="11" t="s">
-        <v>5</v>
+      <c r="D231" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B232" t="s">
-        <v>163</v>
+        <v>20397</v>
+      </c>
+      <c r="B232" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="1" t="s">
-        <v>8</v>
+      <c r="D232" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B233" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="13" t="s">
-        <v>5</v>
+      <c r="D233" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B234" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
@@ -5028,24 +5031,24 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B235" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>8</v>
+      <c r="D235" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B236" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
@@ -5056,24 +5059,24 @@
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B237" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="10" t="s">
+      <c r="D237" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B238" t="s">
-        <v>321</v>
+        <v>118</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
@@ -5084,66 +5087,66 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B239" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="1" t="s">
+      <c r="D239" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B240" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="13" t="s">
-        <v>5</v>
+      <c r="D240" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B241" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="10" t="s">
-        <v>8</v>
+      <c r="D241" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B242" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="13" t="s">
-        <v>5</v>
+      <c r="D242" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B243" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
@@ -5154,206 +5157,206 @@
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B244" t="s">
-        <v>396</v>
+        <v>161</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="19" t="s">
-        <v>8</v>
+      <c r="D244" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B245" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="10" t="s">
+      <c r="D245" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B246" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="1" t="s">
+      <c r="D246" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B247" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="13" t="s">
-        <v>5</v>
+      <c r="D247" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B248" t="s">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="1" t="s">
-        <v>8</v>
+      <c r="D248" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B249" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="10" t="s">
+      <c r="D249" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B250" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="3" t="s">
-        <v>5</v>
+      <c r="D250" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B251" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="1" t="s">
-        <v>8</v>
+      <c r="D251" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B252" t="s">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="11" t="s">
-        <v>5</v>
+      <c r="D252" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B253" t="s">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="13" t="s">
+      <c r="D253" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B254" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="1" t="s">
-        <v>8</v>
+      <c r="D254" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B255" s="8" t="s">
-        <v>341</v>
+        <v>50608</v>
+      </c>
+      <c r="B255" t="s">
+        <v>173</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="14" t="s">
-        <v>5</v>
+      <c r="D255" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B256" t="s">
-        <v>93</v>
+        <v>50611</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="16" t="s">
-        <v>8</v>
+      <c r="D256" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B257" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="10" t="s">
+      <c r="D257" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B258" t="s">
-        <v>199</v>
+        <v>107</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
@@ -5364,94 +5367,94 @@
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B259" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="1" t="s">
-        <v>5</v>
+      <c r="D259" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B260" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="14" t="s">
-        <v>8</v>
+      <c r="D260" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B261" t="s">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="1" t="s">
+      <c r="D261" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B262" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="10" t="s">
+      <c r="D262" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B263" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="1" t="s">
+      <c r="D263" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B264" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="13" t="s">
-        <v>5</v>
+      <c r="D264" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B265" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
@@ -5462,24 +5465,24 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B266" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="1" t="s">
-        <v>8</v>
+      <c r="D266" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B267" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
@@ -5490,80 +5493,80 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B268" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="17" t="s">
-        <v>9</v>
+      <c r="D268" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B269" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="10" t="s">
-        <v>8</v>
+      <c r="D269" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B270" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="1" t="s">
+      <c r="D270" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B271" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="13" t="s">
-        <v>5</v>
+      <c r="D271" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B272" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="10" t="s">
-        <v>8</v>
+      <c r="D272" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B273" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
@@ -5574,66 +5577,66 @@
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B274" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="1" t="s">
+      <c r="D274" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B275" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="17" t="s">
-        <v>9</v>
+      <c r="D275" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B276" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="13" t="s">
-        <v>5</v>
+      <c r="D276" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B277" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="10" t="s">
-        <v>8</v>
+      <c r="D277" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B278" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
@@ -5644,24 +5647,24 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B279" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="1" t="s">
+      <c r="D279" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B280" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
@@ -5672,136 +5675,136 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B281" t="s">
-        <v>358</v>
+        <v>231</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="11" t="s">
+      <c r="D281" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B282" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B283" s="8" t="s">
-        <v>343</v>
+        <v>50831</v>
+      </c>
+      <c r="B283" t="s">
+        <v>344</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D283" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D285" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>50231</v>
+        <v>50230</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B287" t="s">
-        <v>232</v>
+        <v>50231</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="13" t="s">
-        <v>5</v>
+      <c r="D287" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B288" t="s">
-        <v>322</v>
+        <v>232</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="11" t="s">
-        <v>9</v>
+      <c r="D288" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B289" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="13" t="s">
-        <v>5</v>
+      <c r="D289" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B290" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
@@ -5812,80 +5815,80 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B291" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="10" t="s">
-        <v>8</v>
+      <c r="D291" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B292" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="3" t="s">
-        <v>5</v>
+      <c r="D292" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B293" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="1" t="s">
-        <v>8</v>
+      <c r="D293" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B294" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="13" t="s">
-        <v>5</v>
+      <c r="D294" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B295" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="1" t="s">
-        <v>8</v>
+      <c r="D295" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B296" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5896,10 +5899,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B297" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5910,10 +5913,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B298" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5924,10 +5927,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B299" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5938,10 +5941,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B300" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5952,66 +5955,66 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B301" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="13" t="s">
-        <v>5</v>
+      <c r="D301" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B302" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="10" t="s">
-        <v>8</v>
+      <c r="D302" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B303" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="1" t="s">
+      <c r="D303" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B304" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="13" t="s">
-        <v>5</v>
+      <c r="D304" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B305" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -6022,80 +6025,80 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B306" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="1" t="s">
+      <c r="D306" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B307" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B308" s="8" t="s">
-        <v>331</v>
+        <v>60169</v>
+      </c>
+      <c r="B308" t="s">
+        <v>250</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="11" t="s">
-        <v>5</v>
+      <c r="D308" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B309" t="s">
-        <v>251</v>
+        <v>60170</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="1" t="s">
-        <v>8</v>
+      <c r="D309" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B310" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="13" t="s">
-        <v>5</v>
+      <c r="D310" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B311" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
@@ -6106,52 +6109,52 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B312" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="1" t="s">
-        <v>8</v>
+      <c r="D312" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B313" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="10" t="s">
+      <c r="D313" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B314" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="1" t="s">
+      <c r="D314" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B315" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
@@ -6162,24 +6165,24 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B316" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="10" t="s">
-        <v>8</v>
+      <c r="D316" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B317" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
@@ -6190,38 +6193,38 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B318" s="18" t="s">
-        <v>400</v>
+        <v>60192</v>
+      </c>
+      <c r="B318" t="s">
+        <v>259</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D318" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B319" t="s">
-        <v>260</v>
+        <v>60194</v>
+      </c>
+      <c r="B319" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D319" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B320" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
@@ -6232,10 +6235,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B321" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
@@ -6246,52 +6249,52 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B322" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" t="s">
-        <v>9</v>
+      <c r="D322" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B323" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="13" t="s">
-        <v>5</v>
+      <c r="D323" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B324" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="1" t="s">
-        <v>8</v>
+      <c r="D324" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B325" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
@@ -6302,10 +6305,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B326" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
@@ -6316,192 +6319,192 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B327" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="10" t="s">
+      <c r="D327" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B328" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="1" t="s">
+      <c r="D328" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B329" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="10" t="s">
+      <c r="D329" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B330" t="s">
-        <v>442</v>
+        <v>270</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D330" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B331" t="s">
-        <v>271</v>
+        <v>442</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D331" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B332" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="1" t="s">
+      <c r="D332" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B333" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="10" t="s">
-        <v>5</v>
+      <c r="D333" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B334" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="17" t="s">
-        <v>9</v>
+      <c r="D334" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B335" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="10" t="s">
-        <v>8</v>
+      <c r="D335" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B336" s="8" t="s">
-        <v>332</v>
+        <v>60230</v>
+      </c>
+      <c r="B336" t="s">
+        <v>275</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="7" t="s">
-        <v>9</v>
+      <c r="D336" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D337" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D338" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D339" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6512,10 +6515,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60247</v>
+        <v>60246</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6526,10 +6529,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B342" s="18" t="s">
-        <v>399</v>
+        <v>60247</v>
+      </c>
+      <c r="B342" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6540,38 +6543,38 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B343" s="8" t="s">
-        <v>333</v>
+        <v>60249</v>
+      </c>
+      <c r="B343" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="11" t="s">
-        <v>8</v>
+      <c r="D343" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B344" t="s">
-        <v>276</v>
+        <v>60250</v>
+      </c>
+      <c r="B344" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="1" t="s">
+      <c r="D344" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B345" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
@@ -6582,24 +6585,24 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B346" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B347" t="s">
-        <v>451</v>
+        <v>278</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6610,66 +6613,66 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B348" s="8" t="s">
-        <v>337</v>
+        <v>60258</v>
+      </c>
+      <c r="B348" t="s">
+        <v>451</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="11" t="s">
-        <v>8</v>
+      <c r="D348" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B349" t="s">
-        <v>279</v>
+        <v>60266</v>
+      </c>
+      <c r="B349" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="10" t="s">
+      <c r="D349" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B350" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="1" t="s">
-        <v>9</v>
+      <c r="D350" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B351" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B352" t="s">
-        <v>372</v>
+        <v>281</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6680,10 +6683,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B353" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6694,10 +6697,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B354" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6708,38 +6711,38 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B355" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="13" t="s">
+      <c r="D355" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B356" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="1" t="s">
-        <v>5</v>
+      <c r="D356" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B357" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6750,66 +6753,66 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B358" s="8" t="s">
-        <v>330</v>
+        <v>60280</v>
+      </c>
+      <c r="B358" t="s">
+        <v>286</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="11" t="s">
-        <v>9</v>
+      <c r="D358" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B359" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D359" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B360" t="s">
-        <v>370</v>
+        <v>60282</v>
+      </c>
+      <c r="B360" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="1" t="s">
-        <v>8</v>
+      <c r="D360" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B361" s="8" t="s">
-        <v>329</v>
+        <v>60283</v>
+      </c>
+      <c r="B361" t="s">
+        <v>370</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="9" t="s">
-        <v>5</v>
+      <c r="D361" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>444</v>
+        <v>329</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6820,10 +6823,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B363" s="8" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6834,52 +6837,52 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B364" t="s">
-        <v>369</v>
+        <v>60286</v>
+      </c>
+      <c r="B364" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="12" t="s">
+      <c r="D364" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B365" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B366" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B367" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6890,10 +6893,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B368" s="18" t="s">
-        <v>391</v>
+        <v>60291</v>
+      </c>
+      <c r="B368" t="s">
+        <v>368</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6904,10 +6907,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60293</v>
+        <v>60292</v>
       </c>
       <c r="B369" s="18" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6918,10 +6921,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B370" t="s">
-        <v>382</v>
+        <v>60293</v>
+      </c>
+      <c r="B370" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6932,10 +6935,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B371" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6946,10 +6949,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B372" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6960,10 +6963,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B373" s="18" t="s">
-        <v>401</v>
+        <v>60299</v>
+      </c>
+      <c r="B373" t="s">
+        <v>379</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6974,10 +6977,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B374" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6988,10 +6991,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>60305</v>
+        <v>60303</v>
       </c>
       <c r="B375" s="18" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -7002,24 +7005,24 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>60306</v>
+        <v>60305</v>
       </c>
       <c r="B376" s="18" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D376" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>60308</v>
+        <v>60306</v>
       </c>
       <c r="B377" s="18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -7030,38 +7033,38 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B378" t="s">
-        <v>394</v>
+        <v>60308</v>
+      </c>
+      <c r="B378" s="18" t="s">
+        <v>452</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D378" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B379" t="s">
-        <v>287</v>
+        <v>394</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="15" t="s">
-        <v>5</v>
+      <c r="D379" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B380" t="s">
-        <v>405</v>
+        <v>287</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -7072,24 +7075,24 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B381" t="s">
-        <v>288</v>
+        <v>405</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="12" t="s">
-        <v>8</v>
+      <c r="D381" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B382" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -7100,10 +7103,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B383" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -7114,10 +7117,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B384" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7128,52 +7131,52 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B385" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="15" t="s">
-        <v>5</v>
+      <c r="D385" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B386" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="12" t="s">
-        <v>8</v>
+      <c r="D386" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B387" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="15" t="s">
-        <v>5</v>
+      <c r="D387" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B388" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7184,94 +7187,94 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B389" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="12" t="s">
-        <v>8</v>
+      <c r="D389" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B390" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D390" s="15" t="s">
-        <v>5</v>
+      <c r="D390" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B391" t="s">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D391" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B392" t="s">
-        <v>298</v>
+        <v>409</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D392" s="12" t="s">
+      <c r="D392" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B393" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D393" s="15" t="s">
-        <v>5</v>
+      <c r="D393" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B394" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D394" s="9" t="s">
-        <v>9</v>
+      <c r="D394" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B395" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7282,38 +7285,38 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B396" t="s">
-        <v>410</v>
+        <v>325</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D396" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>70638</v>
+        <v>70116</v>
       </c>
       <c r="B397" t="s">
-        <v>300</v>
+        <v>410</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D397" s="12" t="s">
+      <c r="D397" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B398" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7324,10 +7327,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B399" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7338,10 +7341,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B400" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7352,10 +7355,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B401" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7366,10 +7369,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B402" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7380,52 +7383,52 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B403" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D403" s="15" t="s">
-        <v>5</v>
+      <c r="D403" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B404" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D404" s="12" t="s">
-        <v>8</v>
+      <c r="D404" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B405" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D405" s="9" t="s">
+      <c r="D405" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B406" s="8" t="s">
-        <v>336</v>
+        <v>90622</v>
+      </c>
+      <c r="B406" t="s">
+        <v>327</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7436,24 +7439,24 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B407" t="s">
-        <v>308</v>
+        <v>90631</v>
+      </c>
+      <c r="B407" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D407" s="12" t="s">
-        <v>8</v>
+      <c r="D407" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B408" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7464,10 +7467,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B409" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
@@ -7478,10 +7481,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B410" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7492,10 +7495,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B411" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7506,10 +7509,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B412" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7520,10 +7523,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B413" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7534,10 +7537,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B414" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7548,10 +7551,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B415" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7562,10 +7565,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B416" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7576,38 +7579,38 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B417" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D417" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B418" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D418" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B419" s="8" t="s">
-        <v>374</v>
+        <v>1218</v>
+      </c>
+      <c r="B419" t="s">
+        <v>373</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7618,10 +7621,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B420" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
@@ -7632,10 +7635,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
@@ -7646,10 +7649,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>4</v>
@@ -7660,68 +7663,68 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D423" s="9" t="s">
-        <v>9</v>
+      <c r="D423" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B424" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D424" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A425" s="6">
         <v>1045</v>
       </c>
-      <c r="B424" s="8" t="s">
+      <c r="B425" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C424" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D424" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A425">
-        <v>1043</v>
-      </c>
-      <c r="B425" t="s">
-        <v>412</v>
-      </c>
-      <c r="C425" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D425" t="s">
-        <v>8</v>
+      <c r="C425" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D425" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426">
+        <v>1043</v>
+      </c>
+      <c r="B426" t="s">
+        <v>412</v>
+      </c>
+      <c r="C426" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D426" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A427">
         <v>20340</v>
       </c>
-      <c r="B426" t="s">
+      <c r="B427" t="s">
         <v>413</v>
       </c>
-      <c r="C426" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D426" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A427">
-        <v>40146</v>
-      </c>
-      <c r="B427" t="s">
-        <v>414</v>
-      </c>
-      <c r="C427" s="14" t="s">
+      <c r="C427" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D427" t="s">
@@ -7730,24 +7733,24 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B428" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C428" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D428" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B429" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>4</v>
@@ -7758,10 +7761,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B430" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
@@ -7772,66 +7775,66 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B431" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D431" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B432" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B433" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D433" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B434" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D434" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B435" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
@@ -7842,24 +7845,24 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B436" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B437" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
@@ -7870,10 +7873,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B438" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
@@ -7884,38 +7887,38 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B439" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B440" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D440" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B441" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7926,10 +7929,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B442" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
@@ -7940,38 +7943,38 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B443" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D443" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B444" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D444" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B445" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C445" s="14" t="s">
         <v>4</v>
@@ -7982,24 +7985,24 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B446" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C446" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D446" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B447" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C447" s="14" t="s">
         <v>4</v>
@@ -8010,20 +8013,34 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448">
+        <v>1047</v>
+      </c>
+      <c r="B448" t="s">
+        <v>434</v>
+      </c>
+      <c r="C448" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D448" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A449">
         <v>20398</v>
       </c>
-      <c r="B448" t="s">
+      <c r="B449" t="s">
         <v>435</v>
       </c>
-      <c r="C448" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D448" t="s">
+      <c r="C449" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D449" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D448"/>
+  <autoFilter ref="A1:D449"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$449</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$451</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="459">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1390,6 +1390,15 @@
   </si>
   <si>
     <t>DEPO P.BAJA</t>
+  </si>
+  <si>
+    <t>F. RAUCH ADRIAN</t>
+  </si>
+  <si>
+    <t>FERRETERIA ANIBAL</t>
+  </si>
+  <si>
+    <t>FERRETERIA VALVERDE</t>
   </si>
 </sst>
 </file>
@@ -1745,7 +1754,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D449"/>
+  <dimension ref="A1:D452"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6090,7 +6099,7 @@
         <v>4</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6580,7 +6589,7 @@
         <v>4</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7313,38 +7322,38 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>70638</v>
+        <v>70117</v>
       </c>
       <c r="B398" t="s">
-        <v>300</v>
+        <v>457</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D398" s="12" t="s">
-        <v>8</v>
+      <c r="D398" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>70639</v>
+        <v>70118</v>
       </c>
       <c r="B399" t="s">
-        <v>301</v>
+        <v>458</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D399" s="12" t="s">
-        <v>8</v>
+      <c r="D399" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>70640</v>
+        <v>70638</v>
       </c>
       <c r="B400" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7355,10 +7364,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>70642</v>
+        <v>70639</v>
       </c>
       <c r="B401" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7369,10 +7378,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>90504</v>
+        <v>70640</v>
       </c>
       <c r="B402" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7383,10 +7392,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>90509</v>
+        <v>70642</v>
       </c>
       <c r="B403" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7397,94 +7406,94 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90602</v>
+        <v>90504</v>
       </c>
       <c r="B404" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D404" s="15" t="s">
-        <v>5</v>
+      <c r="D404" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90621</v>
+        <v>90509</v>
       </c>
       <c r="B405" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D405" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90622</v>
+        <v>90602</v>
       </c>
       <c r="B406" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D406" s="9" t="s">
+      <c r="D406" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B407" s="8" t="s">
-        <v>336</v>
+        <v>90621</v>
+      </c>
+      <c r="B407" t="s">
+        <v>307</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D407" s="9" t="s">
+      <c r="D407" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90658</v>
+        <v>90622</v>
       </c>
       <c r="B408" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D408" s="12" t="s">
-        <v>8</v>
+      <c r="D408" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90660</v>
-      </c>
-      <c r="B409" t="s">
-        <v>309</v>
+        <v>90631</v>
+      </c>
+      <c r="B409" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D409" s="12" t="s">
-        <v>8</v>
+      <c r="D409" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90668</v>
+        <v>90658</v>
       </c>
       <c r="B410" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7495,10 +7504,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90671</v>
+        <v>90660</v>
       </c>
       <c r="B411" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7509,10 +7518,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90679</v>
+        <v>90668</v>
       </c>
       <c r="B412" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7523,10 +7532,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90683</v>
+        <v>90671</v>
       </c>
       <c r="B413" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7537,10 +7546,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>90705</v>
+        <v>90679</v>
       </c>
       <c r="B414" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7551,10 +7560,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>90706</v>
+        <v>90683</v>
       </c>
       <c r="B415" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7565,10 +7574,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>90708</v>
+        <v>90705</v>
       </c>
       <c r="B416" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7579,10 +7588,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="B417" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
@@ -7593,24 +7602,24 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>90713</v>
+        <v>90708</v>
       </c>
       <c r="B418" t="s">
-        <v>393</v>
+        <v>316</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D418" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>1218</v>
+        <v>90709</v>
       </c>
       <c r="B419" t="s">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7621,24 +7630,24 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B420" s="8" t="s">
-        <v>374</v>
+        <v>90713</v>
+      </c>
+      <c r="B420" t="s">
+        <v>393</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D420" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B421" s="8" t="s">
-        <v>375</v>
+        <v>1218</v>
+      </c>
+      <c r="B421" t="s">
+        <v>373</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
@@ -7649,10 +7658,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6">
-        <v>1817</v>
+        <v>1959</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>4</v>
@@ -7663,10 +7672,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6">
-        <v>5737</v>
+        <v>5625</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>4</v>
@@ -7677,108 +7686,108 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6">
-        <v>60295</v>
+        <v>1817</v>
       </c>
       <c r="B424" s="8" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D424" s="9" t="s">
-        <v>9</v>
+      <c r="D424" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B425" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D425" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A426" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B426" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D426" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A427" s="6">
         <v>1045</v>
       </c>
-      <c r="B425" s="8" t="s">
+      <c r="B427" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C425" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D425" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A426">
+      <c r="C427" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D427" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A428">
         <v>1043</v>
       </c>
-      <c r="B426" t="s">
+      <c r="B428" t="s">
         <v>412</v>
       </c>
-      <c r="C426" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D426" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A427">
+      <c r="C428" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D428" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A429">
         <v>20340</v>
       </c>
-      <c r="B427" t="s">
+      <c r="B429" t="s">
         <v>413</v>
       </c>
-      <c r="C427" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D427" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A428">
-        <v>40146</v>
-      </c>
-      <c r="B428" t="s">
-        <v>414</v>
-      </c>
-      <c r="C428" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D428" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A429">
-        <v>60260</v>
-      </c>
-      <c r="B429" t="s">
-        <v>415</v>
-      </c>
-      <c r="C429" s="14" t="s">
+      <c r="C429" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D429" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>1017</v>
+        <v>40146</v>
       </c>
       <c r="B430" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C430" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D430" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>60300</v>
+        <v>60260</v>
       </c>
       <c r="B431" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
@@ -7789,24 +7798,24 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>20191</v>
+        <v>1017</v>
       </c>
       <c r="B432" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>20399</v>
+        <v>60300</v>
       </c>
       <c r="B433" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
@@ -7817,10 +7826,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>60240</v>
+        <v>20191</v>
       </c>
       <c r="B434" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7831,10 +7840,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>60244</v>
+        <v>20399</v>
       </c>
       <c r="B435" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
@@ -7845,80 +7854,80 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>60248</v>
+        <v>60240</v>
       </c>
       <c r="B436" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>60288</v>
+        <v>60244</v>
       </c>
       <c r="B437" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>90714</v>
+        <v>60248</v>
       </c>
       <c r="B438" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D438" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>1014</v>
+        <v>60288</v>
       </c>
       <c r="B439" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>1016</v>
+        <v>90714</v>
       </c>
       <c r="B440" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D440" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>60301</v>
+        <v>1014</v>
       </c>
       <c r="B441" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7929,24 +7938,24 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>1041</v>
+        <v>1016</v>
       </c>
       <c r="B442" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>971</v>
+        <v>60301</v>
       </c>
       <c r="B443" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
@@ -7957,24 +7966,24 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>50610</v>
+        <v>1041</v>
       </c>
       <c r="B444" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D444" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>943</v>
+        <v>971</v>
       </c>
       <c r="B445" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C445" s="14" t="s">
         <v>4</v>
@@ -7985,62 +7994,104 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>20306</v>
+        <v>50610</v>
       </c>
       <c r="B446" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C446" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D446" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>90630</v>
+        <v>943</v>
       </c>
       <c r="B447" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C447" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D447" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>1047</v>
+        <v>20306</v>
       </c>
       <c r="B448" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C448" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D448" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="449" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449">
+        <v>90630</v>
+      </c>
+      <c r="B449" t="s">
+        <v>433</v>
+      </c>
+      <c r="C449" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D449" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>1047</v>
+      </c>
+      <c r="B450" t="s">
+        <v>434</v>
+      </c>
+      <c r="C450" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D450" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A451">
         <v>20398</v>
       </c>
-      <c r="B449" t="s">
+      <c r="B451" t="s">
         <v>435</v>
       </c>
-      <c r="C449" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D449" t="s">
-        <v>8</v>
+      <c r="C451" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D451" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>50226</v>
+      </c>
+      <c r="B452" t="s">
+        <v>456</v>
+      </c>
+      <c r="C452" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D452" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D449"/>
+  <autoFilter ref="A1:D451"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$451</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$452</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="461">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1399,12 +1399,18 @@
   </si>
   <si>
     <t>FERRETERIA VALVERDE</t>
+  </si>
+  <si>
+    <t>FERRETERIA SENEGAL</t>
+  </si>
+  <si>
+    <t>CONSUMIDOR FINAL 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1754,7 +1760,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D452"/>
+  <dimension ref="A1:D454"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1805,25 +1811,25 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>5</v>
+      <c r="A4" s="1">
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -1834,10 +1840,10 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>206</v>
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -1848,24 +1854,24 @@
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>138</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -1876,10 +1882,10 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -1890,10 +1896,10 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <v>233</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>449</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1904,10 +1910,10 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>449</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1918,10 +1924,10 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1932,10 +1938,10 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1946,10 +1952,10 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B14" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1960,10 +1966,10 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>207</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1974,10 +1980,10 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>916</v>
+        <v>308</v>
       </c>
       <c r="B16" t="s">
-        <v>406</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1988,10 +1994,10 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>406</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -2002,24 +2008,24 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B18" t="s">
-        <v>384</v>
+        <v>190</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>933</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>403</v>
+        <v>921</v>
+      </c>
+      <c r="B19" t="s">
+        <v>384</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -2030,52 +2036,52 @@
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>936</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
+        <v>933</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>403</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B21" t="s">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>8</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -2086,38 +2092,38 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D24" t="s">
-        <v>5</v>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B25" t="s">
-        <v>195</v>
+        <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>8</v>
+      <c r="D25" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>195</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -2128,10 +2134,10 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -2142,52 +2148,52 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
+      <c r="D29" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>8</v>
+      <c r="D30" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B31" t="s">
-        <v>448</v>
+        <v>125</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -2198,10 +2204,10 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
+        <v>448</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -2212,38 +2218,38 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
+      <c r="D33" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>8</v>
+      <c r="D34" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -2254,24 +2260,24 @@
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>5</v>
+      <c r="D36" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -2282,66 +2288,66 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>8</v>
+      <c r="D38" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B39" t="s">
-        <v>221</v>
+        <v>85</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D39" t="s">
-        <v>9</v>
+      <c r="D39" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>5</v>
+      <c r="D40" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>8</v>
+      <c r="D41" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B42" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -2352,10 +2358,10 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -2366,24 +2372,24 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -2394,66 +2400,66 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B46" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>990</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>404</v>
+        <v>989</v>
+      </c>
+      <c r="B47" t="s">
+        <v>186</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D48" s="20" t="s">
-        <v>8</v>
+      <c r="D48" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>992</v>
-      </c>
-      <c r="B49" t="s">
-        <v>65</v>
+        <v>991</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>407</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -2464,10 +2470,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -2478,10 +2484,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B52" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -2492,10 +2498,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -2506,38 +2512,38 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B54" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D54" t="s">
-        <v>9</v>
+      <c r="D54" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B55" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>8</v>
+      <c r="D55" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>217</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -2548,10 +2554,10 @@
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
@@ -2562,10 +2568,10 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B58" t="s">
-        <v>443</v>
+        <v>46</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
@@ -2576,38 +2582,38 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>443</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B60" t="s">
-        <v>209</v>
+        <v>112</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>8</v>
+      <c r="D60" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
@@ -2618,24 +2624,24 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D62" t="s">
-        <v>9</v>
+      <c r="D62" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B63" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
@@ -2646,24 +2652,24 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>8</v>
+      <c r="D64" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B65" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
@@ -2674,10 +2680,10 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>1018</v>
-      </c>
-      <c r="B66" s="18" t="s">
-        <v>390</v>
+        <v>1015</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
@@ -2688,52 +2694,52 @@
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>1020</v>
-      </c>
-      <c r="B67" t="s">
-        <v>354</v>
+        <v>1018</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>390</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D67" s="11" t="s">
-        <v>5</v>
+      <c r="D67" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B68" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="D68" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B69" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B70" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
@@ -2744,136 +2750,136 @@
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B71" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B72" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D72" s="14" t="s">
-        <v>5</v>
+      <c r="D72" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B73" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B74" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D74" s="14" t="s">
-        <v>8</v>
+      <c r="D74" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B75" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="11" t="s">
-        <v>5</v>
+      <c r="D75" s="14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B76" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>1031</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>340</v>
+        <v>1030</v>
+      </c>
+      <c r="B77" t="s">
+        <v>348</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>1032</v>
-      </c>
-      <c r="B78" t="s">
-        <v>361</v>
+        <v>1031</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B79" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>1034</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>365</v>
+        <v>1033</v>
+      </c>
+      <c r="B80" t="s">
+        <v>349</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
@@ -2884,10 +2890,10 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
@@ -2898,10 +2904,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>1036</v>
-      </c>
-      <c r="B82" t="s">
-        <v>350</v>
+        <v>1035</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
@@ -2912,10 +2918,10 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B83" t="s">
-        <v>447</v>
+        <v>350</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
@@ -2926,10 +2932,10 @@
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B84" t="s">
-        <v>345</v>
+        <v>447</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
@@ -2940,10 +2946,10 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B85" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
@@ -2954,66 +2960,66 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B86" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B87" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B88" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B89" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B90" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
@@ -3024,24 +3030,24 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>1050</v>
-      </c>
-      <c r="B91" s="18" t="s">
-        <v>446</v>
+        <v>1049</v>
+      </c>
+      <c r="B91" t="s">
+        <v>397</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
@@ -3052,38 +3058,38 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>1416</v>
-      </c>
-      <c r="B93" t="s">
-        <v>212</v>
+        <v>1051</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>437</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>8</v>
+      <c r="D93" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>1987</v>
+        <v>1416</v>
       </c>
       <c r="B94" t="s">
-        <v>439</v>
+        <v>212</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B95" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
@@ -3094,10 +3100,10 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>1989</v>
-      </c>
-      <c r="B96" s="18" t="s">
-        <v>455</v>
+        <v>1988</v>
+      </c>
+      <c r="B96" t="s">
+        <v>440</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
@@ -3108,38 +3114,38 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10107</v>
-      </c>
-      <c r="B97" t="s">
-        <v>94</v>
+        <v>1989</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>455</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" t="s">
-        <v>9</v>
+      <c r="D97" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B98" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>8</v>
+      <c r="D98" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B99" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
@@ -3150,10 +3156,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B100" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
@@ -3164,94 +3170,94 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B101" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D101" s="13" t="s">
-        <v>5</v>
+      <c r="D101" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>8</v>
+      <c r="D102" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B103" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="13" t="s">
-        <v>5</v>
+      <c r="D103" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B104" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>8</v>
+      <c r="D104" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>342</v>
+        <v>10165</v>
+      </c>
+      <c r="B105" t="s">
+        <v>19</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D105" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B106" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="13" t="s">
-        <v>5</v>
+      <c r="D106" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>10168</v>
+        <v>10167</v>
       </c>
       <c r="B107" t="s">
-        <v>441</v>
+        <v>39</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
@@ -3262,24 +3268,24 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>10424</v>
+        <v>10168</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>441</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="17" t="s">
-        <v>9</v>
+      <c r="D108" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
@@ -3290,24 +3296,24 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B110" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="10" t="s">
-        <v>8</v>
+      <c r="D110" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B111" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3318,150 +3324,150 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B112" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B113" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>8</v>
+      <c r="D113" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B114" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B115" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B116" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B117" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="D117" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B118" t="s">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="13" t="s">
-        <v>5</v>
+      <c r="D119" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B120" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="10" t="s">
-        <v>8</v>
+      <c r="D120" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B121" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3472,10 +3478,10 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B123" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
@@ -3486,10 +3492,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B124" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3500,10 +3506,10 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B125" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3514,10 +3520,10 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B126" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
@@ -3528,38 +3534,38 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B127" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="D127" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B128" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B129" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
@@ -3570,52 +3576,52 @@
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B130" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="D130" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B131" t="s">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>5</v>
+      <c r="D131" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B132" t="s">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="13" t="s">
+      <c r="D132" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B133" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
@@ -3626,24 +3632,24 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B134" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>8</v>
+      <c r="D134" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B135" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
@@ -3654,10 +3660,10 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
@@ -3668,52 +3674,52 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B137" t="s">
-        <v>175</v>
+        <v>38</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="10" t="s">
+      <c r="D137" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B138" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="17" t="s">
-        <v>9</v>
+      <c r="D138" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B139" t="s">
-        <v>219</v>
+        <v>117</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="10" t="s">
-        <v>8</v>
+      <c r="D139" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B140" t="s">
-        <v>23</v>
+        <v>219</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
@@ -3724,52 +3730,52 @@
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B141" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" t="s">
-        <v>9</v>
+      <c r="D141" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B142" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="10" t="s">
-        <v>8</v>
+      <c r="D142" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B143" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B144" t="s">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
@@ -3780,38 +3786,38 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B145" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="10" t="s">
+      <c r="D145" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B146" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D146" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B147" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
@@ -3822,94 +3828,94 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B148" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" t="s">
-        <v>9</v>
+      <c r="D148" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B149" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>8</v>
+      <c r="D149" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B150" t="s">
-        <v>362</v>
+        <v>145</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="14" t="s">
-        <v>5</v>
+      <c r="D150" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B151" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>8</v>
+      <c r="D151" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20192</v>
+        <v>20189</v>
       </c>
       <c r="B152" t="s">
-        <v>454</v>
+        <v>323</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20200</v>
+        <v>20192</v>
       </c>
       <c r="B153" t="s">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="13" t="s">
+      <c r="D153" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B154" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
@@ -3920,150 +3926,150 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B155" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="10" t="s">
-        <v>8</v>
+      <c r="D155" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B156" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="1" t="s">
-        <v>9</v>
+      <c r="D156" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B157" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="10" t="s">
-        <v>8</v>
+      <c r="D157" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B158" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D158" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B159" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="10" t="s">
+      <c r="D159" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B160" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="13" t="s">
-        <v>5</v>
+      <c r="D160" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B161" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="10" t="s">
-        <v>8</v>
+      <c r="D161" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B162" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="13" t="s">
-        <v>5</v>
+      <c r="D162" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B163" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="D163" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B164" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="13" t="s">
+      <c r="D164" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B165" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
@@ -4074,24 +4080,24 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B166" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="10" t="s">
-        <v>8</v>
+      <c r="D166" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B167" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
@@ -4102,108 +4108,108 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B168" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="13" t="s">
-        <v>5</v>
+      <c r="D168" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B169" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="10" t="s">
-        <v>8</v>
+      <c r="D169" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B170" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="D170" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B171" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="17" t="s">
-        <v>9</v>
+      <c r="D171" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B172" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>8</v>
+      <c r="D172" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B173" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="13" t="s">
-        <v>5</v>
+      <c r="D173" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B174" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="10" t="s">
-        <v>8</v>
+      <c r="D174" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B175" t="s">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
@@ -4214,206 +4220,206 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B176" t="s">
-        <v>392</v>
+        <v>90</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B177" t="s">
-        <v>196</v>
+        <v>392</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="1" t="s">
-        <v>8</v>
+      <c r="D177" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B178" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="13" t="s">
-        <v>5</v>
+      <c r="D178" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B179" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>8</v>
+      <c r="D179" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B180" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="13" t="s">
-        <v>5</v>
+      <c r="D180" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B181" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="1" t="s">
-        <v>8</v>
+      <c r="D181" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B182" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="3" t="s">
-        <v>5</v>
+      <c r="D182" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B183" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="1" t="s">
-        <v>9</v>
+      <c r="D183" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B184" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="17" t="s">
+      <c r="D184" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B185" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="1" t="s">
-        <v>8</v>
+      <c r="D185" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B186" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="3" t="s">
-        <v>5</v>
+      <c r="D186" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B187" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="1" t="s">
-        <v>8</v>
+      <c r="D187" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B188" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="10" t="s">
+      <c r="D188" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B189" t="s">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="13" t="s">
-        <v>5</v>
+      <c r="D189" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B190" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4424,52 +4430,52 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B191" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="10" t="s">
-        <v>8</v>
+      <c r="D191" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B192" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="13" t="s">
-        <v>5</v>
+      <c r="D192" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B193" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>8</v>
+      <c r="D193" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B194" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
@@ -4480,10 +4486,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B195" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
@@ -4494,10 +4500,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B196" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4508,24 +4514,24 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B197" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="13" t="s">
-        <v>5</v>
+      <c r="D197" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B198" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
@@ -4536,52 +4542,52 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B199" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="1" t="s">
-        <v>8</v>
+      <c r="D199" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B200" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="10" t="s">
+      <c r="D200" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B201" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="D201" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B202" t="s">
-        <v>205</v>
+        <v>126</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4592,10 +4598,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B203" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
@@ -4606,38 +4612,38 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B204" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="13" t="s">
-        <v>5</v>
+      <c r="D204" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B205" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="1" t="s">
-        <v>8</v>
+      <c r="D205" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B206" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
@@ -4648,10 +4654,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B207" t="s">
-        <v>445</v>
+        <v>115</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
@@ -4662,66 +4668,66 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B208" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="13" t="s">
-        <v>5</v>
+      <c r="D208" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B209" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="1" t="s">
-        <v>8</v>
+      <c r="D209" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B210" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="13" t="s">
-        <v>5</v>
+      <c r="D210" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B211" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="10" t="s">
-        <v>8</v>
+      <c r="D211" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B212" t="s">
-        <v>208</v>
+        <v>45</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
@@ -4732,38 +4738,38 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B213" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="13" t="s">
-        <v>5</v>
+      <c r="D213" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B214" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="1" t="s">
-        <v>8</v>
+      <c r="D214" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B215" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4774,10 +4780,10 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B216" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
@@ -4788,10 +4794,10 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B217" t="s">
-        <v>218</v>
+        <v>62</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
@@ -4802,52 +4808,52 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B218" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="10" t="s">
+      <c r="D218" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B219" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="D219" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="10" t="s">
+      <c r="D220" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B221" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
@@ -4858,66 +4864,66 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B222" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="13" t="s">
-        <v>5</v>
+      <c r="D222" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B223" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="1" t="s">
-        <v>8</v>
+      <c r="D223" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B224" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="10" t="s">
+      <c r="D224" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B225" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="D225" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B226" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
@@ -4928,66 +4934,66 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B227" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="10" t="s">
+      <c r="D227" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B228" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="1" t="s">
+      <c r="D228" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B229" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="10" t="s">
+      <c r="D229" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B230" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="D230" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B231" t="s">
-        <v>324</v>
+        <v>157</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
@@ -4998,52 +5004,52 @@
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B232" s="8" t="s">
-        <v>338</v>
+        <v>20396</v>
+      </c>
+      <c r="B232" t="s">
+        <v>324</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="11" t="s">
-        <v>5</v>
+      <c r="D232" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B233" t="s">
-        <v>163</v>
+        <v>20397</v>
+      </c>
+      <c r="B233" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="1" t="s">
-        <v>8</v>
+      <c r="D233" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B234" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="13" t="s">
-        <v>5</v>
+      <c r="D234" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B235" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
@@ -5054,24 +5060,24 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B236" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="1" t="s">
-        <v>8</v>
+      <c r="D236" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B237" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
@@ -5082,24 +5088,24 @@
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B238" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="10" t="s">
+      <c r="D238" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B239" t="s">
-        <v>321</v>
+        <v>118</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
@@ -5110,66 +5116,66 @@
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B240" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="1" t="s">
+      <c r="D240" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B241" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="13" t="s">
-        <v>5</v>
+      <c r="D241" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B242" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="10" t="s">
-        <v>8</v>
+      <c r="D242" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B243" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="13" t="s">
-        <v>5</v>
+      <c r="D243" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B244" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
@@ -5180,206 +5186,206 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B245" t="s">
-        <v>396</v>
+        <v>161</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="19" t="s">
-        <v>8</v>
+      <c r="D245" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B246" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="10" t="s">
+      <c r="D246" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B247" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="D247" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B248" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="13" t="s">
-        <v>5</v>
+      <c r="D248" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B249" t="s">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>8</v>
+      <c r="D249" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B250" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="10" t="s">
+      <c r="D250" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B251" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="3" t="s">
-        <v>5</v>
+      <c r="D251" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B252" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>8</v>
+      <c r="D252" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B253" t="s">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="11" t="s">
-        <v>5</v>
+      <c r="D253" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B254" t="s">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="13" t="s">
+      <c r="D254" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B255" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="1" t="s">
-        <v>8</v>
+      <c r="D255" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B256" s="8" t="s">
-        <v>341</v>
+        <v>50608</v>
+      </c>
+      <c r="B256" t="s">
+        <v>173</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="14" t="s">
-        <v>5</v>
+      <c r="D256" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B257" t="s">
-        <v>93</v>
+        <v>50611</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="16" t="s">
-        <v>8</v>
+      <c r="D257" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B258" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="10" t="s">
+      <c r="D258" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B259" t="s">
-        <v>199</v>
+        <v>107</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
@@ -5390,94 +5396,94 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B260" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="1" t="s">
-        <v>5</v>
+      <c r="D260" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B261" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="14" t="s">
-        <v>8</v>
+      <c r="D261" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B262" t="s">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="D262" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B263" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="10" t="s">
+      <c r="D263" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B264" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="1" t="s">
+      <c r="D264" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B265" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="13" t="s">
-        <v>5</v>
+      <c r="D265" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B266" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
@@ -5488,24 +5494,24 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B267" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="1" t="s">
-        <v>8</v>
+      <c r="D267" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B268" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5516,80 +5522,80 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B269" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="17" t="s">
-        <v>9</v>
+      <c r="D269" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B270" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="10" t="s">
-        <v>8</v>
+      <c r="D270" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B271" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="1" t="s">
+      <c r="D271" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B272" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="13" t="s">
-        <v>5</v>
+      <c r="D272" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B273" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="10" t="s">
-        <v>8</v>
+      <c r="D273" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B274" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
@@ -5600,66 +5606,66 @@
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B275" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="1" t="s">
+      <c r="D275" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B276" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="17" t="s">
-        <v>9</v>
+      <c r="D276" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B277" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="13" t="s">
-        <v>5</v>
+      <c r="D277" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B278" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="10" t="s">
-        <v>8</v>
+      <c r="D278" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B279" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
@@ -5670,24 +5676,24 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B280" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="1" t="s">
+      <c r="D280" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B281" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5698,136 +5704,136 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B282" t="s">
-        <v>358</v>
+        <v>231</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="11" t="s">
+      <c r="D282" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B283" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D283" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B284" s="8" t="s">
-        <v>343</v>
+        <v>50831</v>
+      </c>
+      <c r="B284" t="s">
+        <v>344</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D285" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>50231</v>
+        <v>50230</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D287" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B288" t="s">
-        <v>232</v>
+        <v>50231</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="13" t="s">
-        <v>5</v>
+      <c r="D288" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B289" t="s">
-        <v>322</v>
+        <v>232</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="11" t="s">
-        <v>9</v>
+      <c r="D289" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B290" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="13" t="s">
-        <v>5</v>
+      <c r="D290" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B291" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
@@ -5838,80 +5844,80 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B292" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="10" t="s">
-        <v>8</v>
+      <c r="D292" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B293" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="3" t="s">
-        <v>5</v>
+      <c r="D293" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B294" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="1" t="s">
-        <v>8</v>
+      <c r="D294" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B295" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="13" t="s">
-        <v>5</v>
+      <c r="D295" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B296" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="1" t="s">
-        <v>8</v>
+      <c r="D296" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B297" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5922,10 +5928,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B298" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5936,10 +5942,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B299" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5950,10 +5956,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B300" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5964,10 +5970,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B301" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5978,66 +5984,66 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B302" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="13" t="s">
-        <v>5</v>
+      <c r="D302" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B303" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="10" t="s">
-        <v>8</v>
+      <c r="D303" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B304" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="1" t="s">
+      <c r="D304" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B305" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="13" t="s">
-        <v>5</v>
+      <c r="D305" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B306" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -6048,80 +6054,80 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B307" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="1" t="s">
+      <c r="D307" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B308" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B309" s="8" t="s">
-        <v>331</v>
+        <v>60169</v>
+      </c>
+      <c r="B309" t="s">
+        <v>250</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="11" t="s">
-        <v>5</v>
+      <c r="D309" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B310" t="s">
-        <v>251</v>
+        <v>60170</v>
+      </c>
+      <c r="B310" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="1" t="s">
+      <c r="D310" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B311" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="13" t="s">
+      <c r="D311" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B312" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
@@ -6132,80 +6138,80 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B313" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="1" t="s">
-        <v>8</v>
+      <c r="D313" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B314" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="10" t="s">
+      <c r="D314" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B315" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="1" t="s">
+      <c r="D315" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B316" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B317" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="10" t="s">
-        <v>8</v>
+      <c r="D317" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B318" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
@@ -6216,38 +6222,38 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B319" s="18" t="s">
-        <v>400</v>
+        <v>60192</v>
+      </c>
+      <c r="B319" t="s">
+        <v>259</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D319" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B320" t="s">
-        <v>260</v>
+        <v>60194</v>
+      </c>
+      <c r="B320" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D320" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B321" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
@@ -6258,10 +6264,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B322" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
@@ -6272,52 +6278,52 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B323" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" t="s">
-        <v>9</v>
+      <c r="D323" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B324" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="13" t="s">
-        <v>5</v>
+      <c r="D324" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B325" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="1" t="s">
-        <v>8</v>
+      <c r="D325" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B326" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
@@ -6328,10 +6334,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B327" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
@@ -6342,192 +6348,192 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B328" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="10" t="s">
+      <c r="D328" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B329" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="1" t="s">
+      <c r="D329" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B330" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="10" t="s">
+      <c r="D330" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B331" t="s">
-        <v>442</v>
+        <v>270</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D331" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B332" t="s">
-        <v>271</v>
+        <v>442</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D332" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B333" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="1" t="s">
+      <c r="D333" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B334" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="10" t="s">
-        <v>5</v>
+      <c r="D334" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B335" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="17" t="s">
-        <v>9</v>
+      <c r="D335" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B336" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="10" t="s">
-        <v>8</v>
+      <c r="D336" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B337" s="8" t="s">
-        <v>332</v>
+        <v>60230</v>
+      </c>
+      <c r="B337" t="s">
+        <v>275</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="7" t="s">
-        <v>9</v>
+      <c r="D337" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D338" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D339" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D340" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6538,10 +6544,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60247</v>
+        <v>60246</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6552,10 +6558,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B343" s="18" t="s">
-        <v>399</v>
+        <v>60247</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6566,66 +6572,66 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B344" s="8" t="s">
-        <v>333</v>
+        <v>60249</v>
+      </c>
+      <c r="B344" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="11" t="s">
-        <v>8</v>
+      <c r="D344" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B345" t="s">
-        <v>276</v>
+        <v>60250</v>
+      </c>
+      <c r="B345" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="1" t="s">
-        <v>9</v>
+      <c r="D345" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B346" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B347" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B348" t="s">
-        <v>451</v>
+        <v>278</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6636,66 +6642,66 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B349" s="8" t="s">
-        <v>337</v>
+        <v>60258</v>
+      </c>
+      <c r="B349" t="s">
+        <v>451</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="11" t="s">
-        <v>8</v>
+      <c r="D349" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B350" t="s">
-        <v>279</v>
+        <v>60266</v>
+      </c>
+      <c r="B350" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="10" t="s">
+      <c r="D350" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B351" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="1" t="s">
-        <v>9</v>
+      <c r="D351" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B352" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B353" t="s">
-        <v>372</v>
+        <v>281</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6706,10 +6712,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B354" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6720,10 +6726,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B355" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6734,38 +6740,38 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B356" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="13" t="s">
+      <c r="D356" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B357" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="1" t="s">
-        <v>5</v>
+      <c r="D357" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B358" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6776,66 +6782,66 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B359" s="8" t="s">
-        <v>330</v>
+        <v>60280</v>
+      </c>
+      <c r="B359" t="s">
+        <v>286</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="11" t="s">
-        <v>9</v>
+      <c r="D359" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D360" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B361" t="s">
-        <v>370</v>
+        <v>60282</v>
+      </c>
+      <c r="B361" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="1" t="s">
-        <v>8</v>
+      <c r="D361" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B362" s="8" t="s">
-        <v>329</v>
+        <v>60283</v>
+      </c>
+      <c r="B362" t="s">
+        <v>370</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="9" t="s">
-        <v>5</v>
+      <c r="D362" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B363" s="8" t="s">
-        <v>444</v>
+        <v>329</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6846,10 +6852,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6860,52 +6866,52 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B365" t="s">
-        <v>369</v>
+        <v>60286</v>
+      </c>
+      <c r="B365" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="12" t="s">
+      <c r="D365" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D367" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6916,10 +6922,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B369" s="18" t="s">
-        <v>391</v>
+        <v>60291</v>
+      </c>
+      <c r="B369" t="s">
+        <v>368</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6930,10 +6936,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60293</v>
+        <v>60292</v>
       </c>
       <c r="B370" s="18" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6944,10 +6950,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B371" t="s">
-        <v>382</v>
+        <v>60293</v>
+      </c>
+      <c r="B371" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6958,10 +6964,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B372" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6972,10 +6978,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B373" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6986,10 +6992,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B374" s="18" t="s">
-        <v>401</v>
+        <v>60299</v>
+      </c>
+      <c r="B374" t="s">
+        <v>379</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -7000,10 +7006,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B375" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -7014,10 +7020,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>60305</v>
+        <v>60303</v>
       </c>
       <c r="B376" s="18" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -7028,24 +7034,24 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>60306</v>
+        <v>60305</v>
       </c>
       <c r="B377" s="18" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D377" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>60308</v>
+        <v>60306</v>
       </c>
       <c r="B378" s="18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -7056,38 +7062,38 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B379" t="s">
-        <v>394</v>
+        <v>60308</v>
+      </c>
+      <c r="B379" s="18" t="s">
+        <v>452</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D379" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B380" t="s">
-        <v>287</v>
+        <v>394</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="15" t="s">
-        <v>5</v>
+      <c r="D380" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B381" t="s">
-        <v>405</v>
+        <v>287</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -7098,24 +7104,24 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B382" t="s">
-        <v>288</v>
+        <v>405</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="12" t="s">
-        <v>8</v>
+      <c r="D382" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B383" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -7126,10 +7132,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B384" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7140,10 +7146,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B385" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -7154,52 +7160,52 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B386" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="15" t="s">
-        <v>5</v>
+      <c r="D386" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B387" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="12" t="s">
-        <v>8</v>
+      <c r="D387" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B388" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="15" t="s">
-        <v>5</v>
+      <c r="D388" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B389" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7210,94 +7216,94 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B390" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D390" s="12" t="s">
-        <v>8</v>
+      <c r="D390" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B391" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D391" s="15" t="s">
-        <v>5</v>
+      <c r="D391" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B392" t="s">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D392" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B393" t="s">
-        <v>298</v>
+        <v>409</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D393" s="12" t="s">
+      <c r="D393" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B394" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D394" s="15" t="s">
-        <v>5</v>
+      <c r="D394" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B395" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D395" s="9" t="s">
-        <v>9</v>
+      <c r="D395" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B396" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7308,38 +7314,38 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B397" t="s">
-        <v>410</v>
+        <v>325</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D397" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>70117</v>
+        <v>70116</v>
       </c>
       <c r="B398" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D398" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>70118</v>
+        <v>70117</v>
       </c>
       <c r="B399" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7350,24 +7356,24 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>70638</v>
+        <v>70118</v>
       </c>
       <c r="B400" t="s">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D400" s="12" t="s">
-        <v>8</v>
+      <c r="D400" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B401" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7378,10 +7384,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B402" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7392,10 +7398,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B403" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7406,10 +7412,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B404" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7420,10 +7426,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B405" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7434,52 +7440,52 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B406" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D406" s="15" t="s">
-        <v>5</v>
+      <c r="D406" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B407" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D407" s="12" t="s">
+      <c r="D407" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B408" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D408" s="9" t="s">
+      <c r="D408" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B409" s="8" t="s">
-        <v>336</v>
+        <v>90622</v>
+      </c>
+      <c r="B409" t="s">
+        <v>327</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
@@ -7490,24 +7496,24 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B410" t="s">
-        <v>308</v>
+        <v>90631</v>
+      </c>
+      <c r="B410" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D410" s="12" t="s">
-        <v>8</v>
+      <c r="D410" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B411" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7518,10 +7524,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B412" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7532,10 +7538,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B413" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7546,10 +7552,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B414" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7560,10 +7566,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B415" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7574,10 +7580,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B416" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7588,10 +7594,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B417" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
@@ -7602,10 +7608,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B418" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
@@ -7616,10 +7622,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B419" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7630,38 +7636,38 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B420" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D420" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B421" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D421" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B422" s="8" t="s">
-        <v>374</v>
+        <v>1218</v>
+      </c>
+      <c r="B422" t="s">
+        <v>373</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>4</v>
@@ -7672,10 +7678,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>4</v>
@@ -7686,10 +7692,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B424" s="8" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>4</v>
@@ -7700,10 +7706,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B425" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>4</v>
@@ -7714,68 +7720,68 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B426" s="8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D426" s="9" t="s">
-        <v>9</v>
+      <c r="D426" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B427" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D427" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A428" s="6">
         <v>1045</v>
       </c>
-      <c r="B427" s="8" t="s">
+      <c r="B428" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C427" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D427" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A428">
-        <v>1043</v>
-      </c>
-      <c r="B428" t="s">
-        <v>412</v>
-      </c>
-      <c r="C428" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D428" t="s">
-        <v>8</v>
+      <c r="C428" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D428" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429">
+        <v>1043</v>
+      </c>
+      <c r="B429" t="s">
+        <v>412</v>
+      </c>
+      <c r="C429" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D429" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A430">
         <v>20340</v>
       </c>
-      <c r="B429" t="s">
+      <c r="B430" t="s">
         <v>413</v>
       </c>
-      <c r="C429" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D429" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A430">
-        <v>40146</v>
-      </c>
-      <c r="B430" t="s">
-        <v>414</v>
-      </c>
-      <c r="C430" s="14" t="s">
+      <c r="C430" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D430" t="s">
@@ -7784,24 +7790,24 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B431" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C431" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D431" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B432" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
@@ -7812,10 +7818,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B433" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
@@ -7826,66 +7832,66 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B434" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D434" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B435" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B436" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B437" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B438" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
@@ -7896,10 +7902,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B439" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
@@ -7910,24 +7916,24 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B440" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D440" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B441" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7938,38 +7944,38 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B442" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B443" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D443" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B444" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
@@ -7980,10 +7986,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B445" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C445" s="14" t="s">
         <v>4</v>
@@ -7994,38 +8000,38 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B446" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C446" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D446" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B447" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C447" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D447" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B448" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C448" s="14" t="s">
         <v>4</v>
@@ -8036,24 +8042,24 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B449" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C449" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D449" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B450" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C450" s="14" t="s">
         <v>4</v>
@@ -8064,34 +8070,62 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451">
-        <v>20398</v>
+        <v>1047</v>
       </c>
       <c r="B451" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C451" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D451" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452">
+        <v>20398</v>
+      </c>
+      <c r="B452" t="s">
+        <v>435</v>
+      </c>
+      <c r="C452" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D452" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A453">
         <v>50226</v>
       </c>
-      <c r="B452" t="s">
+      <c r="B453" t="s">
         <v>456</v>
       </c>
-      <c r="C452" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D452" t="s">
-        <v>5</v>
+      <c r="C453" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D453" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>20307</v>
+      </c>
+      <c r="B454" t="s">
+        <v>459</v>
+      </c>
+      <c r="C454" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D454" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D451"/>
+  <autoFilter ref="A1:D452"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -3025,7 +3025,7 @@
         <v>4</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -5965,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -1401,10 +1401,10 @@
     <t>FERRETERIA VALVERDE</t>
   </si>
   <si>
-    <t>FERRETERIA SENEGAL</t>
-  </si>
-  <si>
     <t>CONSUMIDOR FINAL 4</t>
+  </si>
+  <si>
+    <t>FERRETERIA SENGUEL</t>
   </si>
 </sst>
 </file>
@@ -1815,7 +1815,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -8115,7 +8115,7 @@
         <v>20307</v>
       </c>
       <c r="B454" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C454" s="14" t="s">
         <v>4</v>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="462">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1405,6 +1405,9 @@
   </si>
   <si>
     <t>FERRETERIA SENGUEL</t>
+  </si>
+  <si>
+    <t>CORRALON MARIA Y TAN</t>
   </si>
 </sst>
 </file>
@@ -1760,7 +1763,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D454"/>
+  <dimension ref="A1:D455"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -8122,6 +8125,20 @@
       </c>
       <c r="D454" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>50206</v>
+      </c>
+      <c r="B455" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="C455" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D455" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$452</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$456</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="463">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1408,6 +1408,9 @@
   </si>
   <si>
     <t>CORRALON MARIA Y TAN</t>
+  </si>
+  <si>
+    <t>CLIENTE PRUEBA- NO FACTURAR</t>
   </si>
 </sst>
 </file>
@@ -1763,7 +1766,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D455"/>
+  <dimension ref="A1:D456"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1842,25 +1845,25 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>11</v>
+      <c r="A6" s="4">
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>462</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>206</v>
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -1871,24 +1874,24 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>138</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -1899,10 +1902,10 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1913,10 +1916,10 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
-        <v>233</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>449</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1927,10 +1930,10 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>449</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1941,10 +1944,10 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B13" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1955,10 +1958,10 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1969,10 +1972,10 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1983,10 +1986,10 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>207</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1997,10 +2000,10 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>916</v>
+        <v>308</v>
       </c>
       <c r="B17" t="s">
-        <v>406</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -2011,10 +2014,10 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>406</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -2025,24 +2028,24 @@
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B19" t="s">
-        <v>384</v>
+        <v>190</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>933</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>403</v>
+        <v>921</v>
+      </c>
+      <c r="B20" t="s">
+        <v>384</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -2053,52 +2056,52 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>936</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
+        <v>933</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>403</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B22" t="s">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>8</v>
+      <c r="D23" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -2109,38 +2112,38 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D25" t="s">
-        <v>5</v>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B26" t="s">
-        <v>195</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>8</v>
+      <c r="D26" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>195</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -2151,10 +2154,10 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -2165,52 +2168,52 @@
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D30" t="s">
-        <v>9</v>
+      <c r="D30" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>8</v>
+      <c r="D31" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B32" t="s">
-        <v>448</v>
+        <v>125</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -2221,10 +2224,10 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B33" t="s">
-        <v>154</v>
+        <v>448</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -2235,38 +2238,38 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>5</v>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>8</v>
+      <c r="D35" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -2277,24 +2280,24 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>5</v>
+      <c r="D37" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -2305,66 +2308,66 @@
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>8</v>
+      <c r="D39" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>85</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D40" t="s">
-        <v>9</v>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B41" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>5</v>
+      <c r="D41" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>8</v>
+      <c r="D42" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B43" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -2375,10 +2378,10 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -2389,24 +2392,24 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -2417,66 +2420,66 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B47" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>990</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>404</v>
+        <v>989</v>
+      </c>
+      <c r="B48" t="s">
+        <v>186</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D49" s="20" t="s">
-        <v>8</v>
+      <c r="D49" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
-        <v>992</v>
-      </c>
-      <c r="B50" t="s">
-        <v>65</v>
+        <v>991</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>407</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -2487,10 +2490,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -2501,10 +2504,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -2515,10 +2518,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -2529,38 +2532,38 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B55" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D55" t="s">
-        <v>9</v>
+      <c r="D55" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B56" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>8</v>
+      <c r="D56" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>217</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
@@ -2571,10 +2574,10 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B58" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
@@ -2585,10 +2588,10 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B59" t="s">
-        <v>443</v>
+        <v>46</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -2599,38 +2602,38 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>443</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>5</v>
+      <c r="D60" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B61" t="s">
-        <v>209</v>
+        <v>112</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>8</v>
+      <c r="D61" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
@@ -2641,24 +2644,24 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D63" t="s">
-        <v>9</v>
+      <c r="D63" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B64" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
@@ -2669,24 +2672,24 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>8</v>
+      <c r="D65" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
@@ -2697,10 +2700,10 @@
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>1018</v>
-      </c>
-      <c r="B67" s="18" t="s">
-        <v>390</v>
+        <v>1015</v>
+      </c>
+      <c r="B67" t="s">
+        <v>35</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
@@ -2711,52 +2714,52 @@
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>1020</v>
-      </c>
-      <c r="B68" t="s">
-        <v>354</v>
+        <v>1018</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>390</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D68" s="11" t="s">
-        <v>5</v>
+      <c r="D68" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B69" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B70" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B71" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
@@ -2767,136 +2770,136 @@
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B72" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B73" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D73" s="14" t="s">
-        <v>5</v>
+      <c r="D73" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B74" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B75" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="14" t="s">
-        <v>8</v>
+      <c r="D75" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B76" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B77" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D77" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>1031</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>340</v>
+        <v>1030</v>
+      </c>
+      <c r="B78" t="s">
+        <v>348</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>1032</v>
-      </c>
-      <c r="B79" t="s">
-        <v>361</v>
+        <v>1031</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B80" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D80" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>1034</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>365</v>
+        <v>1033</v>
+      </c>
+      <c r="B81" t="s">
+        <v>349</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
@@ -2907,10 +2910,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
@@ -2921,10 +2924,10 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>1036</v>
-      </c>
-      <c r="B83" t="s">
-        <v>350</v>
+        <v>1035</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
@@ -2935,10 +2938,10 @@
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B84" t="s">
-        <v>447</v>
+        <v>350</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
@@ -2949,10 +2952,10 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B85" t="s">
-        <v>345</v>
+        <v>447</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
@@ -2963,10 +2966,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B86" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
@@ -2977,94 +2980,94 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B87" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B88" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B89" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B90" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B91" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>1050</v>
-      </c>
-      <c r="B92" s="18" t="s">
-        <v>446</v>
+        <v>1049</v>
+      </c>
+      <c r="B92" t="s">
+        <v>397</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
@@ -3075,38 +3078,38 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>1416</v>
-      </c>
-      <c r="B94" t="s">
-        <v>212</v>
+        <v>1051</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>437</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>8</v>
+      <c r="D94" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>1987</v>
+        <v>1416</v>
       </c>
       <c r="B95" t="s">
-        <v>439</v>
+        <v>212</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B96" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
@@ -3117,10 +3120,10 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>1989</v>
-      </c>
-      <c r="B97" s="18" t="s">
-        <v>455</v>
+        <v>1988</v>
+      </c>
+      <c r="B97" t="s">
+        <v>440</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
@@ -3131,38 +3134,38 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10107</v>
-      </c>
-      <c r="B98" t="s">
-        <v>94</v>
+        <v>1989</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>455</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" t="s">
-        <v>9</v>
+      <c r="D98" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B99" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>8</v>
+      <c r="D99" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B100" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
@@ -3173,10 +3176,10 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B101" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
@@ -3187,94 +3190,94 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="13" t="s">
-        <v>5</v>
+      <c r="D102" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>8</v>
+      <c r="D103" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="13" t="s">
-        <v>5</v>
+      <c r="D104" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B105" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>8</v>
+      <c r="D105" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>342</v>
+        <v>10165</v>
+      </c>
+      <c r="B106" t="s">
+        <v>19</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="11" t="s">
+      <c r="D106" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B107" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="13" t="s">
-        <v>5</v>
+      <c r="D107" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>10168</v>
+        <v>10167</v>
       </c>
       <c r="B108" t="s">
-        <v>441</v>
+        <v>39</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
@@ -3285,24 +3288,24 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>10424</v>
+        <v>10168</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>441</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="17" t="s">
-        <v>9</v>
+      <c r="D109" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
@@ -3313,24 +3316,24 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B111" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D111" s="10" t="s">
-        <v>8</v>
+      <c r="D111" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B112" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
@@ -3341,150 +3344,150 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B113" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B114" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>8</v>
+      <c r="D114" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B115" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B116" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B117" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B118" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="D118" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B119" t="s">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B120" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="13" t="s">
-        <v>5</v>
+      <c r="D120" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B121" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="10" t="s">
-        <v>8</v>
+      <c r="D121" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B122" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
@@ -3495,10 +3498,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B124" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3509,10 +3512,10 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B125" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3523,10 +3526,10 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B126" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
@@ -3537,10 +3540,10 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B127" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
@@ -3551,38 +3554,38 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B128" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="D128" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B129" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B130" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
@@ -3593,52 +3596,52 @@
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B131" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="10" t="s">
+      <c r="D131" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B132" t="s">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>5</v>
+      <c r="D132" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B133" t="s">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="13" t="s">
+      <c r="D133" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B134" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
@@ -3649,24 +3652,24 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B135" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>8</v>
+      <c r="D135" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
@@ -3677,10 +3680,10 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B137" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
@@ -3691,52 +3694,52 @@
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B138" t="s">
-        <v>175</v>
+        <v>38</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="10" t="s">
+      <c r="D138" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B139" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="17" t="s">
-        <v>9</v>
+      <c r="D139" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B140" t="s">
-        <v>219</v>
+        <v>117</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="10" t="s">
-        <v>8</v>
+      <c r="D140" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B141" t="s">
-        <v>23</v>
+        <v>219</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
@@ -3747,52 +3750,52 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B142" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" t="s">
-        <v>9</v>
+      <c r="D142" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B143" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="10" t="s">
-        <v>8</v>
+      <c r="D143" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B144" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B145" t="s">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
@@ -3803,38 +3806,38 @@
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B146" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="10" t="s">
+      <c r="D146" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B147" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D147" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B148" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
@@ -3845,94 +3848,94 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B149" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" t="s">
-        <v>9</v>
+      <c r="D149" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>8</v>
+      <c r="D150" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B151" t="s">
-        <v>362</v>
+        <v>145</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="14" t="s">
-        <v>5</v>
+      <c r="D151" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B152" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="1" t="s">
-        <v>8</v>
+      <c r="D152" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20192</v>
+        <v>20189</v>
       </c>
       <c r="B153" t="s">
-        <v>454</v>
+        <v>323</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20200</v>
+        <v>20192</v>
       </c>
       <c r="B154" t="s">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="13" t="s">
+      <c r="D154" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B155" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
@@ -3943,150 +3946,150 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B156" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="10" t="s">
-        <v>8</v>
+      <c r="D156" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B157" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="1" t="s">
-        <v>9</v>
+      <c r="D157" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B158" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="10" t="s">
-        <v>8</v>
+      <c r="D158" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B159" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="D159" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B160" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="10" t="s">
+      <c r="D160" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B161" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="13" t="s">
-        <v>5</v>
+      <c r="D161" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B162" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="10" t="s">
-        <v>8</v>
+      <c r="D162" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B163" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="13" t="s">
-        <v>5</v>
+      <c r="D163" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B164" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="3" t="s">
+      <c r="D164" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B165" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="13" t="s">
+      <c r="D165" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B166" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
@@ -4097,24 +4100,24 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B167" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="10" t="s">
-        <v>8</v>
+      <c r="D167" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B168" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
@@ -4125,108 +4128,108 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B169" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="13" t="s">
-        <v>5</v>
+      <c r="D169" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B170" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="10" t="s">
-        <v>8</v>
+      <c r="D170" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B171" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="D171" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B172" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="17" t="s">
-        <v>9</v>
+      <c r="D172" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B173" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>8</v>
+      <c r="D173" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B174" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="13" t="s">
-        <v>5</v>
+      <c r="D174" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B175" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="10" t="s">
-        <v>8</v>
+      <c r="D175" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B176" t="s">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
@@ -4237,206 +4240,206 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B177" t="s">
-        <v>392</v>
+        <v>90</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B178" t="s">
-        <v>196</v>
+        <v>392</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>8</v>
+      <c r="D178" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B179" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="13" t="s">
-        <v>5</v>
+      <c r="D179" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B180" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="1" t="s">
-        <v>8</v>
+      <c r="D180" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B181" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="13" t="s">
-        <v>5</v>
+      <c r="D181" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B182" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="1" t="s">
-        <v>8</v>
+      <c r="D182" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B183" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="3" t="s">
-        <v>5</v>
+      <c r="D183" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B184" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="1" t="s">
-        <v>9</v>
+      <c r="D184" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B185" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="17" t="s">
+      <c r="D185" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B186" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="1" t="s">
-        <v>8</v>
+      <c r="D186" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B187" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="3" t="s">
-        <v>5</v>
+      <c r="D187" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B188" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="1" t="s">
-        <v>8</v>
+      <c r="D188" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B189" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="10" t="s">
+      <c r="D189" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B190" t="s">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="13" t="s">
-        <v>5</v>
+      <c r="D190" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B191" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4447,52 +4450,52 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B192" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="10" t="s">
-        <v>8</v>
+      <c r="D192" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B193" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="13" t="s">
-        <v>5</v>
+      <c r="D193" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B194" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="1" t="s">
-        <v>8</v>
+      <c r="D194" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B195" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
@@ -4503,10 +4506,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B196" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4517,10 +4520,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B197" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4531,24 +4534,24 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B198" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="13" t="s">
-        <v>5</v>
+      <c r="D198" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B199" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
@@ -4559,52 +4562,52 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B200" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="1" t="s">
-        <v>8</v>
+      <c r="D200" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B201" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="10" t="s">
+      <c r="D201" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B202" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="1" t="s">
+      <c r="D202" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B203" t="s">
-        <v>205</v>
+        <v>126</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
@@ -4615,10 +4618,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B204" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4629,38 +4632,38 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B205" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="13" t="s">
-        <v>5</v>
+      <c r="D205" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B206" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="1" t="s">
-        <v>8</v>
+      <c r="D206" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B207" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
@@ -4671,10 +4674,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B208" t="s">
-        <v>445</v>
+        <v>115</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
@@ -4685,66 +4688,66 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B209" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="13" t="s">
-        <v>5</v>
+      <c r="D209" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B210" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="1" t="s">
-        <v>8</v>
+      <c r="D210" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B211" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="13" t="s">
-        <v>5</v>
+      <c r="D211" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B212" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="10" t="s">
-        <v>8</v>
+      <c r="D212" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B213" t="s">
-        <v>208</v>
+        <v>45</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
@@ -4755,38 +4758,38 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B214" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="13" t="s">
-        <v>5</v>
+      <c r="D214" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="1" t="s">
-        <v>8</v>
+      <c r="D215" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B216" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
@@ -4797,10 +4800,10 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B217" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
@@ -4811,10 +4814,10 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>62</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
@@ -4825,52 +4828,52 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B219" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="10" t="s">
+      <c r="D219" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B220" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="D220" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="10" t="s">
+      <c r="D221" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B222" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
@@ -4881,66 +4884,66 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B223" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="13" t="s">
-        <v>5</v>
+      <c r="D223" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B224" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="1" t="s">
-        <v>8</v>
+      <c r="D224" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B225" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="10" t="s">
+      <c r="D225" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B226" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="1" t="s">
+      <c r="D226" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B227" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
@@ -4951,66 +4954,66 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B228" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="10" t="s">
+      <c r="D228" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B229" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="D229" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B230" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="10" t="s">
+      <c r="D230" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B231" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="1" t="s">
+      <c r="D231" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B232" t="s">
-        <v>324</v>
+        <v>157</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
@@ -5021,52 +5024,52 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B233" s="8" t="s">
-        <v>338</v>
+        <v>20396</v>
+      </c>
+      <c r="B233" t="s">
+        <v>324</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="11" t="s">
-        <v>5</v>
+      <c r="D233" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B234" t="s">
-        <v>163</v>
+        <v>20397</v>
+      </c>
+      <c r="B234" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="1" t="s">
-        <v>8</v>
+      <c r="D234" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B235" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="13" t="s">
-        <v>5</v>
+      <c r="D235" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B236" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
@@ -5077,24 +5080,24 @@
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B237" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="1" t="s">
-        <v>8</v>
+      <c r="D237" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B238" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
@@ -5105,24 +5108,24 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B239" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="10" t="s">
+      <c r="D239" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B240" t="s">
-        <v>321</v>
+        <v>118</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
@@ -5133,66 +5136,66 @@
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B241" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="D241" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B242" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="13" t="s">
-        <v>5</v>
+      <c r="D242" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B243" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="10" t="s">
-        <v>8</v>
+      <c r="D243" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B244" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="13" t="s">
-        <v>5</v>
+      <c r="D244" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B245" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
@@ -5203,206 +5206,206 @@
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B246" t="s">
-        <v>396</v>
+        <v>161</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="19" t="s">
-        <v>8</v>
+      <c r="D246" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B247" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="10" t="s">
+      <c r="D247" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B248" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="1" t="s">
+      <c r="D248" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B249" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="13" t="s">
-        <v>5</v>
+      <c r="D249" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B250" t="s">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
-        <v>8</v>
+      <c r="D250" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B251" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="10" t="s">
+      <c r="D251" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B252" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="3" t="s">
-        <v>5</v>
+      <c r="D252" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B253" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="1" t="s">
-        <v>8</v>
+      <c r="D253" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B254" t="s">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="11" t="s">
-        <v>5</v>
+      <c r="D254" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B255" t="s">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="13" t="s">
+      <c r="D255" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B256" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="1" t="s">
-        <v>8</v>
+      <c r="D256" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B257" s="8" t="s">
-        <v>341</v>
+        <v>50608</v>
+      </c>
+      <c r="B257" t="s">
+        <v>173</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="14" t="s">
-        <v>5</v>
+      <c r="D257" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B258" t="s">
-        <v>93</v>
+        <v>50611</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="16" t="s">
-        <v>8</v>
+      <c r="D258" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B259" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="10" t="s">
+      <c r="D259" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B260" t="s">
-        <v>199</v>
+        <v>107</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
@@ -5413,94 +5416,94 @@
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B261" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="1" t="s">
-        <v>5</v>
+      <c r="D261" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B262" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="14" t="s">
-        <v>8</v>
+      <c r="D262" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B263" t="s">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="1" t="s">
+      <c r="D263" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B264" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="10" t="s">
+      <c r="D264" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B265" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="1" t="s">
+      <c r="D265" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B266" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="13" t="s">
-        <v>5</v>
+      <c r="D266" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B267" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
@@ -5511,24 +5514,24 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B268" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="1" t="s">
-        <v>8</v>
+      <c r="D268" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B269" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
@@ -5539,80 +5542,80 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B270" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="17" t="s">
-        <v>9</v>
+      <c r="D270" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B271" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="10" t="s">
-        <v>8</v>
+      <c r="D271" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B272" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="1" t="s">
+      <c r="D272" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B273" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="13" t="s">
-        <v>5</v>
+      <c r="D273" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B274" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="10" t="s">
-        <v>8</v>
+      <c r="D274" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B275" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
@@ -5623,66 +5626,66 @@
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B276" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="1" t="s">
+      <c r="D276" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B277" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="17" t="s">
-        <v>9</v>
+      <c r="D277" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B278" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="13" t="s">
-        <v>5</v>
+      <c r="D278" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B279" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="10" t="s">
-        <v>8</v>
+      <c r="D279" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B280" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
@@ -5693,24 +5696,24 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B281" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="1" t="s">
+      <c r="D281" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B282" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5721,136 +5724,136 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B283" t="s">
-        <v>358</v>
+        <v>231</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="11" t="s">
+      <c r="D283" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B284" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B285" s="8" t="s">
-        <v>343</v>
+        <v>50831</v>
+      </c>
+      <c r="B285" t="s">
+        <v>344</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D285" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D287" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>50231</v>
+        <v>50230</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B289" t="s">
-        <v>232</v>
+        <v>50231</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="13" t="s">
-        <v>5</v>
+      <c r="D289" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B290" t="s">
-        <v>322</v>
+        <v>232</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="11" t="s">
-        <v>9</v>
+      <c r="D290" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B291" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="13" t="s">
-        <v>5</v>
+      <c r="D291" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B292" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
@@ -5861,80 +5864,80 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B293" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="10" t="s">
-        <v>8</v>
+      <c r="D293" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B294" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="3" t="s">
-        <v>5</v>
+      <c r="D294" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B295" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="1" t="s">
-        <v>8</v>
+      <c r="D295" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B296" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="13" t="s">
-        <v>5</v>
+      <c r="D296" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B297" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="1" t="s">
-        <v>8</v>
+      <c r="D297" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B298" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5945,10 +5948,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B299" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5959,38 +5962,38 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B300" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B301" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B302" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -6001,66 +6004,66 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B303" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="13" t="s">
-        <v>5</v>
+      <c r="D303" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B304" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="10" t="s">
-        <v>8</v>
+      <c r="D304" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B305" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="1" t="s">
+      <c r="D305" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B306" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="13" t="s">
-        <v>5</v>
+      <c r="D306" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B307" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -6071,80 +6074,80 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B308" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="1" t="s">
+      <c r="D308" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B309" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B310" s="8" t="s">
-        <v>331</v>
+        <v>60169</v>
+      </c>
+      <c r="B310" t="s">
+        <v>250</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="11" t="s">
-        <v>5</v>
+      <c r="D310" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B311" t="s">
-        <v>251</v>
+        <v>60170</v>
+      </c>
+      <c r="B311" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="1" t="s">
+      <c r="D311" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B312" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="13" t="s">
+      <c r="D312" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B313" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -6155,80 +6158,80 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B314" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="1" t="s">
-        <v>8</v>
+      <c r="D314" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B315" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="10" t="s">
+      <c r="D315" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B316" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="1" t="s">
+      <c r="D316" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B317" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B318" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="10" t="s">
-        <v>8</v>
+      <c r="D318" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B319" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
@@ -6239,38 +6242,38 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B320" s="18" t="s">
-        <v>400</v>
+        <v>60192</v>
+      </c>
+      <c r="B320" t="s">
+        <v>259</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D320" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B321" t="s">
-        <v>260</v>
+        <v>60194</v>
+      </c>
+      <c r="B321" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B322" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
@@ -6281,10 +6284,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B323" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
@@ -6295,52 +6298,52 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B324" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" t="s">
-        <v>9</v>
+      <c r="D324" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B325" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="13" t="s">
-        <v>5</v>
+      <c r="D325" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B326" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="1" t="s">
-        <v>8</v>
+      <c r="D326" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B327" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
@@ -6351,10 +6354,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B328" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6365,192 +6368,192 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B329" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="10" t="s">
+      <c r="D329" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B330" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="1" t="s">
+      <c r="D330" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B331" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="10" t="s">
+      <c r="D331" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B332" t="s">
-        <v>442</v>
+        <v>270</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D332" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B333" t="s">
-        <v>271</v>
+        <v>442</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D333" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B334" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="1" t="s">
+      <c r="D334" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B335" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="10" t="s">
-        <v>5</v>
+      <c r="D335" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B336" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="17" t="s">
-        <v>9</v>
+      <c r="D336" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B337" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="10" t="s">
-        <v>8</v>
+      <c r="D337" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B338" s="8" t="s">
-        <v>332</v>
+        <v>60230</v>
+      </c>
+      <c r="B338" t="s">
+        <v>275</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="7" t="s">
-        <v>9</v>
+      <c r="D338" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D339" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D340" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D341" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6561,10 +6564,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60247</v>
+        <v>60246</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6575,10 +6578,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B344" s="18" t="s">
-        <v>399</v>
+        <v>60247</v>
+      </c>
+      <c r="B344" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
@@ -6589,66 +6592,66 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B345" s="8" t="s">
-        <v>333</v>
+        <v>60249</v>
+      </c>
+      <c r="B345" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="11" t="s">
-        <v>8</v>
+      <c r="D345" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B346" t="s">
-        <v>276</v>
+        <v>60250</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="1" t="s">
-        <v>9</v>
+      <c r="D346" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B347" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B348" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B349" t="s">
-        <v>451</v>
+        <v>278</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6659,80 +6662,80 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B350" s="8" t="s">
-        <v>337</v>
+        <v>60258</v>
+      </c>
+      <c r="B350" t="s">
+        <v>451</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="11" t="s">
-        <v>8</v>
+      <c r="D350" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B351" t="s">
-        <v>279</v>
+        <v>60266</v>
+      </c>
+      <c r="B351" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="10" t="s">
+      <c r="D351" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B352" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D352" s="1" t="s">
-        <v>9</v>
+      <c r="D352" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B353" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B354" t="s">
-        <v>372</v>
+        <v>281</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B355" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6743,10 +6746,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B356" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6757,38 +6760,38 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B357" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="13" t="s">
+      <c r="D357" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B358" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="1" t="s">
-        <v>5</v>
+      <c r="D358" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B359" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6799,66 +6802,66 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B360" s="8" t="s">
-        <v>330</v>
+        <v>60280</v>
+      </c>
+      <c r="B360" t="s">
+        <v>286</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="11" t="s">
-        <v>9</v>
+      <c r="D360" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D361" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B362" t="s">
-        <v>370</v>
+        <v>60282</v>
+      </c>
+      <c r="B362" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="1" t="s">
-        <v>8</v>
+      <c r="D362" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B363" s="8" t="s">
-        <v>329</v>
+        <v>60283</v>
+      </c>
+      <c r="B363" t="s">
+        <v>370</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="9" t="s">
-        <v>5</v>
+      <c r="D363" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>444</v>
+        <v>329</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6869,10 +6872,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B365" s="8" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6883,52 +6886,52 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B366" t="s">
-        <v>369</v>
+        <v>60286</v>
+      </c>
+      <c r="B366" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="12" t="s">
+      <c r="D366" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B367" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D367" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B368" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D368" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B369" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6939,10 +6942,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B370" s="18" t="s">
-        <v>391</v>
+        <v>60291</v>
+      </c>
+      <c r="B370" t="s">
+        <v>368</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6953,10 +6956,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>60293</v>
+        <v>60292</v>
       </c>
       <c r="B371" s="18" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6967,10 +6970,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B372" t="s">
-        <v>382</v>
+        <v>60293</v>
+      </c>
+      <c r="B372" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6981,10 +6984,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B373" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6995,10 +6998,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B374" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -7009,10 +7012,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B375" s="18" t="s">
-        <v>401</v>
+        <v>60299</v>
+      </c>
+      <c r="B375" t="s">
+        <v>379</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -7023,10 +7026,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B376" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -7037,10 +7040,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>60305</v>
+        <v>60303</v>
       </c>
       <c r="B377" s="18" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -7051,24 +7054,24 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>60306</v>
+        <v>60305</v>
       </c>
       <c r="B378" s="18" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D378" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>60308</v>
+        <v>60306</v>
       </c>
       <c r="B379" s="18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -7079,38 +7082,38 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B380" t="s">
-        <v>394</v>
+        <v>60308</v>
+      </c>
+      <c r="B380" s="18" t="s">
+        <v>452</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D380" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B381" t="s">
-        <v>287</v>
+        <v>394</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="15" t="s">
-        <v>5</v>
+      <c r="D381" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B382" t="s">
-        <v>405</v>
+        <v>287</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -7121,24 +7124,24 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B383" t="s">
-        <v>288</v>
+        <v>405</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="12" t="s">
-        <v>8</v>
+      <c r="D383" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B384" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7149,10 +7152,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B385" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -7163,10 +7166,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B386" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7177,52 +7180,52 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B387" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="15" t="s">
-        <v>5</v>
+      <c r="D387" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B388" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="12" t="s">
-        <v>8</v>
+      <c r="D388" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B389" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="15" t="s">
-        <v>5</v>
+      <c r="D389" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B390" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7233,94 +7236,94 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B391" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D391" s="12" t="s">
-        <v>8</v>
+      <c r="D391" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B392" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D392" s="15" t="s">
-        <v>5</v>
+      <c r="D392" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B393" t="s">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D393" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B394" t="s">
-        <v>298</v>
+        <v>409</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D394" s="12" t="s">
+      <c r="D394" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B395" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D395" s="15" t="s">
-        <v>5</v>
+      <c r="D395" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B396" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D396" s="9" t="s">
-        <v>9</v>
+      <c r="D396" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B397" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7331,38 +7334,38 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B398" t="s">
-        <v>410</v>
+        <v>325</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D398" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>70117</v>
+        <v>70116</v>
       </c>
       <c r="B399" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D399" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>70118</v>
+        <v>70117</v>
       </c>
       <c r="B400" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7373,24 +7376,24 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>70638</v>
+        <v>70118</v>
       </c>
       <c r="B401" t="s">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D401" s="12" t="s">
-        <v>8</v>
+      <c r="D401" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B402" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7401,10 +7404,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B403" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7415,10 +7418,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B404" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7429,10 +7432,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B405" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7443,10 +7446,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B406" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7457,52 +7460,52 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B407" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D407" s="15" t="s">
-        <v>5</v>
+      <c r="D407" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B408" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D408" s="12" t="s">
+      <c r="D408" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B409" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D409" s="9" t="s">
+      <c r="D409" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B410" s="8" t="s">
-        <v>336</v>
+        <v>90622</v>
+      </c>
+      <c r="B410" t="s">
+        <v>327</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
@@ -7513,24 +7516,24 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B411" t="s">
-        <v>308</v>
+        <v>90631</v>
+      </c>
+      <c r="B411" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D411" s="12" t="s">
-        <v>8</v>
+      <c r="D411" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B412" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
@@ -7541,10 +7544,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B413" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7555,10 +7558,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B414" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7569,10 +7572,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B415" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7583,10 +7586,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B416" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7597,10 +7600,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B417" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
@@ -7611,10 +7614,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B418" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
@@ -7625,10 +7628,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B419" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7639,10 +7642,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B420" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
@@ -7653,38 +7656,38 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B421" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D421" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B422" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D422" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B423" s="8" t="s">
-        <v>374</v>
+        <v>1218</v>
+      </c>
+      <c r="B423" t="s">
+        <v>373</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>4</v>
@@ -7695,10 +7698,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B424" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>4</v>
@@ -7709,10 +7712,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B425" s="8" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>4</v>
@@ -7723,10 +7726,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B426" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>4</v>
@@ -7737,68 +7740,68 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B427" s="8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D427" s="9" t="s">
-        <v>9</v>
+      <c r="D427" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B428" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D428" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A429" s="6">
         <v>1045</v>
       </c>
-      <c r="B428" s="8" t="s">
+      <c r="B429" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C428" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D428" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A429">
-        <v>1043</v>
-      </c>
-      <c r="B429" t="s">
-        <v>412</v>
-      </c>
-      <c r="C429" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D429" t="s">
+      <c r="C429" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D429" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430">
+        <v>1043</v>
+      </c>
+      <c r="B430" t="s">
+        <v>412</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D430" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A431">
         <v>20340</v>
       </c>
-      <c r="B430" t="s">
+      <c r="B431" t="s">
         <v>413</v>
       </c>
-      <c r="C430" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D430" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A431">
-        <v>40146</v>
-      </c>
-      <c r="B431" t="s">
-        <v>414</v>
-      </c>
-      <c r="C431" s="14" t="s">
+      <c r="C431" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D431" t="s">
@@ -7807,24 +7810,24 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B432" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C432" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B433" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
@@ -7835,10 +7838,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B434" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7849,66 +7852,66 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B435" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B436" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B437" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B438" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D438" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B439" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
@@ -7919,10 +7922,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B440" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
@@ -7933,24 +7936,24 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B441" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D441" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B442" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
@@ -7961,38 +7964,38 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B443" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D443" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B444" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D444" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B445" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C445" s="14" t="s">
         <v>4</v>
@@ -8003,10 +8006,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B446" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C446" s="14" t="s">
         <v>4</v>
@@ -8017,38 +8020,38 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B447" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C447" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D447" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B448" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C448" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D448" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="449" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B449" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C449" s="14" t="s">
         <v>4</v>
@@ -8059,24 +8062,24 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B450" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C450" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D450" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="451" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B451" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C451" s="14" t="s">
         <v>4</v>
@@ -8087,62 +8090,76 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452">
-        <v>20398</v>
+        <v>1047</v>
       </c>
       <c r="B452" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C452" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D452" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="453" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453">
-        <v>50226</v>
+        <v>20398</v>
       </c>
       <c r="B453" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="C453" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D453" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="454" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454">
-        <v>20307</v>
+        <v>50226</v>
       </c>
       <c r="B454" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C454" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D454" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="455" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455">
+        <v>20307</v>
+      </c>
+      <c r="B455" t="s">
+        <v>460</v>
+      </c>
+      <c r="C455" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D455" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A456">
         <v>50206</v>
       </c>
-      <c r="B455" s="18" t="s">
+      <c r="B456" s="18" t="s">
         <v>461</v>
       </c>
-      <c r="C455" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D455" s="3" t="s">
+      <c r="C456" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D456" s="3" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D452"/>
+  <autoFilter ref="A1:D456"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -6867,7 +6867,7 @@
         <v>4</v>
       </c>
       <c r="D364" s="9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$456</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$457</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="465">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1411,6 +1411,12 @@
   </si>
   <si>
     <t>CLIENTE PRUEBA- NO FACTURAR</t>
+  </si>
+  <si>
+    <t>20325</t>
+  </si>
+  <si>
+    <t>CATAN CITY FERRETERI</t>
   </si>
 </sst>
 </file>
@@ -1766,7 +1772,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D456"/>
+  <dimension ref="A1:D457"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3059,7 +3065,7 @@
         <v>4</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4631,53 +4637,53 @@
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="6">
-        <v>20331</v>
-      </c>
-      <c r="B205" t="s">
-        <v>50</v>
+      <c r="A205" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="B205" s="18" t="s">
+        <v>464</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B206" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="13" t="s">
-        <v>5</v>
+      <c r="D206" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B207" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="1" t="s">
-        <v>8</v>
+      <c r="D207" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B208" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
@@ -4688,10 +4694,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B209" t="s">
-        <v>445</v>
+        <v>115</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
@@ -4702,66 +4708,66 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B210" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="13" t="s">
-        <v>5</v>
+      <c r="D210" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B211" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="1" t="s">
-        <v>8</v>
+      <c r="D211" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B212" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="13" t="s">
-        <v>5</v>
+      <c r="D212" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B213" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="10" t="s">
-        <v>8</v>
+      <c r="D213" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B214" t="s">
-        <v>208</v>
+        <v>45</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4772,38 +4778,38 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B215" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="13" t="s">
-        <v>5</v>
+      <c r="D215" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="1" t="s">
-        <v>8</v>
+      <c r="D216" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B217" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
@@ -4814,10 +4820,10 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B218" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
@@ -4828,10 +4834,10 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>62</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
@@ -4842,52 +4848,52 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B220" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="10" t="s">
+      <c r="D220" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B221" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="D221" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B222" t="s">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="10" t="s">
+      <c r="D222" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B223" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
@@ -4898,66 +4904,66 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B224" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="13" t="s">
-        <v>5</v>
+      <c r="D224" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B225" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="1" t="s">
-        <v>8</v>
+      <c r="D225" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B226" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="10" t="s">
+      <c r="D226" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B227" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="D227" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B228" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
@@ -4968,66 +4974,66 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B229" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="10" t="s">
+      <c r="D229" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B230" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="D230" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B231" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="10" t="s">
+      <c r="D231" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B232" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="1" t="s">
+      <c r="D232" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B233" t="s">
-        <v>324</v>
+        <v>157</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
@@ -5038,52 +5044,52 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B234" s="8" t="s">
-        <v>338</v>
+        <v>20396</v>
+      </c>
+      <c r="B234" t="s">
+        <v>324</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="11" t="s">
-        <v>5</v>
+      <c r="D234" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B235" t="s">
-        <v>163</v>
+        <v>20397</v>
+      </c>
+      <c r="B235" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>8</v>
+      <c r="D235" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B236" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="13" t="s">
-        <v>5</v>
+      <c r="D236" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B237" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
@@ -5094,24 +5100,24 @@
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B238" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="1" t="s">
-        <v>8</v>
+      <c r="D238" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B239" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
@@ -5122,24 +5128,24 @@
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B240" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="10" t="s">
+      <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B241" t="s">
-        <v>321</v>
+        <v>118</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
@@ -5150,66 +5156,66 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B242" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="D242" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B243" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="13" t="s">
-        <v>5</v>
+      <c r="D243" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B244" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="10" t="s">
-        <v>8</v>
+      <c r="D244" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B245" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="13" t="s">
-        <v>5</v>
+      <c r="D245" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B246" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
@@ -5220,206 +5226,206 @@
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B247" t="s">
-        <v>396</v>
+        <v>161</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="19" t="s">
-        <v>8</v>
+      <c r="D247" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B248" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="10" t="s">
+      <c r="D248" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B249" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="1" t="s">
+      <c r="D249" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B250" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="13" t="s">
-        <v>5</v>
+      <c r="D250" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B251" t="s">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="1" t="s">
-        <v>8</v>
+      <c r="D251" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B252" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="10" t="s">
+      <c r="D252" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B253" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="3" t="s">
-        <v>5</v>
+      <c r="D253" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B254" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="1" t="s">
-        <v>8</v>
+      <c r="D254" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B255" t="s">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="11" t="s">
-        <v>5</v>
+      <c r="D255" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B256" t="s">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="13" t="s">
+      <c r="D256" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B257" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="1" t="s">
-        <v>8</v>
+      <c r="D257" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B258" s="8" t="s">
-        <v>341</v>
+        <v>50608</v>
+      </c>
+      <c r="B258" t="s">
+        <v>173</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="14" t="s">
-        <v>5</v>
+      <c r="D258" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B259" t="s">
-        <v>93</v>
+        <v>50611</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="16" t="s">
-        <v>8</v>
+      <c r="D259" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B260" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="10" t="s">
+      <c r="D260" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B261" t="s">
-        <v>199</v>
+        <v>107</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
@@ -5430,94 +5436,94 @@
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B262" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="1" t="s">
-        <v>5</v>
+      <c r="D262" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B263" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="14" t="s">
-        <v>8</v>
+      <c r="D263" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B264" t="s">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="1" t="s">
+      <c r="D264" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B265" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="10" t="s">
+      <c r="D265" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B266" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="1" t="s">
+      <c r="D266" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B267" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="13" t="s">
-        <v>5</v>
+      <c r="D267" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B268" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5528,24 +5534,24 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B269" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="1" t="s">
-        <v>8</v>
+      <c r="D269" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B270" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
@@ -5556,80 +5562,80 @@
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B271" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="17" t="s">
-        <v>9</v>
+      <c r="D271" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B272" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="10" t="s">
-        <v>8</v>
+      <c r="D272" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B273" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="1" t="s">
+      <c r="D273" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B274" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="13" t="s">
-        <v>5</v>
+      <c r="D274" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B275" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="10" t="s">
-        <v>8</v>
+      <c r="D275" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B276" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
@@ -5640,66 +5646,66 @@
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B277" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="1" t="s">
+      <c r="D277" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B278" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="17" t="s">
-        <v>9</v>
+      <c r="D278" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B279" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="13" t="s">
-        <v>5</v>
+      <c r="D279" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B280" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="10" t="s">
-        <v>8</v>
+      <c r="D280" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B281" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5710,24 +5716,24 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B282" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="1" t="s">
+      <c r="D282" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B283" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
@@ -5738,136 +5744,136 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B284" t="s">
-        <v>358</v>
+        <v>231</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="11" t="s">
+      <c r="D284" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B285" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D285" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B286" s="8" t="s">
-        <v>343</v>
+        <v>50831</v>
+      </c>
+      <c r="B286" t="s">
+        <v>344</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D287" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>50231</v>
+        <v>50230</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D289" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B290" t="s">
-        <v>232</v>
+        <v>50231</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="13" t="s">
-        <v>5</v>
+      <c r="D290" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B291" t="s">
-        <v>322</v>
+        <v>232</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="11" t="s">
-        <v>9</v>
+      <c r="D291" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B292" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="13" t="s">
-        <v>5</v>
+      <c r="D292" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B293" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
@@ -5878,80 +5884,80 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B294" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="10" t="s">
-        <v>8</v>
+      <c r="D294" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B295" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="3" t="s">
-        <v>5</v>
+      <c r="D295" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B296" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="1" t="s">
-        <v>8</v>
+      <c r="D296" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B297" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="13" t="s">
-        <v>5</v>
+      <c r="D297" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B298" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="1" t="s">
-        <v>8</v>
+      <c r="D298" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B299" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5962,10 +5968,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B300" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5976,38 +5982,38 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B301" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B302" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B303" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -6018,66 +6024,66 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B304" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="13" t="s">
-        <v>5</v>
+      <c r="D304" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B305" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="10" t="s">
-        <v>8</v>
+      <c r="D305" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B306" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="1" t="s">
+      <c r="D306" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B307" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="13" t="s">
-        <v>5</v>
+      <c r="D307" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B308" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -6088,80 +6094,80 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B309" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="1" t="s">
+      <c r="D309" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B310" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B311" s="8" t="s">
-        <v>331</v>
+        <v>60169</v>
+      </c>
+      <c r="B311" t="s">
+        <v>250</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="11" t="s">
-        <v>5</v>
+      <c r="D311" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B312" t="s">
-        <v>251</v>
+        <v>60170</v>
+      </c>
+      <c r="B312" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="1" t="s">
+      <c r="D312" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B313" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="13" t="s">
+      <c r="D313" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B314" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
@@ -6172,80 +6178,80 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B315" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="1" t="s">
-        <v>8</v>
+      <c r="D315" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B316" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="10" t="s">
+      <c r="D316" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B317" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="1" t="s">
+      <c r="D317" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B318" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B319" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="10" t="s">
-        <v>8</v>
+      <c r="D319" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B320" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
@@ -6256,38 +6262,38 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B321" s="18" t="s">
-        <v>400</v>
+        <v>60192</v>
+      </c>
+      <c r="B321" t="s">
+        <v>259</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B322" t="s">
-        <v>260</v>
+        <v>60194</v>
+      </c>
+      <c r="B322" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D322" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B323" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
@@ -6298,10 +6304,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B324" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
@@ -6312,52 +6318,52 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B325" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" t="s">
-        <v>9</v>
+      <c r="D325" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B326" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="13" t="s">
-        <v>5</v>
+      <c r="D326" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B327" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="1" t="s">
-        <v>8</v>
+      <c r="D327" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B328" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6368,10 +6374,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B329" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
@@ -6382,192 +6388,192 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B330" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="10" t="s">
+      <c r="D330" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B331" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="1" t="s">
+      <c r="D331" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B332" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="10" t="s">
+      <c r="D332" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B333" t="s">
-        <v>442</v>
+        <v>270</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D333" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B334" t="s">
-        <v>271</v>
+        <v>442</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D334" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B335" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="1" t="s">
+      <c r="D335" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B336" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="10" t="s">
-        <v>5</v>
+      <c r="D336" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B337" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="17" t="s">
-        <v>9</v>
+      <c r="D337" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B338" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="10" t="s">
-        <v>8</v>
+      <c r="D338" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B339" s="8" t="s">
-        <v>332</v>
+        <v>60230</v>
+      </c>
+      <c r="B339" t="s">
+        <v>275</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="7" t="s">
-        <v>9</v>
+      <c r="D339" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D340" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D341" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D342" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6578,10 +6584,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60247</v>
+        <v>60246</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
@@ -6592,10 +6598,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B345" s="18" t="s">
-        <v>399</v>
+        <v>60247</v>
+      </c>
+      <c r="B345" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
@@ -6606,66 +6612,66 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B346" s="8" t="s">
-        <v>333</v>
+        <v>60249</v>
+      </c>
+      <c r="B346" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="11" t="s">
-        <v>8</v>
+      <c r="D346" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B347" t="s">
-        <v>276</v>
+        <v>60250</v>
+      </c>
+      <c r="B347" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="1" t="s">
-        <v>9</v>
+      <c r="D347" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B348" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B349" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B350" t="s">
-        <v>451</v>
+        <v>278</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6676,80 +6682,80 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B351" s="8" t="s">
-        <v>337</v>
+        <v>60258</v>
+      </c>
+      <c r="B351" t="s">
+        <v>451</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="11" t="s">
-        <v>8</v>
+      <c r="D351" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B352" t="s">
-        <v>279</v>
+        <v>60266</v>
+      </c>
+      <c r="B352" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D352" s="10" t="s">
+      <c r="D352" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B353" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="1" t="s">
-        <v>9</v>
+      <c r="D353" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B354" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B355" t="s">
-        <v>372</v>
+        <v>281</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B356" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6760,10 +6766,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B357" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6774,38 +6780,38 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B358" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="13" t="s">
+      <c r="D358" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B359" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="1" t="s">
-        <v>5</v>
+      <c r="D359" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B360" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
@@ -6816,80 +6822,80 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B361" s="8" t="s">
-        <v>330</v>
+        <v>60280</v>
+      </c>
+      <c r="B361" t="s">
+        <v>286</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="11" t="s">
-        <v>9</v>
+      <c r="D361" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D362" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B363" t="s">
-        <v>370</v>
+        <v>60282</v>
+      </c>
+      <c r="B363" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="1" t="s">
-        <v>8</v>
+      <c r="D363" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B364" s="8" t="s">
-        <v>329</v>
+        <v>60283</v>
+      </c>
+      <c r="B364" t="s">
+        <v>370</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="9" t="s">
-        <v>9</v>
+      <c r="D364" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B365" s="8" t="s">
-        <v>444</v>
+        <v>329</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D365" s="9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B366" s="8" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6900,52 +6906,52 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B367" t="s">
-        <v>369</v>
+        <v>60286</v>
+      </c>
+      <c r="B367" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="12" t="s">
+      <c r="D367" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D368" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6956,10 +6962,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B371" s="18" t="s">
-        <v>391</v>
+        <v>60291</v>
+      </c>
+      <c r="B371" t="s">
+        <v>368</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6970,10 +6976,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>60293</v>
+        <v>60292</v>
       </c>
       <c r="B372" s="18" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6984,10 +6990,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B373" t="s">
-        <v>382</v>
+        <v>60293</v>
+      </c>
+      <c r="B373" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6998,10 +7004,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B374" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -7012,10 +7018,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B375" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -7026,10 +7032,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B376" s="18" t="s">
-        <v>401</v>
+        <v>60299</v>
+      </c>
+      <c r="B376" t="s">
+        <v>379</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -7040,10 +7046,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B377" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -7054,10 +7060,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>60305</v>
+        <v>60303</v>
       </c>
       <c r="B378" s="18" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -7068,24 +7074,24 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>60306</v>
+        <v>60305</v>
       </c>
       <c r="B379" s="18" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D379" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>60308</v>
+        <v>60306</v>
       </c>
       <c r="B380" s="18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -7096,38 +7102,38 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B381" t="s">
-        <v>394</v>
+        <v>60308</v>
+      </c>
+      <c r="B381" s="18" t="s">
+        <v>452</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D381" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B382" t="s">
-        <v>287</v>
+        <v>394</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="15" t="s">
-        <v>5</v>
+      <c r="D382" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>61007</v>
+        <v>61004</v>
       </c>
       <c r="B383" t="s">
-        <v>405</v>
+        <v>287</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -7138,24 +7144,24 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>61009</v>
+        <v>61007</v>
       </c>
       <c r="B384" t="s">
-        <v>288</v>
+        <v>405</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D384" s="12" t="s">
-        <v>8</v>
+      <c r="D384" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B385" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -7166,10 +7172,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B386" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7180,10 +7186,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B387" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7194,52 +7200,52 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B388" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="15" t="s">
-        <v>5</v>
+      <c r="D388" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B389" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="12" t="s">
-        <v>8</v>
+      <c r="D389" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B390" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D390" s="15" t="s">
-        <v>5</v>
+      <c r="D390" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B391" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7250,94 +7256,94 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B392" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D392" s="12" t="s">
-        <v>8</v>
+      <c r="D392" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B393" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D393" s="15" t="s">
-        <v>5</v>
+      <c r="D393" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70107</v>
+        <v>70106</v>
       </c>
       <c r="B394" t="s">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D394" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>70109</v>
+        <v>70107</v>
       </c>
       <c r="B395" t="s">
-        <v>298</v>
+        <v>409</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D395" s="12" t="s">
+      <c r="D395" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B396" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D396" s="15" t="s">
-        <v>5</v>
+      <c r="D396" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B397" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D397" s="9" t="s">
-        <v>9</v>
+      <c r="D397" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B398" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7348,38 +7354,38 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>70116</v>
+        <v>70115</v>
       </c>
       <c r="B399" t="s">
-        <v>410</v>
+        <v>325</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D399" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>70117</v>
+        <v>70116</v>
       </c>
       <c r="B400" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D400" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>70118</v>
+        <v>70117</v>
       </c>
       <c r="B401" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7390,24 +7396,24 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>70638</v>
+        <v>70118</v>
       </c>
       <c r="B402" t="s">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D402" s="12" t="s">
-        <v>8</v>
+      <c r="D402" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B403" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7418,10 +7424,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B404" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7432,10 +7438,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B405" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7446,10 +7452,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B406" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7460,10 +7466,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B407" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7474,52 +7480,52 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B408" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D408" s="15" t="s">
-        <v>5</v>
+      <c r="D408" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B409" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D409" s="12" t="s">
+      <c r="D409" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B410" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D410" s="9" t="s">
+      <c r="D410" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B411" s="8" t="s">
-        <v>336</v>
+        <v>90622</v>
+      </c>
+      <c r="B411" t="s">
+        <v>327</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
@@ -7530,24 +7536,24 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B412" t="s">
-        <v>308</v>
+        <v>90631</v>
+      </c>
+      <c r="B412" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D412" s="12" t="s">
-        <v>8</v>
+      <c r="D412" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B413" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
@@ -7558,10 +7564,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B414" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
@@ -7572,10 +7578,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B415" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
@@ -7586,10 +7592,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B416" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7600,10 +7606,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B417" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
@@ -7614,10 +7620,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B418" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
@@ -7628,10 +7634,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B419" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7642,10 +7648,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B420" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
@@ -7656,10 +7662,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B421" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
@@ -7670,38 +7676,38 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B422" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D422" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B423" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D423" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B424" s="8" t="s">
-        <v>374</v>
+        <v>1218</v>
+      </c>
+      <c r="B424" t="s">
+        <v>373</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>4</v>
@@ -7712,10 +7718,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B425" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>4</v>
@@ -7726,10 +7732,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B426" s="8" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>4</v>
@@ -7740,10 +7746,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B427" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>4</v>
@@ -7754,68 +7760,68 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D428" s="9" t="s">
-        <v>9</v>
+      <c r="D428" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B429" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D429" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A430" s="6">
         <v>1045</v>
       </c>
-      <c r="B429" s="8" t="s">
+      <c r="B430" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C429" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D429" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A430">
-        <v>1043</v>
-      </c>
-      <c r="B430" t="s">
-        <v>412</v>
-      </c>
-      <c r="C430" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D430" t="s">
+      <c r="C430" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D430" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431">
+        <v>1043</v>
+      </c>
+      <c r="B431" t="s">
+        <v>412</v>
+      </c>
+      <c r="C431" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D431" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A432">
         <v>20340</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B432" t="s">
         <v>413</v>
       </c>
-      <c r="C431" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D431" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A432">
-        <v>40146</v>
-      </c>
-      <c r="B432" t="s">
-        <v>414</v>
-      </c>
-      <c r="C432" s="14" t="s">
+      <c r="C432" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D432" t="s">
@@ -7824,24 +7830,24 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>60260</v>
+        <v>40146</v>
       </c>
       <c r="B433" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C433" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D433" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>1017</v>
+        <v>60260</v>
       </c>
       <c r="B434" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C434" s="14" t="s">
         <v>4</v>
@@ -7852,10 +7858,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>60300</v>
+        <v>1017</v>
       </c>
       <c r="B435" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C435" s="14" t="s">
         <v>4</v>
@@ -7866,66 +7872,66 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>20191</v>
+        <v>60300</v>
       </c>
       <c r="B436" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>20399</v>
+        <v>20191</v>
       </c>
       <c r="B437" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>60240</v>
+        <v>20399</v>
       </c>
       <c r="B438" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D438" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>60244</v>
+        <v>60240</v>
       </c>
       <c r="B439" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>60248</v>
+        <v>60244</v>
       </c>
       <c r="B440" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
@@ -7936,10 +7942,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>60288</v>
+        <v>60248</v>
       </c>
       <c r="B441" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7950,24 +7956,24 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>90714</v>
+        <v>60288</v>
       </c>
       <c r="B442" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>1014</v>
+        <v>90714</v>
       </c>
       <c r="B443" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
@@ -7978,38 +7984,38 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B444" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D444" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>60301</v>
+        <v>1016</v>
       </c>
       <c r="B445" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C445" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D445" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>1041</v>
+        <v>60301</v>
       </c>
       <c r="B446" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C446" s="14" t="s">
         <v>4</v>
@@ -8020,10 +8026,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="B447" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C447" s="14" t="s">
         <v>4</v>
@@ -8034,38 +8040,38 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>50610</v>
+        <v>971</v>
       </c>
       <c r="B448" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C448" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D448" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="449" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>943</v>
+        <v>50610</v>
       </c>
       <c r="B449" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C449" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D449" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>20306</v>
+        <v>943</v>
       </c>
       <c r="B450" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C450" s="14" t="s">
         <v>4</v>
@@ -8076,24 +8082,24 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451">
-        <v>90630</v>
+        <v>20306</v>
       </c>
       <c r="B451" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C451" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D451" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452">
-        <v>1047</v>
+        <v>90630</v>
       </c>
       <c r="B452" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C452" s="14" t="s">
         <v>4</v>
@@ -8104,62 +8110,76 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453">
-        <v>20398</v>
+        <v>1047</v>
       </c>
       <c r="B453" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C453" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D453" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="454" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454">
-        <v>50226</v>
+        <v>20398</v>
       </c>
       <c r="B454" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="C454" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D454" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="455" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455">
-        <v>20307</v>
+        <v>50226</v>
       </c>
       <c r="B455" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C455" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D455" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="456" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456">
+        <v>20307</v>
+      </c>
+      <c r="B456" t="s">
+        <v>460</v>
+      </c>
+      <c r="C456" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D456" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A457">
         <v>50206</v>
       </c>
-      <c r="B456" s="18" t="s">
+      <c r="B457" s="18" t="s">
         <v>461</v>
       </c>
-      <c r="C456" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D456" s="3" t="s">
+      <c r="C457" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D457" s="3" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D456"/>
+  <autoFilter ref="A1:D457"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$457</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$460</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="471">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1417,6 +1417,24 @@
   </si>
   <si>
     <t>CATAN CITY FERRETERI</t>
+  </si>
+  <si>
+    <t>50836</t>
+  </si>
+  <si>
+    <t>FERRETERIA MAESTRO</t>
+  </si>
+  <si>
+    <t>50814</t>
+  </si>
+  <si>
+    <t>CASA PEKY</t>
+  </si>
+  <si>
+    <t>20297</t>
+  </si>
+  <si>
+    <t>FERRETERIA LUNA</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1543,6 +1561,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1772,7 +1794,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D457"/>
+  <dimension ref="A1:D460"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -4497,25 +4519,25 @@
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="6">
-        <v>20298</v>
-      </c>
-      <c r="B195" t="s">
-        <v>165</v>
+      <c r="A195" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="B195" s="18" t="s">
+        <v>470</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="1" t="s">
-        <v>8</v>
+      <c r="D195" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B196" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4526,10 +4548,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B197" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4540,10 +4562,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B198" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
@@ -4554,24 +4576,24 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B199" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="13" t="s">
-        <v>5</v>
+      <c r="D199" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B200" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4582,122 +4604,122 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B201" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="1" t="s">
-        <v>8</v>
+      <c r="D201" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B202" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="10" t="s">
+      <c r="D202" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B203" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="D203" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
+        <v>20320</v>
+      </c>
+      <c r="B204" t="s">
+        <v>126</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="6">
         <v>20324</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B205" t="s">
         <v>205</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="18" t="s">
+      <c r="C205" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="21" t="s">
         <v>463</v>
       </c>
-      <c r="B205" s="18" t="s">
+      <c r="B206" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="6">
-        <v>20331</v>
-      </c>
-      <c r="B206" t="s">
-        <v>50</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B207" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="13" t="s">
-        <v>5</v>
+      <c r="D207" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B208" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="1" t="s">
-        <v>8</v>
+      <c r="D208" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B209" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
@@ -4708,10 +4730,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B210" t="s">
-        <v>445</v>
+        <v>115</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
@@ -4722,66 +4744,66 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B211" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="13" t="s">
-        <v>5</v>
+      <c r="D211" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B212" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="1" t="s">
-        <v>8</v>
+      <c r="D212" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B213" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="13" t="s">
-        <v>5</v>
+      <c r="D213" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B214" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="10" t="s">
-        <v>8</v>
+      <c r="D214" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B215" t="s">
-        <v>208</v>
+        <v>45</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4792,38 +4814,38 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B216" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="13" t="s">
-        <v>5</v>
+      <c r="D216" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B217" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="1" t="s">
-        <v>8</v>
+      <c r="D217" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B218" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
@@ -4834,10 +4856,10 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B219" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
@@ -4848,10 +4870,10 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B220" t="s">
-        <v>218</v>
+        <v>62</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
@@ -4862,52 +4884,52 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B221" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="10" t="s">
+      <c r="D221" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B222" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="D222" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B223" t="s">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="10" t="s">
+      <c r="D223" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B224" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
@@ -4918,66 +4940,66 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B225" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="13" t="s">
-        <v>5</v>
+      <c r="D225" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B226" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="1" t="s">
-        <v>8</v>
+      <c r="D226" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B227" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="10" t="s">
+      <c r="D227" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B228" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="1" t="s">
+      <c r="D228" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B229" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
@@ -4988,66 +5010,66 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B230" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="10" t="s">
+      <c r="D230" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B231" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="1" t="s">
+      <c r="D231" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B232" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="10" t="s">
+      <c r="D232" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B233" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="1" t="s">
+      <c r="D233" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B234" t="s">
-        <v>324</v>
+        <v>157</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
@@ -5058,52 +5080,52 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B235" s="8" t="s">
-        <v>338</v>
+        <v>20396</v>
+      </c>
+      <c r="B235" t="s">
+        <v>324</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="11" t="s">
-        <v>5</v>
+      <c r="D235" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B236" t="s">
-        <v>163</v>
+        <v>20397</v>
+      </c>
+      <c r="B236" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="1" t="s">
-        <v>8</v>
+      <c r="D236" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B237" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="13" t="s">
-        <v>5</v>
+      <c r="D237" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B238" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
@@ -5114,24 +5136,24 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B239" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="1" t="s">
-        <v>8</v>
+      <c r="D239" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B240" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
@@ -5142,24 +5164,24 @@
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B241" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="10" t="s">
+      <c r="D241" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B242" t="s">
-        <v>321</v>
+        <v>118</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
@@ -5170,66 +5192,66 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B243" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="D243" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B244" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="13" t="s">
-        <v>5</v>
+      <c r="D244" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B245" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="10" t="s">
-        <v>8</v>
+      <c r="D245" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B246" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="13" t="s">
-        <v>5</v>
+      <c r="D246" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B247" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
@@ -5240,206 +5262,206 @@
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B248" t="s">
-        <v>396</v>
+        <v>161</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="19" t="s">
-        <v>8</v>
+      <c r="D248" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B249" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="10" t="s">
+      <c r="D249" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B250" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
+      <c r="D250" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B251" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="13" t="s">
-        <v>5</v>
+      <c r="D251" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B252" t="s">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>8</v>
+      <c r="D252" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B253" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="10" t="s">
+      <c r="D253" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B254" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="3" t="s">
-        <v>5</v>
+      <c r="D254" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B255" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="1" t="s">
-        <v>8</v>
+      <c r="D255" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B256" t="s">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="11" t="s">
-        <v>5</v>
+      <c r="D256" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B257" t="s">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="13" t="s">
+      <c r="D257" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B258" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="1" t="s">
-        <v>8</v>
+      <c r="D258" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B259" s="8" t="s">
-        <v>341</v>
+        <v>50608</v>
+      </c>
+      <c r="B259" t="s">
+        <v>173</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="14" t="s">
-        <v>5</v>
+      <c r="D259" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B260" t="s">
-        <v>93</v>
+        <v>50611</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="16" t="s">
-        <v>8</v>
+      <c r="D260" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B261" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="10" t="s">
+      <c r="D261" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B262" t="s">
-        <v>199</v>
+        <v>107</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
@@ -5450,94 +5472,94 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B263" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="1" t="s">
-        <v>5</v>
+      <c r="D263" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B264" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="14" t="s">
-        <v>8</v>
+      <c r="D264" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B265" t="s">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="1" t="s">
+      <c r="D265" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B266" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="10" t="s">
+      <c r="D266" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B267" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="1" t="s">
+      <c r="D267" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B268" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="13" t="s">
-        <v>5</v>
+      <c r="D268" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B269" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
@@ -5548,24 +5570,24 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B270" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="1" t="s">
-        <v>8</v>
+      <c r="D270" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B271" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
@@ -5576,248 +5598,248 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B272" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="17" t="s">
-        <v>9</v>
+      <c r="D272" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B273" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="10" t="s">
-        <v>8</v>
+      <c r="D273" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="6">
-        <v>50816</v>
-      </c>
-      <c r="B274" t="s">
-        <v>200</v>
+      <c r="A274" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="B274" s="18" t="s">
+        <v>468</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="1" t="s">
-        <v>8</v>
+      <c r="D274" s="22" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50818</v>
+        <v>50815</v>
       </c>
       <c r="B275" t="s">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="13" t="s">
-        <v>5</v>
+      <c r="D275" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50819</v>
+        <v>50816</v>
       </c>
       <c r="B276" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="10" t="s">
+      <c r="D276" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50820</v>
+        <v>50818</v>
       </c>
       <c r="B277" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="10" t="s">
-        <v>8</v>
+      <c r="D277" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>50821</v>
+        <v>50819</v>
       </c>
       <c r="B278" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="1" t="s">
+      <c r="D278" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>50823</v>
+        <v>50820</v>
       </c>
       <c r="B279" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="17" t="s">
-        <v>9</v>
+      <c r="D279" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>50824</v>
+        <v>50821</v>
       </c>
       <c r="B280" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="13" t="s">
-        <v>5</v>
+      <c r="D280" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>50825</v>
+        <v>50823</v>
       </c>
       <c r="B281" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="10" t="s">
-        <v>8</v>
+      <c r="D281" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>50826</v>
+        <v>50824</v>
       </c>
       <c r="B282" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="10" t="s">
-        <v>8</v>
+      <c r="D282" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>50827</v>
+        <v>50825</v>
       </c>
       <c r="B283" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="1" t="s">
+      <c r="D283" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>50829</v>
+        <v>50826</v>
       </c>
       <c r="B284" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="1" t="s">
+      <c r="D284" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>50830</v>
+        <v>50827</v>
       </c>
       <c r="B285" t="s">
-        <v>358</v>
+        <v>230</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="11" t="s">
+      <c r="D285" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>50831</v>
+        <v>50829</v>
       </c>
       <c r="B286" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="11" t="s">
-        <v>9</v>
+      <c r="D286" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B287" s="8" t="s">
-        <v>343</v>
+        <v>50830</v>
+      </c>
+      <c r="B287" t="s">
+        <v>358</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D287" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>50833</v>
-      </c>
-      <c r="B288" s="8" t="s">
-        <v>388</v>
+        <v>50831</v>
+      </c>
+      <c r="B288" t="s">
+        <v>344</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>50230</v>
+        <v>50832</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
@@ -5828,10 +5850,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>50231</v>
+        <v>50833</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
@@ -5841,53 +5863,53 @@
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B291" t="s">
-        <v>232</v>
+      <c r="A291" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="B291" s="18" t="s">
+        <v>466</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="13" t="s">
+      <c r="D291" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60109</v>
-      </c>
-      <c r="B292" t="s">
-        <v>322</v>
+        <v>50230</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>371</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D292" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60124</v>
-      </c>
-      <c r="B293" t="s">
-        <v>233</v>
+        <v>50231</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="13" t="s">
-        <v>5</v>
+      <c r="D293" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60125</v>
+        <v>60103</v>
       </c>
       <c r="B294" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
@@ -5898,80 +5920,80 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60126</v>
+        <v>60109</v>
       </c>
       <c r="B295" t="s">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="10" t="s">
-        <v>8</v>
+      <c r="D295" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60128</v>
+        <v>60124</v>
       </c>
       <c r="B296" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="3" t="s">
+      <c r="D296" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60130</v>
+        <v>60125</v>
       </c>
       <c r="B297" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="1" t="s">
-        <v>8</v>
+      <c r="D297" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60133</v>
+        <v>60126</v>
       </c>
       <c r="B298" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="13" t="s">
-        <v>5</v>
+      <c r="D298" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="B299" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="1" t="s">
-        <v>8</v>
+      <c r="D299" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60137</v>
+        <v>60130</v>
       </c>
       <c r="B300" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5982,38 +6004,38 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60139</v>
+        <v>60133</v>
       </c>
       <c r="B301" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="1" t="s">
-        <v>8</v>
+      <c r="D301" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60142</v>
+        <v>60134</v>
       </c>
       <c r="B302" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60148</v>
+        <v>60137</v>
       </c>
       <c r="B303" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -6024,10 +6046,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60149</v>
+        <v>60139</v>
       </c>
       <c r="B304" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -6038,38 +6060,38 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60150</v>
+        <v>60142</v>
       </c>
       <c r="B305" t="s">
-        <v>326</v>
+        <v>242</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="13" t="s">
+      <c r="D305" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60158</v>
+        <v>60148</v>
       </c>
       <c r="B306" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="10" t="s">
+      <c r="D306" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60159</v>
+        <v>60149</v>
       </c>
       <c r="B307" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -6080,10 +6102,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60162</v>
+        <v>60150</v>
       </c>
       <c r="B308" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -6094,66 +6116,66 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60163</v>
+        <v>60158</v>
       </c>
       <c r="B309" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="13" t="s">
-        <v>5</v>
+      <c r="D309" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60165</v>
+        <v>60159</v>
       </c>
       <c r="B310" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60169</v>
+        <v>60162</v>
       </c>
       <c r="B311" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="1" t="s">
-        <v>8</v>
+      <c r="D311" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B312" s="8" t="s">
-        <v>331</v>
+        <v>60163</v>
+      </c>
+      <c r="B312" t="s">
+        <v>248</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="11" t="s">
+      <c r="D312" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60172</v>
+        <v>60165</v>
       </c>
       <c r="B313" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -6164,94 +6186,94 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60174</v>
+        <v>60169</v>
       </c>
       <c r="B314" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="13" t="s">
-        <v>5</v>
+      <c r="D314" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60176</v>
-      </c>
-      <c r="B315" t="s">
-        <v>253</v>
+        <v>60170</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="13" t="s">
+      <c r="D315" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60178</v>
+        <v>60172</v>
       </c>
       <c r="B316" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60180</v>
+        <v>60174</v>
       </c>
       <c r="B317" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="10" t="s">
-        <v>8</v>
+      <c r="D317" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60184</v>
+        <v>60176</v>
       </c>
       <c r="B318" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="1" t="s">
-        <v>8</v>
+      <c r="D318" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60190</v>
+        <v>60178</v>
       </c>
       <c r="B319" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60191</v>
+        <v>60180</v>
       </c>
       <c r="B320" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
@@ -6262,38 +6284,38 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60192</v>
+        <v>60184</v>
       </c>
       <c r="B321" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="10" t="s">
+      <c r="D321" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B322" s="18" t="s">
-        <v>400</v>
+        <v>60190</v>
+      </c>
+      <c r="B322" t="s">
+        <v>257</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="10" t="s">
-        <v>5</v>
+      <c r="D322" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60195</v>
+        <v>60191</v>
       </c>
       <c r="B323" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
@@ -6304,10 +6326,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60196</v>
+        <v>60192</v>
       </c>
       <c r="B324" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
@@ -6318,108 +6340,108 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60198</v>
-      </c>
-      <c r="B325" t="s">
-        <v>262</v>
+        <v>60194</v>
+      </c>
+      <c r="B325" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D325" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60201</v>
+        <v>60195</v>
       </c>
       <c r="B326" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" t="s">
-        <v>9</v>
+      <c r="D326" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60202</v>
+        <v>60196</v>
       </c>
       <c r="B327" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="13" t="s">
-        <v>5</v>
+      <c r="D327" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60204</v>
+        <v>60198</v>
       </c>
       <c r="B328" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="1" t="s">
+      <c r="D328" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60205</v>
+        <v>60201</v>
       </c>
       <c r="B329" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="1" t="s">
-        <v>8</v>
+      <c r="D329" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60206</v>
+        <v>60202</v>
       </c>
       <c r="B330" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="1" t="s">
-        <v>8</v>
+      <c r="D330" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60209</v>
+        <v>60204</v>
       </c>
       <c r="B331" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="10" t="s">
+      <c r="D331" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60211</v>
+        <v>60205</v>
       </c>
       <c r="B332" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6430,24 +6452,24 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60215</v>
+        <v>60206</v>
       </c>
       <c r="B333" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="10" t="s">
+      <c r="D333" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60216</v>
+        <v>60209</v>
       </c>
       <c r="B334" t="s">
-        <v>442</v>
+        <v>268</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6458,136 +6480,136 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60217</v>
+        <v>60211</v>
       </c>
       <c r="B335" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="10" t="s">
+      <c r="D335" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60219</v>
+        <v>60215</v>
       </c>
       <c r="B336" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="1" t="s">
+      <c r="D336" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60222</v>
+        <v>60216</v>
       </c>
       <c r="B337" t="s">
-        <v>273</v>
+        <v>442</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D337" s="10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60225</v>
+        <v>60217</v>
       </c>
       <c r="B338" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="17" t="s">
-        <v>9</v>
+      <c r="D338" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60230</v>
+        <v>60219</v>
       </c>
       <c r="B339" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="10" t="s">
+      <c r="D339" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B340" s="8" t="s">
-        <v>332</v>
+        <v>60222</v>
+      </c>
+      <c r="B340" t="s">
+        <v>273</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="7" t="s">
-        <v>9</v>
+      <c r="D340" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60242</v>
-      </c>
-      <c r="B341" s="8" t="s">
-        <v>335</v>
+        <v>60225</v>
+      </c>
+      <c r="B341" t="s">
+        <v>274</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="7" t="s">
-        <v>5</v>
+      <c r="D341" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60243</v>
-      </c>
-      <c r="B342" s="8" t="s">
-        <v>386</v>
+        <v>60230</v>
+      </c>
+      <c r="B342" t="s">
+        <v>275</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="7" t="s">
-        <v>9</v>
+      <c r="D342" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60245</v>
+        <v>60241</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D343" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60246</v>
+        <v>60242</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>398</v>
+        <v>335</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
@@ -6598,24 +6620,24 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60247</v>
+        <v>60243</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>438</v>
+        <v>386</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D345" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B346" s="18" t="s">
-        <v>399</v>
+        <v>60245</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>378</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
@@ -6626,346 +6648,346 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60250</v>
+        <v>60246</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="11" t="s">
-        <v>8</v>
+      <c r="D347" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B348" t="s">
-        <v>276</v>
+        <v>60247</v>
+      </c>
+      <c r="B348" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="1" t="s">
-        <v>9</v>
+      <c r="D348" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60254</v>
-      </c>
-      <c r="B349" t="s">
-        <v>277</v>
+        <v>60249</v>
+      </c>
+      <c r="B349" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="1" t="s">
-        <v>8</v>
+      <c r="D349" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60257</v>
-      </c>
-      <c r="B350" t="s">
-        <v>278</v>
+        <v>60250</v>
+      </c>
+      <c r="B350" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="1" t="s">
-        <v>5</v>
+      <c r="D350" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60258</v>
+        <v>60253</v>
       </c>
       <c r="B351" t="s">
-        <v>451</v>
+        <v>276</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B352" s="8" t="s">
-        <v>337</v>
+        <v>60254</v>
+      </c>
+      <c r="B352" t="s">
+        <v>277</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D352" s="11" t="s">
+      <c r="D352" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60269</v>
+        <v>60257</v>
       </c>
       <c r="B353" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="10" t="s">
-        <v>8</v>
+      <c r="D353" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60270</v>
+        <v>60258</v>
       </c>
       <c r="B354" t="s">
-        <v>280</v>
+        <v>451</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60272</v>
-      </c>
-      <c r="B355" t="s">
-        <v>281</v>
+        <v>60266</v>
+      </c>
+      <c r="B355" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="1" t="s">
-        <v>5</v>
+      <c r="D355" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60274</v>
+        <v>60269</v>
       </c>
       <c r="B356" t="s">
-        <v>372</v>
+        <v>279</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="1" t="s">
+      <c r="D356" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60275</v>
+        <v>60270</v>
       </c>
       <c r="B357" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60276</v>
+        <v>60272</v>
       </c>
       <c r="B358" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60278</v>
+        <v>60274</v>
       </c>
       <c r="B359" t="s">
-        <v>284</v>
+        <v>372</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="13" t="s">
+      <c r="D359" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60279</v>
+        <v>60275</v>
       </c>
       <c r="B360" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60280</v>
+        <v>60276</v>
       </c>
       <c r="B361" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B362" s="8" t="s">
-        <v>330</v>
+        <v>60278</v>
+      </c>
+      <c r="B362" t="s">
+        <v>284</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="11" t="s">
-        <v>9</v>
+      <c r="D362" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60282</v>
-      </c>
-      <c r="B363" s="8" t="s">
-        <v>334</v>
+        <v>60279</v>
+      </c>
+      <c r="B363" t="s">
+        <v>285</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="11" t="s">
+      <c r="D363" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>60283</v>
+        <v>60280</v>
       </c>
       <c r="B364" t="s">
-        <v>370</v>
+        <v>286</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>60284</v>
+        <v>60281</v>
       </c>
       <c r="B365" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="9" t="s">
+      <c r="D365" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>60285</v>
+        <v>60282</v>
       </c>
       <c r="B366" s="8" t="s">
-        <v>444</v>
+        <v>334</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="9" t="s">
+      <c r="D366" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>60286</v>
-      </c>
-      <c r="B367" s="8" t="s">
-        <v>328</v>
+        <v>60283</v>
+      </c>
+      <c r="B367" t="s">
+        <v>370</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="9" t="s">
-        <v>5</v>
+      <c r="D367" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B368" t="s">
-        <v>369</v>
+        <v>60284</v>
+      </c>
+      <c r="B368" s="8" t="s">
+        <v>329</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="12" t="s">
-        <v>5</v>
+      <c r="D368" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>60289</v>
-      </c>
-      <c r="B369" t="s">
-        <v>366</v>
+        <v>60285</v>
+      </c>
+      <c r="B369" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="12" t="s">
-        <v>9</v>
+      <c r="D369" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>60290</v>
-      </c>
-      <c r="B370" t="s">
-        <v>367</v>
+        <v>60286</v>
+      </c>
+      <c r="B370" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="12" t="s">
+      <c r="D370" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>60291</v>
+        <v>60287</v>
       </c>
       <c r="B371" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6976,24 +6998,24 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B372" s="18" t="s">
-        <v>391</v>
+        <v>60289</v>
+      </c>
+      <c r="B372" t="s">
+        <v>366</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D372" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>60293</v>
-      </c>
-      <c r="B373" s="18" t="s">
-        <v>408</v>
+        <v>60290</v>
+      </c>
+      <c r="B373" t="s">
+        <v>367</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -7004,10 +7026,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>60296</v>
+        <v>60291</v>
       </c>
       <c r="B374" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -7018,10 +7040,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>60297</v>
-      </c>
-      <c r="B375" t="s">
-        <v>383</v>
+        <v>60292</v>
+      </c>
+      <c r="B375" s="18" t="s">
+        <v>391</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -7032,10 +7054,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>60299</v>
-      </c>
-      <c r="B376" t="s">
-        <v>379</v>
+        <v>60293</v>
+      </c>
+      <c r="B376" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -7046,10 +7068,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B377" s="18" t="s">
-        <v>401</v>
+        <v>60296</v>
+      </c>
+      <c r="B377" t="s">
+        <v>382</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -7060,10 +7082,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>60303</v>
-      </c>
-      <c r="B378" s="18" t="s">
-        <v>402</v>
+        <v>60297</v>
+      </c>
+      <c r="B378" t="s">
+        <v>383</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -7074,10 +7096,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>60305</v>
-      </c>
-      <c r="B379" s="18" t="s">
-        <v>436</v>
+        <v>60299</v>
+      </c>
+      <c r="B379" t="s">
+        <v>379</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -7088,80 +7110,80 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>60306</v>
+        <v>60302</v>
       </c>
       <c r="B380" s="18" t="s">
-        <v>453</v>
+        <v>401</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D380" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>60308</v>
+        <v>60303</v>
       </c>
       <c r="B381" s="18" t="s">
-        <v>452</v>
+        <v>402</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D381" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B382" t="s">
-        <v>394</v>
+        <v>60305</v>
+      </c>
+      <c r="B382" s="18" t="s">
+        <v>436</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D382" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>61004</v>
-      </c>
-      <c r="B383" t="s">
-        <v>287</v>
+        <v>60306</v>
+      </c>
+      <c r="B383" s="18" t="s">
+        <v>453</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="15" t="s">
-        <v>5</v>
+      <c r="D383" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>61007</v>
-      </c>
-      <c r="B384" t="s">
-        <v>405</v>
+        <v>60308</v>
+      </c>
+      <c r="B384" s="18" t="s">
+        <v>452</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D384" s="15" t="s">
-        <v>5</v>
+      <c r="D384" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>61009</v>
+        <v>61001</v>
       </c>
       <c r="B385" t="s">
-        <v>288</v>
+        <v>394</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -7172,38 +7194,38 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>61012</v>
+        <v>61004</v>
       </c>
       <c r="B386" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="12" t="s">
-        <v>8</v>
+      <c r="D386" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>61018</v>
+        <v>61007</v>
       </c>
       <c r="B387" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="12" t="s">
-        <v>8</v>
+      <c r="D387" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>61102</v>
+        <v>61009</v>
       </c>
       <c r="B388" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7214,24 +7236,24 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>61205</v>
+        <v>61012</v>
       </c>
       <c r="B389" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="15" t="s">
-        <v>5</v>
+      <c r="D389" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>70100</v>
+        <v>61018</v>
       </c>
       <c r="B390" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7242,24 +7264,24 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>70101</v>
+        <v>61102</v>
       </c>
       <c r="B391" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D391" s="15" t="s">
-        <v>5</v>
+      <c r="D391" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>70102</v>
+        <v>61205</v>
       </c>
       <c r="B392" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7270,10 +7292,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>70103</v>
+        <v>70100</v>
       </c>
       <c r="B393" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7284,10 +7306,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>70106</v>
+        <v>70101</v>
       </c>
       <c r="B394" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7298,24 +7320,24 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>70107</v>
+        <v>70102</v>
       </c>
       <c r="B395" t="s">
-        <v>409</v>
+        <v>295</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D395" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>70109</v>
+        <v>70103</v>
       </c>
       <c r="B396" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7326,10 +7348,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>70113</v>
+        <v>70106</v>
       </c>
       <c r="B397" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7340,52 +7362,52 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>70114</v>
+        <v>70107</v>
       </c>
       <c r="B398" t="s">
-        <v>319</v>
+        <v>409</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D398" s="9" t="s">
-        <v>9</v>
+      <c r="D398" s="15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>70115</v>
+        <v>70109</v>
       </c>
       <c r="B399" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D399" s="9" t="s">
-        <v>9</v>
+      <c r="D399" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>70116</v>
+        <v>70113</v>
       </c>
       <c r="B400" t="s">
-        <v>410</v>
+        <v>299</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D400" s="9" t="s">
-        <v>8</v>
+      <c r="D400" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>70117</v>
+        <v>70114</v>
       </c>
       <c r="B401" t="s">
-        <v>457</v>
+        <v>319</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7396,10 +7418,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>70118</v>
+        <v>70115</v>
       </c>
       <c r="B402" t="s">
-        <v>458</v>
+        <v>325</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7410,52 +7432,52 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>70638</v>
+        <v>70116</v>
       </c>
       <c r="B403" t="s">
-        <v>300</v>
+        <v>410</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D403" s="12" t="s">
+      <c r="D403" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>70639</v>
+        <v>70117</v>
       </c>
       <c r="B404" t="s">
-        <v>301</v>
+        <v>457</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D404" s="12" t="s">
-        <v>8</v>
+      <c r="D404" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>70640</v>
+        <v>70118</v>
       </c>
       <c r="B405" t="s">
-        <v>302</v>
+        <v>458</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D405" s="12" t="s">
-        <v>8</v>
+      <c r="D405" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>70642</v>
+        <v>70638</v>
       </c>
       <c r="B406" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
@@ -7466,10 +7488,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
-        <v>90504</v>
+        <v>70639</v>
       </c>
       <c r="B407" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
@@ -7480,10 +7502,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6">
-        <v>90509</v>
+        <v>70640</v>
       </c>
       <c r="B408" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
@@ -7494,108 +7516,108 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6">
-        <v>90602</v>
+        <v>70642</v>
       </c>
       <c r="B409" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D409" s="15" t="s">
-        <v>5</v>
+      <c r="D409" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6">
-        <v>90621</v>
+        <v>90504</v>
       </c>
       <c r="B410" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D410" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6">
-        <v>90622</v>
+        <v>90509</v>
       </c>
       <c r="B411" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D411" s="9" t="s">
-        <v>5</v>
+      <c r="D411" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B412" s="8" t="s">
-        <v>336</v>
+        <v>90602</v>
+      </c>
+      <c r="B412" t="s">
+        <v>306</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D412" s="9" t="s">
+      <c r="D412" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6">
-        <v>90658</v>
+        <v>90621</v>
       </c>
       <c r="B413" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D413" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6">
-        <v>90660</v>
+        <v>90622</v>
       </c>
       <c r="B414" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D414" s="12" t="s">
-        <v>8</v>
+      <c r="D414" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6">
-        <v>90668</v>
-      </c>
-      <c r="B415" t="s">
-        <v>310</v>
+        <v>90631</v>
+      </c>
+      <c r="B415" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D415" s="12" t="s">
-        <v>8</v>
+      <c r="D415" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="416" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6">
-        <v>90671</v>
+        <v>90658</v>
       </c>
       <c r="B416" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
@@ -7606,10 +7628,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6">
-        <v>90679</v>
+        <v>90660</v>
       </c>
       <c r="B417" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
@@ -7620,10 +7642,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6">
-        <v>90683</v>
+        <v>90668</v>
       </c>
       <c r="B418" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
@@ -7634,10 +7656,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6">
-        <v>90705</v>
+        <v>90671</v>
       </c>
       <c r="B419" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
@@ -7648,10 +7670,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6">
-        <v>90706</v>
+        <v>90679</v>
       </c>
       <c r="B420" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
@@ -7662,10 +7684,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6">
-        <v>90708</v>
+        <v>90683</v>
       </c>
       <c r="B421" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
@@ -7676,10 +7698,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6">
-        <v>90709</v>
+        <v>90705</v>
       </c>
       <c r="B422" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>4</v>
@@ -7690,24 +7712,24 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6">
-        <v>90713</v>
+        <v>90706</v>
       </c>
       <c r="B423" t="s">
-        <v>393</v>
+        <v>315</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D423" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6">
-        <v>1218</v>
+        <v>90708</v>
       </c>
       <c r="B424" t="s">
-        <v>373</v>
+        <v>316</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>4</v>
@@ -7718,10 +7740,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B425" s="8" t="s">
-        <v>374</v>
+        <v>90709</v>
+      </c>
+      <c r="B425" t="s">
+        <v>317</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>4</v>
@@ -7732,24 +7754,24 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B426" s="8" t="s">
-        <v>375</v>
+        <v>90713</v>
+      </c>
+      <c r="B426" t="s">
+        <v>393</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D426" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6">
-        <v>1817</v>
-      </c>
-      <c r="B427" s="8" t="s">
-        <v>380</v>
+        <v>1218</v>
+      </c>
+      <c r="B427" t="s">
+        <v>373</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>4</v>
@@ -7760,10 +7782,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6">
-        <v>5737</v>
+        <v>1959</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>4</v>
@@ -7774,136 +7796,136 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6">
-        <v>60295</v>
+        <v>5625</v>
       </c>
       <c r="B429" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D429" s="9" t="s">
-        <v>9</v>
+      <c r="D429" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A430" s="6">
+        <v>1817</v>
+      </c>
+      <c r="B430" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C430" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D430" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A431" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B431" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="C431" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D431" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A432" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B432" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D432" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A433" s="6">
         <v>1045</v>
       </c>
-      <c r="B430" s="8" t="s">
+      <c r="B433" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C430" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D430" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A431">
+      <c r="C433" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D433" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A434">
         <v>1043</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B434" t="s">
         <v>412</v>
       </c>
-      <c r="C431" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D431" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A432">
+      <c r="C434" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D434" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A435">
         <v>20340</v>
       </c>
-      <c r="B432" t="s">
+      <c r="B435" t="s">
         <v>413</v>
       </c>
-      <c r="C432" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D432" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A433">
-        <v>40146</v>
-      </c>
-      <c r="B433" t="s">
-        <v>414</v>
-      </c>
-      <c r="C433" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D433" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A434">
-        <v>60260</v>
-      </c>
-      <c r="B434" t="s">
-        <v>415</v>
-      </c>
-      <c r="C434" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D434" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A435">
-        <v>1017</v>
-      </c>
-      <c r="B435" t="s">
-        <v>416</v>
-      </c>
-      <c r="C435" s="14" t="s">
+      <c r="C435" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>60300</v>
+        <v>40146</v>
       </c>
       <c r="B436" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C436" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>20191</v>
+        <v>60260</v>
       </c>
       <c r="B437" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C437" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>20399</v>
+        <v>1017</v>
       </c>
       <c r="B438" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C438" s="14" t="s">
         <v>4</v>
@@ -7914,38 +7936,38 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>60240</v>
+        <v>60300</v>
       </c>
       <c r="B439" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C439" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>60244</v>
+        <v>20191</v>
       </c>
       <c r="B440" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C440" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D440" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>60248</v>
+        <v>20399</v>
       </c>
       <c r="B441" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C441" s="14" t="s">
         <v>4</v>
@@ -7956,52 +7978,52 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>60288</v>
+        <v>60240</v>
       </c>
       <c r="B442" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C442" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>90714</v>
+        <v>60244</v>
       </c>
       <c r="B443" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C443" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D443" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>1014</v>
+        <v>60248</v>
       </c>
       <c r="B444" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C444" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D444" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>1016</v>
+        <v>60288</v>
       </c>
       <c r="B445" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C445" s="14" t="s">
         <v>4</v>
@@ -8012,10 +8034,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>60301</v>
+        <v>90714</v>
       </c>
       <c r="B446" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C446" s="14" t="s">
         <v>4</v>
@@ -8026,10 +8048,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>1041</v>
+        <v>1014</v>
       </c>
       <c r="B447" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C447" s="14" t="s">
         <v>4</v>
@@ -8040,38 +8062,38 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>971</v>
+        <v>1016</v>
       </c>
       <c r="B448" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C448" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D448" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="449" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>50610</v>
+        <v>60301</v>
       </c>
       <c r="B449" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C449" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D449" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>943</v>
+        <v>1041</v>
       </c>
       <c r="B450" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C450" s="14" t="s">
         <v>4</v>
@@ -8082,10 +8104,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451">
-        <v>20306</v>
+        <v>971</v>
       </c>
       <c r="B451" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C451" s="14" t="s">
         <v>4</v>
@@ -8096,10 +8118,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452">
-        <v>90630</v>
+        <v>50610</v>
       </c>
       <c r="B452" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C452" s="14" t="s">
         <v>4</v>
@@ -8110,24 +8132,24 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453">
-        <v>1047</v>
+        <v>943</v>
       </c>
       <c r="B453" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C453" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D453" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="454" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454">
-        <v>20398</v>
+        <v>20306</v>
       </c>
       <c r="B454" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C454" s="14" t="s">
         <v>4</v>
@@ -8138,10 +8160,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455">
-        <v>50226</v>
+        <v>90630</v>
       </c>
       <c r="B455" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="C455" s="14" t="s">
         <v>4</v>
@@ -8152,34 +8174,76 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456">
-        <v>20307</v>
+        <v>1047</v>
       </c>
       <c r="B456" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="C456" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D456" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="457" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457">
+        <v>20398</v>
+      </c>
+      <c r="B457" t="s">
+        <v>435</v>
+      </c>
+      <c r="C457" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D457" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>50226</v>
+      </c>
+      <c r="B458" t="s">
+        <v>456</v>
+      </c>
+      <c r="C458" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D458" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>20307</v>
+      </c>
+      <c r="B459" t="s">
+        <v>460</v>
+      </c>
+      <c r="C459" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D459" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A460">
         <v>50206</v>
       </c>
-      <c r="B457" s="18" t="s">
+      <c r="B460" s="18" t="s">
         <v>461</v>
       </c>
-      <c r="C457" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D457" s="3" t="s">
+      <c r="C460" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D460" s="3" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D457"/>
+  <autoFilter ref="A1:D460"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -4249,7 +4249,7 @@
         <v>4</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6937,7 +6937,7 @@
         <v>4</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
